--- a/submissions/03-pretreatment-smr-q3-2026/solution/vandeveer_smr_q3_2026.xlsx
+++ b/submissions/03-pretreatment-smr-q3-2026/solution/vandeveer_smr_q3_2026.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C14DF9-BE80-FC4F-8661-85C351BF425D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7102B0D2-22D9-AF4A-A743-BA70419E34A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="377">
   <si>
     <t>SELF-MONITORING REPORT, THIRD QUARTER 2026 (JULY 1 THROUGH SEPTEMBER 30, 2026)</t>
   </si>
@@ -130,7 +130,7 @@
     <t>SEPTEMBER 2026</t>
   </si>
   <si>
-    <t>In-line meter: one excursion, 09/17/2026</t>
+    <t>In-line meter: one excursion, 09/17/2026; the 6.0 low of 09/11/2026 is inside the range</t>
   </si>
   <si>
     <t>Exceeded</t>
@@ -175,55 +175,64 @@
     <t>July 2026</t>
   </si>
   <si>
+    <t>Copper, monthly average, one valid sample</t>
+  </si>
+  <si>
+    <t>2.07 mg/L</t>
+  </si>
+  <si>
+    <t>The July 21 result stands alone after the July 7 sample's metals were analyzed outside the holding period</t>
+  </si>
+  <si>
+    <t>Cadmium, chromium, copper, nickel and zinc, monitoring frequency</t>
+  </si>
+  <si>
+    <t>2 valid samples</t>
+  </si>
+  <si>
+    <t>Section 2.3</t>
+  </si>
+  <si>
+    <t>Metals of sample VP-260707 analyzed 08/06/2026, 30 days after collection, outside the 28-day holding period; the laboratory reported the month on 08/07/2026 after it had ended, so no replacement could be collected</t>
+  </si>
+  <si>
+    <t>08/11/2026</t>
+  </si>
+  <si>
+    <t>Copper, daily maximum, sample VP-260811</t>
+  </si>
+  <si>
+    <t>Copper carryover from the plating line</t>
+  </si>
+  <si>
+    <t>08/25/2026</t>
+  </si>
+  <si>
+    <t>Copper, daily maximum, sample VP-260825</t>
+  </si>
+  <si>
+    <t>August 2026</t>
+  </si>
+  <si>
     <t>Copper, monthly average</t>
   </si>
   <si>
-    <t>2.07 mg/L</t>
-  </si>
-  <si>
     <t>Same cause as the daily maximum exceedances</t>
   </si>
   <si>
-    <t>08/11/2026</t>
-  </si>
-  <si>
-    <t>Copper, daily maximum, sample VP-260811</t>
-  </si>
-  <si>
-    <t>Copper carryover from the plating line</t>
-  </si>
-  <si>
-    <t>08/25/2026</t>
-  </si>
-  <si>
-    <t>Copper, daily maximum, sample VP-260825</t>
-  </si>
-  <si>
-    <t>4.15</t>
-  </si>
-  <si>
-    <t>August 2026</t>
-  </si>
-  <si>
     <t>Nickel, monthly average, one valid sample</t>
   </si>
   <si>
     <t>2.38 mg/L</t>
   </si>
   <si>
-    <t>Nickel result of 08/11/2026 stands alone after the 08/25/2026 sample was invalidated</t>
+    <t>Nickel result of 08/11/2026 stands alone after the 08/25/2026 nickel result was analyzed 34 days after collection, outside the holding period</t>
   </si>
   <si>
     <t>Nickel, monitoring frequency</t>
   </si>
   <si>
-    <t>2 valid samples</t>
-  </si>
-  <si>
-    <t>Section 2.3</t>
-  </si>
-  <si>
-    <t>Laboratory holding time exceeded on sample VP-260825; no replacement before month end</t>
+    <t>Nickel of sample VP-260825 analyzed 09/28/2026, outside the 28-day holding period; no replacement before month end</t>
   </si>
   <si>
     <t>09/09/2026</t>
@@ -250,7 +259,7 @@
     <t>The 09/09/2026 result carries the month</t>
   </si>
   <si>
-    <t>Flow, daily</t>
+    <t>Flow, daily, worked from the totalizer register</t>
   </si>
   <si>
     <t>45,000 gallons per day</t>
@@ -304,7 +313,7 @@
     <t>Section 2.4 and Section 4.2</t>
   </si>
   <si>
-    <t>Acid dump from the pickle tank; caustic feed increased, pH 6.9 by 15:00</t>
+    <t>Acid dump from the pickle tank; caustic feed increased, pH 6.9 by 15:00; called in at 15:20 and reported in writing 09/21/2026</t>
   </si>
   <si>
     <t>07/31/2026</t>
@@ -316,7 +325,7 @@
     <t>none made</t>
   </si>
   <si>
-    <t>Plant relied on the laboratory's copy of the report to the City</t>
+    <t>No call in the City's telephone log after the laboratory report; the laboratory's copy of the report to the City is not a notice under Section 3.2</t>
   </si>
   <si>
     <t>08/21/2026</t>
@@ -334,7 +343,7 @@
     <t>SIX-MONTH SIGNIFICANT NONCOMPLIANCE EVALUATION, APRIL THROUGH SEPTEMBER 2026</t>
   </si>
   <si>
-    <t>Copper measurements in the period</t>
+    <t>Copper measurements in the period, valid results only</t>
   </si>
   <si>
     <t>Copper measurements above the technical review criterion threshold</t>
@@ -349,7 +358,7 @@
     <t>Copper significant noncompliance status</t>
   </si>
   <si>
-    <t>No other parameter reaches either threshold; see the evaluation tab for every parameter.</t>
+    <t>No other parameter reaches either threshold; see the evaluation tab for every parameter. The second quarter report reached the City on 07/14/2026 against its 07/15/2026 due date, so the report arm of Section 3.4 is not triggered.</t>
   </si>
   <si>
     <t>CERTIFICATION</t>
@@ -436,10 +445,19 @@
     <t>Section 3.1 of the permit</t>
   </si>
   <si>
+    <t>Holding period, total metals, days from collection</t>
+  </si>
+  <si>
+    <t>Section 2.3 of the permit (40 CFR Part 136); the period the laboratory's chain of custody log states</t>
+  </si>
+  <si>
+    <t>Holding period, total cyanide, days from collection</t>
+  </si>
+  <si>
     <t>Laboratory results April through September 2026, Outfall 001, as reported (lab_results_apr_sep2026.xlsx)</t>
   </si>
   <si>
-    <t>RESULT and QUAL are the laboratory's figures as typed. VALID is N for a result qualified H (holding time exceeded) or NS (not sampled), Section 2.3. TREATED carries a U result at zero for averaging, Section 2.2.</t>
+    <t>RESULT and QUAL are the laboratory's figures as typed; the ANALYZED dates are from the laboratory's chain of custody log, and the SERIAL columns carry the same dates as Excel serials for the day count. VALID is N for a result not sampled (NS) or analyzed more than the holding period after collection, Section 2.3 and Parameters rows 23 and 24. TREATED carries a U result at zero for averaging, Section 2.2.</t>
   </si>
   <si>
     <t>SAMPLE ID</t>
@@ -532,6 +550,36 @@
     <t>LAB REPORT DATE</t>
   </si>
   <si>
+    <t>METALS ANALYZED</t>
+  </si>
+  <si>
+    <t>NICKEL ANALYZED</t>
+  </si>
+  <si>
+    <t>CYANIDE ANALYZED</t>
+  </si>
+  <si>
+    <t>METALS HOLD DAYS</t>
+  </si>
+  <si>
+    <t>NICKEL HOLD DAYS</t>
+  </si>
+  <si>
+    <t>CYANIDE HOLD DAYS</t>
+  </si>
+  <si>
+    <t>COLLECTED, SERIAL</t>
+  </si>
+  <si>
+    <t>METALS ANALYZED, SERIAL</t>
+  </si>
+  <si>
+    <t>NICKEL ANALYZED, SERIAL</t>
+  </si>
+  <si>
+    <t>CYANIDE ANALYZED, SERIAL</t>
+  </si>
+  <si>
     <t>VP-260407</t>
   </si>
   <si>
@@ -550,6 +598,12 @@
     <t>04/17/2026</t>
   </si>
   <si>
+    <t>04/11/2026</t>
+  </si>
+  <si>
+    <t>04/12/2026</t>
+  </si>
+  <si>
     <t>VP-260421</t>
   </si>
   <si>
@@ -559,6 +613,12 @@
     <t>04/30/2026</t>
   </si>
   <si>
+    <t>04/25/2026</t>
+  </si>
+  <si>
+    <t>04/23/2026</t>
+  </si>
+  <si>
     <t>VP-260505</t>
   </si>
   <si>
@@ -571,6 +631,12 @@
     <t>05/14/2026</t>
   </si>
   <si>
+    <t>05/08/2026</t>
+  </si>
+  <si>
+    <t>05/10/2026</t>
+  </si>
+  <si>
     <t>VP-260519</t>
   </si>
   <si>
@@ -583,6 +649,12 @@
     <t>05/29/2026</t>
   </si>
   <si>
+    <t>05/26/2026</t>
+  </si>
+  <si>
+    <t>05/25/2026</t>
+  </si>
+  <si>
     <t>VP-260602</t>
   </si>
   <si>
@@ -595,6 +667,12 @@
     <t>06/12/2026</t>
   </si>
   <si>
+    <t>06/08/2026</t>
+  </si>
+  <si>
+    <t>06/07/2026</t>
+  </si>
+  <si>
     <t>VP-260616</t>
   </si>
   <si>
@@ -604,6 +682,12 @@
     <t>06/26/2026</t>
   </si>
   <si>
+    <t>07/13/2026</t>
+  </si>
+  <si>
+    <t>06/18/2026</t>
+  </si>
+  <si>
     <t>VP-260707</t>
   </si>
   <si>
@@ -613,7 +697,10 @@
     <t>Jul</t>
   </si>
   <si>
-    <t>07/17/2026</t>
+    <t>08/07/2026</t>
+  </si>
+  <si>
+    <t>08/06/2026</t>
   </si>
   <si>
     <t>VP-260721</t>
@@ -622,6 +709,12 @@
     <t>07/30/2026</t>
   </si>
   <si>
+    <t>07/26/2026</t>
+  </si>
+  <si>
+    <t>07/25/2026</t>
+  </si>
+  <si>
     <t>VP-260811</t>
   </si>
   <si>
@@ -631,15 +724,27 @@
     <t>08/20/2026</t>
   </si>
   <si>
+    <t>08/15/2026</t>
+  </si>
+  <si>
+    <t>08/14/2026</t>
+  </si>
+  <si>
     <t>VP-260825</t>
   </si>
   <si>
-    <t>H</t>
-  </si>
-  <si>
     <t>09/04/2026</t>
   </si>
   <si>
+    <t>08/29/2026</t>
+  </si>
+  <si>
+    <t>09/28/2026</t>
+  </si>
+  <si>
+    <t>08/27/2026</t>
+  </si>
+  <si>
     <t>VP-260909</t>
   </si>
   <si>
@@ -649,15 +754,21 @@
     <t>09/15/2026</t>
   </si>
   <si>
+    <t>09/12/2026</t>
+  </si>
+  <si>
+    <t>09/22/2026</t>
+  </si>
+  <si>
     <t>VP-260922</t>
   </si>
   <si>
-    <t>09/22/2026</t>
-  </si>
-  <si>
     <t>10/01/2026</t>
   </si>
   <si>
+    <t>09/30/2026</t>
+  </si>
+  <si>
     <t>VP-260923</t>
   </si>
   <si>
@@ -670,10 +781,16 @@
     <t>NS</t>
   </si>
   <si>
+    <t>09/26/2026</t>
+  </si>
+  <si>
+    <t>not collected</t>
+  </si>
+  <si>
     <t>Monthly averages and daily maximums by parameter, April through September 2026</t>
   </si>
   <si>
-    <t>Monthly average is the arithmetic mean of the valid results in the month, resamples included, non-detects at zero (Section 2.2); daily maximum is the highest valid result in the month. A month with fewer valid samples than required is monitored below frequency (Section 2.3).</t>
+    <t>Monthly average is the arithmetic mean of the valid results in the month, resamples included, non-detects at zero (Section 2.2); daily maximum is the highest valid result in the month. A result analyzed outside its holding period is not a valid sample, and a month with fewer valid samples than required is monitored below frequency (Section 2.3).</t>
   </si>
   <si>
     <t>DAILY MAXIMUM LIMIT</t>
@@ -739,18 +856,54 @@
     <t>TRC THRESHOLD PCT</t>
   </si>
   <si>
-    <t>A parameter in significant noncompliance is published in the City's annual notice and goes to the enforcement response plan (Section 3.4). Copper is the one parameter over the technical review criterion threshold.</t>
-  </si>
-  <si>
-    <t>Daily flow, September 2026, gallons, from the operator log</t>
-  </si>
-  <si>
-    <t>FLOW GALLONS</t>
+    <t>A parameter in significant noncompliance is published in the City's annual notice and goes to the enforcement response plan (Section 3.4). Copper is the one parameter over the technical review criterion threshold, and only because the July 7 sample's metals are not valid measurements.</t>
+  </si>
+  <si>
+    <t>REPORT DUE IN THE PERIOD</t>
+  </si>
+  <si>
+    <t>DUE</t>
+  </si>
+  <si>
+    <t>RECEIVED</t>
+  </si>
+  <si>
+    <t>45-DAY ARM OF SECTION 3.4</t>
+  </si>
+  <si>
+    <t>Second quarter self-monitoring report (Section 3.1)</t>
+  </si>
+  <si>
+    <t>07/15/2026</t>
+  </si>
+  <si>
+    <t>07/14/2026</t>
+  </si>
+  <si>
+    <t>Not late</t>
+  </si>
+  <si>
+    <t>The received date is the Pretreatment Coordinator's, from her note of September 30, 2026.</t>
+  </si>
+  <si>
+    <t>Daily flow, September 2026, gallons, worked from the totalizer register readings in the operator log</t>
+  </si>
+  <si>
+    <t>The log carries the register at 07:00 the following morning; a day's flow is that reading less the one before it. The month's total is the end register less the start register.</t>
+  </si>
+  <si>
+    <t>REGISTER AT 07:00 NEXT DAY, GAL</t>
+  </si>
+  <si>
+    <t>DAILY FLOW, GAL</t>
   </si>
   <si>
     <t>ABOVE LIMIT</t>
   </si>
   <si>
+    <t>Register at 07:00 on 09/01/2026</t>
+  </si>
+  <si>
     <t>09/01/2026</t>
   </si>
   <si>
@@ -772,9 +925,6 @@
     <t>09/11/2026</t>
   </si>
   <si>
-    <t>09/12/2026</t>
-  </si>
-  <si>
     <t>09/13/2026</t>
   </si>
   <si>
@@ -802,28 +952,22 @@
     <t>09/25/2026</t>
   </si>
   <si>
-    <t>09/26/2026</t>
-  </si>
-  <si>
     <t>09/27/2026</t>
   </si>
   <si>
-    <t>09/28/2026</t>
-  </si>
-  <si>
     <t>09/29/2026</t>
   </si>
   <si>
-    <t>09/30/2026</t>
-  </si>
-  <si>
     <t>Highest daily flow in September</t>
   </si>
   <si>
     <t>Days above the daily flow limit</t>
   </si>
   <si>
-    <t>Total for the month, ties to the totalizer register in the operator log</t>
+    <t>Total for the month, the end register less the start register</t>
+  </si>
+  <si>
+    <t>Sum of the daily flows, which ties to the register total</t>
   </si>
   <si>
     <t>Notifications and resampling the quarter required, with the dates due and the dates done</t>
@@ -838,9 +982,6 @@
     <t>REQUIREMENT</t>
   </si>
   <si>
-    <t>DUE</t>
-  </si>
-  <si>
     <t>DONE</t>
   </si>
   <si>
@@ -874,6 +1015,21 @@
     <t>Written report within 5 days</t>
   </si>
   <si>
+    <t>In-line pH excursion of 09/17/2026, 14:10 to 14:55, called in as a discharge under Section 3.2</t>
+  </si>
+  <si>
+    <t>09/17/2026 14:10</t>
+  </si>
+  <si>
+    <t>09/18/2026 14:10</t>
+  </si>
+  <si>
+    <t>09/17/2026 15:20</t>
+  </si>
+  <si>
+    <t>In-line pH excursion of 09/17/2026, written report</t>
+  </si>
+  <si>
     <t>Zinc daily maximum exceedance, sample VP-260909, 3.14 mg/L</t>
   </si>
   <si>
@@ -901,9 +1057,6 @@
     <t>Resample within 30 days; a routine sample in the period satisfies it</t>
   </si>
   <si>
-    <t>08/29/2026</t>
-  </si>
-  <si>
     <t>08/11/2026 routine sample</t>
   </si>
   <si>
@@ -940,12 +1093,27 @@
     <t>07/31/2026, 08/21/2026, 09/05/2026</t>
   </si>
   <si>
-    <t>Not made; the laboratory's copies to the City are not a telephone notice</t>
+    <t>Not made; the City's telephone log for the quarter shows the calls of 09/10/2026 and 09/17/2026 only</t>
   </si>
   <si>
     <t>Not made</t>
   </si>
   <si>
+    <t>Second quarter self-monitoring report</t>
+  </si>
+  <si>
+    <t>Section 3.1 and Section 3.4</t>
+  </si>
+  <si>
+    <t>06/30/2026 (quarter end)</t>
+  </si>
+  <si>
+    <t>Report in the Attachment B format by the 15th; 45 days late is significant noncompliance</t>
+  </si>
+  <si>
+    <t>07/14/2026, received by the City</t>
+  </si>
+  <si>
     <t>Third quarter self-monitoring report</t>
   </si>
   <si>
@@ -973,25 +1141,28 @@
     <t>Re: Third quarter 2026 self-monitoring report, Permit IP-0421, before you sign</t>
   </si>
   <si>
-    <t>The overflow is not the quarter's only problem. The six-month review that Renee runs on the April through September results puts the plant in significant noncompliance for copper under Section 3.4: 5 of the 13 copper measurements since April exceed the daily maximum by more than the technical review criterion of 1.2, which is 38.5 percent against the 33 percent threshold, so the plant goes into the annual publication and the enforcement response plan on copper. The overflow and its notice produce five lines in the violations table, and copper produces eight more.</t>
-  </si>
-  <si>
-    <t>Copper exceeded the daily maximum on July 21 at 4.09 mg/L, on August 11 at 4.33 mg/L, and on August 25 at 4.15 mg/L, against the 3.38 mg/L limit, and the July and August monthly averages of 2.93 mg/L and 4.24 mg/L exceed the 2.07 mg/L limit. September's copper average is 2.053 mg/L and meets the limit only because the resample of September 23 counts in the month's average, as Section 2.2 provides. Without the resample the September average would be 2.32 mg/L.</t>
-  </si>
-  <si>
-    <t>The September 9 overflow is a bypass under Section 4.1, and it is reported as one. Zinc on the composite that day was 3.14 mg/L against the 2.61 mg/L daily maximum, and that one result carries the September zinc average to 1.653 mg/L against the 1.48 mg/L monthly limit. The day's flow of 47,300 gallons is above the 45,000 gallon daily limit. The telephone notice to Renee was made at 16:30 on September 10, which is past the 24 hours Section 3.2 allows from the 07:50 event, so the late notice is reported as a violation of Section 3.2. The written report of September 14 was inside the five days.</t>
-  </si>
-  <si>
-    <t>The resample requirement of Section 3.3 is met on every exceedance. The zinc resample was due within 30 days of the September 15 lab report and was collected on September 22 and September 23. Each of the three copper exceedances was followed by a routine sample inside its 30-day period, which Section 3.3 accepts.</t>
-  </si>
-  <si>
-    <t>Nickel has a reporting problem in August. The laboratory invalidated the nickel result on the August 25 sample for holding time, so the August nickel average rests on the August 11 result alone, 2.61 mg/L against the 2.38 mg/L monthly limit, and August is reported as monitored below the required frequency for nickel under Section 2.3, since no replacement sample was collected before the month ended.</t>
-  </si>
-  <si>
-    <t>The in-line pH reading of 5.8 on September 17, from 14:10 to 14:55 during the pickle tank acid dump, is a violation under Section 2.4 even though the grab readings at every sampling event were inside the range, and it is listed with its duration and cause. Not-detected results are carried at zero in the averages, as Section 2.2 directs, which is why the September cadmium average reads 0.004 mg/L rather than the detection limit.</t>
-  </si>
-  <si>
-    <t>Section 3.2 also calls for a telephone notice within 24 hours of becoming aware of any discharge exceeding a daily maximum. No call was made after the July 30, August 20 or September 4 lab reports on the copper exceedances, as you say in your note, and the laboratory's copies to Renee are not the telephone notice the section calls for. Those three are reported as violations of Section 3.2 in the violations table.</t>
+    <t>The overflow is not the quarter's only problem. The six-month review that Renee runs on the April through September results puts the plant in significant noncompliance for copper under Section 3.4: 4 of the 12 copper measurements since April exceed the daily maximum by more than the technical review criterion of 1.2, which is 33.3 percent against the 33 percent threshold, so the plant goes into the annual publication and the enforcement response plan on copper. The count is 12 rather than 13 because the July 7 sample's metals are not valid measurements, and that one reading is what puts the plant over the line.</t>
+  </si>
+  <si>
+    <t>The laboratory's chain of custody log shows the metals on sample VP-260707 of July 7 analyzed on August 6, 30 days after collection and outside the 28-day holding period for total metals, so under Section 2.3 that sample is not a valid sample for cadmium, chromium, copper, nickel or zinc. The laboratory did not flag it, and it shows only in the analysis dates. With the July 7 sample counted, the share would read 30.8 percent, and the plant would be clear. The permit does not allow it to be counted. The same test drops the August 25 nickel result, analyzed on September 28, 34 days after collection. The June 16 metals, analyzed on July 13 at 27 days, and the September 9 cyanide, analyzed on September 22 at 13 days, are inside their holding periods and stand.</t>
+  </si>
+  <si>
+    <t>July is reported as monitored below the required frequency for the five metals, since the laboratory reported the July 7 sample on August 7 after the month had ended and no replacement could be collected in July. The July copper monthly average therefore rests on the July 21 result alone, 4.09 mg/L against the 2.07 mg/L limit, and August's is 4.24 mg/L. Copper exceeded the daily maximum on July 21 at 4.09 mg/L, on August 11 at 4.33 mg/L, and on August 25 at 4.15 mg/L, against the 3.38 mg/L limit. September's copper average is 2.053 mg/L and meets the limit only because the resample of September 23 counts in the month's average, as Section 2.2 provides. Without the resample the September average would be 2.32 mg/L.</t>
+  </si>
+  <si>
+    <t>The September 9 overflow is a bypass under Section 4.1, and it is reported as one. Zinc on the composite that day was 3.14 mg/L against the 2.61 mg/L daily maximum, and that one result carries the September zinc average to 1.653 mg/L against the 1.48 mg/L monthly limit. The day's flow, worked from the totalizer register readings in Luis's log, is 47,300 gallons against the 45,000 gallon daily limit. The telephone notice to Renee was made at 16:30 on September 10, which is past the 24 hours Section 3.2 allows from the 07:50 event, so the late notice is reported as a violation of Section 3.2. The written report of September 14 was inside the five days.</t>
+  </si>
+  <si>
+    <t>The pH reading of 5.8 on the in-line meter on September 17, from 14:10 to 14:55 during the pickle tank acid dump, is a violation under Section 2.4 and Section 4.2 even though every grab at sampling was inside the range, and it is listed with its duration and cause. Luis's call to Renee at 15:20 the same afternoon and the written report of September 21 meet Section 3.2 on that event. The meter's low of 6.0 on the morning of September 11 is inside the range and is not a violation.</t>
+  </si>
+  <si>
+    <t>Nickel has a reporting problem in August. The August 25 nickel result is not valid under Section 2.3, so the August nickel average rests on the August 11 result alone, 2.61 mg/L against the 2.38 mg/L monthly limit, and August is reported as monitored below the required frequency for nickel, since no replacement sample was collected before the month ended. Not-detected results are carried at zero in the averages, as Section 2.2 directs, which is why the September cadmium average reads 0.004 mg/L rather than the detection limit.</t>
+  </si>
+  <si>
+    <t>Section 3.2 also calls for a telephone notice within 24 hours of becoming aware of any discharge exceeding a daily maximum, and Section 3.3 dates awareness to the laboratory report. Renee's telephone log for the quarter shows the calls of September 10 and September 17 and nothing after the July 30, August 20 or September 4 lab reports on the copper exceedances, and the laboratory's copies to Renee are not the telephone notice the section calls for. Those three are reported as violations of Section 3.2 in the violations table. The resample requirement of Section 3.3 is met on every exceedance: the zinc resample was due within 30 days of the September 15 lab report and was collected on September 22 and September 23, and each of the three copper exceedances was followed by a routine sample inside its 30-day period, which Section 3.3 accepts.</t>
+  </si>
+  <si>
+    <t>The second quarter report reached Renee on July 14 against its July 15 due date, so the report arm of Section 3.4 is not triggered, and no parameter other than copper reaches either threshold.</t>
   </si>
   <si>
     <t>Two things the file leaves open. Whether Renee treats the laboratory's copies of the July and August reports as any notice at all is her call, and the report states the facts as the file shows them. The copper treatment itself is the plant's to fix, and the report states the cause only as far as the log and the lab results show it.</t>
@@ -1070,7 +1241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1095,6 +1266,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1397,7 +1569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -1410,7 +1582,7 @@
     <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1481,7 +1653,7 @@
       </c>
       <c r="D8" s="2">
         <f>'Monthly Stats'!E23</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2">
         <f>'Monthly Stats'!F23</f>
@@ -1505,7 +1677,7 @@
       </c>
       <c r="J8" s="2" t="str">
         <f>'Monthly Stats'!K23</f>
-        <v>Met</v>
+        <v>Below frequency</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1522,7 +1694,7 @@
       </c>
       <c r="D9" s="2">
         <f>'Monthly Stats'!E24</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2">
         <f>'Monthly Stats'!F24</f>
@@ -1530,7 +1702,7 @@
       </c>
       <c r="F9" s="6">
         <f>'Monthly Stats'!G24</f>
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="G9" s="6">
         <f>'Monthly Stats'!H24</f>
@@ -1546,7 +1718,7 @@
       </c>
       <c r="J9" s="2" t="str">
         <f>'Monthly Stats'!K24</f>
-        <v>Met</v>
+        <v>Below frequency</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1563,7 +1735,7 @@
       </c>
       <c r="D10" s="2">
         <f>'Monthly Stats'!E25</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2">
         <f>'Monthly Stats'!F25</f>
@@ -1571,7 +1743,7 @@
       </c>
       <c r="F10" s="6">
         <f>'Monthly Stats'!G25</f>
-        <v>2.93</v>
+        <v>4.09</v>
       </c>
       <c r="G10" s="6">
         <f>'Monthly Stats'!H25</f>
@@ -1587,7 +1759,7 @@
       </c>
       <c r="J10" s="2" t="str">
         <f>'Monthly Stats'!K25</f>
-        <v>Met</v>
+        <v>Below frequency</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1604,7 +1776,7 @@
       </c>
       <c r="D11" s="2">
         <f>'Monthly Stats'!E26</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2">
         <f>'Monthly Stats'!F26</f>
@@ -1612,7 +1784,7 @@
       </c>
       <c r="F11" s="6">
         <f>'Monthly Stats'!G26</f>
-        <v>1.395</v>
+        <v>1.57</v>
       </c>
       <c r="G11" s="6">
         <f>'Monthly Stats'!H26</f>
@@ -1628,7 +1800,7 @@
       </c>
       <c r="J11" s="2" t="str">
         <f>'Monthly Stats'!K26</f>
-        <v>Met</v>
+        <v>Below frequency</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -1645,7 +1817,7 @@
       </c>
       <c r="D12" s="2">
         <f>'Monthly Stats'!E27</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2">
         <f>'Monthly Stats'!F27</f>
@@ -1653,7 +1825,7 @@
       </c>
       <c r="F12" s="6">
         <f>'Monthly Stats'!G27</f>
-        <v>1.165</v>
+        <v>1.27</v>
       </c>
       <c r="G12" s="6">
         <f>'Monthly Stats'!H27</f>
@@ -1669,7 +1841,7 @@
       </c>
       <c r="J12" s="2" t="str">
         <f>'Monthly Stats'!K27</f>
-        <v>Met</v>
+        <v>Below frequency</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -2465,7 +2637,7 @@
         <v>27</v>
       </c>
       <c r="G37" s="8">
-        <f>'Flow Sep'!$B$34</f>
+        <f>'Flow Sep'!$B$36</f>
         <v>47300</v>
       </c>
       <c r="H37" s="2" t="s">
@@ -2504,7 +2676,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="70" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
         <v>40</v>
       </c>
@@ -2525,7 +2697,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
         <v>45</v>
       </c>
@@ -2534,7 +2706,7 @@
       </c>
       <c r="C42" s="10">
         <f>'Monthly Stats'!G25</f>
-        <v>2.93</v>
+        <v>4.09</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>47</v>
@@ -2546,37 +2718,38 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="C43" s="11">
+        <f>'Monthly Stats'!E25</f>
+        <v>1</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="10">
+      <c r="E43" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="10">
         <f>'Monthly Stats'!H31</f>
         <v>4.33</v>
       </c>
-      <c r="D43" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="42" x14ac:dyDescent="0.2">
-      <c r="A44" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="D44" s="9" t="s">
         <v>42</v>
       </c>
@@ -2584,125 +2757,125 @@
         <v>43</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="42" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" s="10">
+        <f>'Lab Data'!M14</f>
+        <v>4.15</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" s="10">
+    </row>
+    <row r="46" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" s="10">
         <f>'Monthly Stats'!G31</f>
         <v>4.24</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D46" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E46" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F45" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="84" x14ac:dyDescent="0.2">
-      <c r="A46" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C46" s="10">
+      <c r="F46" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" s="10">
         <f>'Monthly Stats'!G32</f>
         <v>2.61</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E46" s="9" t="s">
+      <c r="D47" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="F47" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="9" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" ht="84" x14ac:dyDescent="0.2">
-      <c r="A47" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C47" s="11">
+      <c r="B48" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="11">
         <f>'Monthly Stats'!E32</f>
         <v>1</v>
       </c>
-      <c r="D47" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="42" x14ac:dyDescent="0.2">
-      <c r="A48" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="10">
+      <c r="D48" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="10">
         <f>'Monthly Stats'!H39</f>
         <v>3.14</v>
       </c>
-      <c r="D48" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E48" s="9" t="s">
+      <c r="D49" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F48" s="9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="42" x14ac:dyDescent="0.2">
-      <c r="A49" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C49" s="10">
+      <c r="F49" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="10">
         <f>'Monthly Stats'!G39</f>
         <v>1.653</v>
       </c>
-      <c r="D49" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="70" x14ac:dyDescent="0.2">
-      <c r="A50" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C50" s="12">
-        <f>'Flow Sep'!$B$34</f>
-        <v>47300</v>
-      </c>
       <c r="D50" s="9" t="s">
         <v>72</v>
       </c>
@@ -2713,209 +2886,237 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="56" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" s="12">
+        <f>'Flow Sep'!$B$36</f>
+        <v>47300</v>
+      </c>
+      <c r="D51" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="E51" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F51" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E51" s="9" t="s">
+    </row>
+    <row r="52" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="C52" s="9" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="70" x14ac:dyDescent="0.2">
-      <c r="A52" s="9" t="s">
+      <c r="D52" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="E52" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="F52" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D52" s="9" t="s">
+    </row>
+    <row r="53" spans="1:6" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="B53" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="C53" s="9" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" ht="70" x14ac:dyDescent="0.2">
-      <c r="A53" s="9" t="s">
+      <c r="D53" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="E53" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="F53" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D53" s="9" t="s">
+    </row>
+    <row r="54" spans="1:6" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D54" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E53" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="98" x14ac:dyDescent="0.2">
-      <c r="A54" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B54" s="9" t="s">
+      <c r="E54" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="F54" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="D54" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F54" s="9" t="s">
+    </row>
+    <row r="55" spans="1:6" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="9" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" ht="98" x14ac:dyDescent="0.2">
-      <c r="A55" s="9" t="s">
+      <c r="B55" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="C55" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C55" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="D55" s="9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="98" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="98" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F56" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B56" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>93</v>
+    </row>
+    <row r="57" spans="1:6" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="A58" s="3"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B59" s="2">
-        <f>'SNC Review'!B7</f>
-        <v>13</v>
-      </c>
+      <c r="A59" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B59" s="2"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B60" s="2">
-        <f>'SNC Review'!H7</f>
-        <v>5</v>
+        <f>'SNC Review'!B7</f>
+        <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B61" s="7">
-        <f>'SNC Review'!I7</f>
-        <v>38.5</v>
+        <v>103</v>
+      </c>
+      <c r="B61" s="2">
+        <f>'SNC Review'!H7</f>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B62" s="2">
+        <v>104</v>
+      </c>
+      <c r="B62" s="7">
+        <f>'SNC Review'!I7</f>
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B63" s="2">
         <f>Parameters!$B$18</f>
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B63" s="13" t="str">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B64" s="13" t="str">
         <f>'SNC Review'!L7</f>
         <v>Significant noncompliance</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="2" t="s">
-        <v>104</v>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" s="2" t="s">
-        <v>107</v>
+      <c r="A66" s="3"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="9" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2925,7 +3126,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
@@ -2935,9 +3136,9 @@
     <col min="5" max="5" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -2951,10 +3152,10 @@
         <v>10</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -2971,7 +3172,7 @@
         <v>0.005</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -2988,7 +3189,7 @@
         <v>0.01</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -3005,7 +3206,7 @@
         <v>0.01</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -3022,7 +3223,7 @@
         <v>0.02</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -3039,7 +3240,7 @@
         <v>0.02</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -3056,12 +3257,12 @@
         <v>0.005</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>36</v>
@@ -3069,128 +3270,150 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B12" s="8">
         <v>45000</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B13" s="7">
         <v>6</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B14" s="7">
         <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B15" s="14">
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B16" s="7">
         <v>1.2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B17" s="14">
         <v>66</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B18" s="14">
         <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B19" s="14">
         <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B20" s="14">
         <v>5</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B21" s="14">
         <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B22" s="14">
         <v>15</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" s="14">
+        <v>28</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" s="14">
+        <v>14</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -3200,7 +3423,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:AN17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -3219,136 +3442,168 @@
     <col min="24" max="25" width="9" customWidth="1"/>
     <col min="26" max="27" width="7" customWidth="1"/>
     <col min="28" max="29" width="9" customWidth="1"/>
-    <col min="30" max="30" width="14" customWidth="1"/>
+    <col min="30" max="33" width="14" customWidth="1"/>
+    <col min="34" max="36" width="11" customWidth="1"/>
+    <col min="37" max="40" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="AA4" s="4" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AB4" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AC4" s="4" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="AD4" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+      <c r="AE4" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="AF4" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="AG4" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="AH4" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="AI4" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="AJ4" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="AK4" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="AL4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="AM4" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="AN4" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E5" s="6">
         <v>0.005</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="G5" s="2" t="str">
-        <f t="shared" ref="G5:G17" si="0">IF(OR(F5="H",F5="NS"),"N","Y")</f>
+        <f>IF(F5="NS","N",IF($AH5&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="H5" s="6">
-        <f t="shared" ref="H5:H17" si="1">IF(F5="U",0,E5)</f>
+        <f t="shared" ref="H5:H17" si="0">IF(F5="U",0,E5)</f>
         <v>0</v>
       </c>
       <c r="I5" s="6">
@@ -3356,11 +3611,11 @@
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="str">
-        <f t="shared" ref="K5:K17" si="2">IF(OR(J5="H",J5="NS"),"N","Y")</f>
+        <f>IF(J5="NS","N",IF($AH5&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="L5" s="6">
-        <f t="shared" ref="L5:L17" si="3">IF(J5="U",0,I5)</f>
+        <f t="shared" ref="L5:L17" si="1">IF(J5="U",0,I5)</f>
         <v>0.62</v>
       </c>
       <c r="M5" s="6">
@@ -3368,11 +3623,11 @@
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2" t="str">
-        <f t="shared" ref="O5:O17" si="4">IF(OR(N5="H",N5="NS"),"N","Y")</f>
+        <f>IF(N5="NS","N",IF($AH5&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="P5" s="6">
-        <f t="shared" ref="P5:P17" si="5">IF(N5="U",0,M5)</f>
+        <f t="shared" ref="P5:P17" si="2">IF(N5="U",0,M5)</f>
         <v>1.84</v>
       </c>
       <c r="Q5" s="6">
@@ -3380,11 +3635,11 @@
       </c>
       <c r="R5" s="2"/>
       <c r="S5" s="2" t="str">
-        <f t="shared" ref="S5:S17" si="6">IF(OR(R5="H",R5="NS"),"N","Y")</f>
+        <f>IF(R5="NS","N",IF($AI5&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="T5" s="6">
-        <f t="shared" ref="T5:T17" si="7">IF(R5="U",0,Q5)</f>
+        <f t="shared" ref="T5:T17" si="3">IF(R5="U",0,Q5)</f>
         <v>0.91</v>
       </c>
       <c r="U5" s="6">
@@ -3392,11 +3647,11 @@
       </c>
       <c r="V5" s="2"/>
       <c r="W5" s="2" t="str">
-        <f t="shared" ref="W5:W17" si="8">IF(OR(V5="H",V5="NS"),"N","Y")</f>
+        <f>IF(V5="NS","N",IF($AH5&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="X5" s="6">
-        <f t="shared" ref="X5:X17" si="9">IF(V5="U",0,U5)</f>
+        <f t="shared" ref="X5:X17" si="4">IF(V5="U",0,U5)</f>
         <v>0.74</v>
       </c>
       <c r="Y5" s="6">
@@ -3404,43 +3659,80 @@
       </c>
       <c r="Z5" s="2"/>
       <c r="AA5" s="2" t="str">
-        <f t="shared" ref="AA5:AA17" si="10">IF(OR(Z5="H",Z5="NS"),"N","Y")</f>
+        <f>IF(Z5="NS","N",IF($AJ5&gt;Parameters!$B$24,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="AB5" s="6">
-        <f t="shared" ref="AB5:AB17" si="11">IF(Z5="U",0,Y5)</f>
+        <f t="shared" ref="AB5:AB17" si="5">IF(Z5="U",0,Y5)</f>
         <v>0.18</v>
       </c>
       <c r="AC5" s="7">
         <v>7.4</v>
       </c>
       <c r="AD5" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+        <v>186</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="AH5" s="14">
+        <f t="shared" ref="AH5:AH17" si="6">_xlfn.DAYS(AL5,AK5)</f>
+        <v>4</v>
+      </c>
+      <c r="AI5" s="14">
+        <f t="shared" ref="AI5:AI17" si="7">_xlfn.DAYS(AM5,AK5)</f>
+        <v>4</v>
+      </c>
+      <c r="AJ5" s="14">
+        <f t="shared" ref="AJ5:AJ16" si="8">_xlfn.DAYS(AN5,AK5)</f>
+        <v>5</v>
+      </c>
+      <c r="AK5" s="14">
+        <f t="shared" ref="AK5:AK17" si="9">DATE(VALUE(RIGHT(B5,4)),VALUE(LEFT(B5,2)),VALUE(MID(B5,4,2)))</f>
+        <v>46119</v>
+      </c>
+      <c r="AL5" s="14">
+        <f t="shared" ref="AL5:AL16" si="10">DATE(VALUE(RIGHT(AE5,4)),VALUE(LEFT(AE5,2)),VALUE(MID(AE5,4,2)))</f>
+        <v>46123</v>
+      </c>
+      <c r="AM5" s="14">
+        <f t="shared" ref="AM5:AM16" si="11">DATE(VALUE(RIGHT(AF5,4)),VALUE(LEFT(AF5,2)),VALUE(MID(AF5,4,2)))</f>
+        <v>46123</v>
+      </c>
+      <c r="AN5" s="14">
+        <f t="shared" ref="AN5:AN16" si="12">DATE(VALUE(RIGHT(AG5,4)),VALUE(LEFT(AG5,2)),VALUE(MID(AG5,4,2)))</f>
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E6" s="6">
         <v>0.012</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="str">
+        <f>IF(F6="NS","N",IF($AH6&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>Y</v>
+      </c>
+      <c r="H6" s="6">
         <f t="shared" si="0"/>
-        <v>Y</v>
-      </c>
-      <c r="H6" s="6">
-        <f t="shared" si="1"/>
         <v>0.012</v>
       </c>
       <c r="I6" s="6">
@@ -3448,11 +3740,11 @@
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(J6="NS","N",IF($AH6&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="L6" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.48</v>
       </c>
       <c r="M6" s="6">
@@ -3460,11 +3752,11 @@
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N6="NS","N",IF($AH6&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="P6" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>3.62</v>
       </c>
       <c r="Q6" s="6">
@@ -3472,11 +3764,11 @@
       </c>
       <c r="R6" s="2"/>
       <c r="S6" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(R6="NS","N",IF($AI6&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="T6" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1.44</v>
       </c>
       <c r="U6" s="6">
@@ -3484,11 +3776,11 @@
       </c>
       <c r="V6" s="2"/>
       <c r="W6" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(V6="NS","N",IF($AH6&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="X6" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1.12</v>
       </c>
       <c r="Y6" s="6">
@@ -3496,45 +3788,82 @@
       </c>
       <c r="Z6" s="2"/>
       <c r="AA6" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(Z6="NS","N",IF($AJ6&gt;Parameters!$B$24,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="AB6" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0.31</v>
       </c>
       <c r="AC6" s="7">
         <v>7.1</v>
       </c>
       <c r="AD6" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+        <v>191</v>
+      </c>
+      <c r="AE6" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AF6" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="AH6" s="14">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AI6" s="14">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="AJ6" s="14">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="AK6" s="14">
+        <f t="shared" si="9"/>
+        <v>46133</v>
+      </c>
+      <c r="AL6" s="14">
+        <f t="shared" si="10"/>
+        <v>46137</v>
+      </c>
+      <c r="AM6" s="14">
+        <f t="shared" si="11"/>
+        <v>46137</v>
+      </c>
+      <c r="AN6" s="14">
+        <f t="shared" si="12"/>
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E7" s="6">
         <v>0.005</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="G7" s="2" t="str">
+        <f>IF(F7="NS","N",IF($AH7&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>Y</v>
+      </c>
+      <c r="H7" s="6">
         <f t="shared" si="0"/>
-        <v>Y</v>
-      </c>
-      <c r="H7" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I7" s="6">
@@ -3542,11 +3871,11 @@
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(J7="NS","N",IF($AH7&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="L7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.13</v>
       </c>
       <c r="M7" s="6">
@@ -3554,11 +3883,11 @@
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N7="NS","N",IF($AH7&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="P7" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>4.21</v>
       </c>
       <c r="Q7" s="6">
@@ -3566,11 +3895,11 @@
       </c>
       <c r="R7" s="2"/>
       <c r="S7" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(R7="NS","N",IF($AI7&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="T7" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0.77</v>
       </c>
       <c r="U7" s="6">
@@ -3578,11 +3907,11 @@
       </c>
       <c r="V7" s="2"/>
       <c r="W7" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(V7="NS","N",IF($AH7&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="X7" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>0.68</v>
       </c>
       <c r="Y7" s="6">
@@ -3590,45 +3919,82 @@
       </c>
       <c r="Z7" s="2"/>
       <c r="AA7" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(Z7="NS","N",IF($AJ7&gt;Parameters!$B$24,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="AB7" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0.22</v>
       </c>
       <c r="AC7" s="7">
         <v>8.2</v>
       </c>
       <c r="AD7" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+        <v>197</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="AF7" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="AH7" s="14">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AI7" s="14">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="AJ7" s="14">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="AK7" s="14">
+        <f t="shared" si="9"/>
+        <v>46147</v>
+      </c>
+      <c r="AL7" s="14">
+        <f t="shared" si="10"/>
+        <v>46150</v>
+      </c>
+      <c r="AM7" s="14">
+        <f t="shared" si="11"/>
+        <v>46150</v>
+      </c>
+      <c r="AN7" s="14">
+        <f t="shared" si="12"/>
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E8" s="6">
         <v>0.005</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="G8" s="2" t="str">
+        <f>IF(F8="NS","N",IF($AH8&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>Y</v>
+      </c>
+      <c r="H8" s="6">
         <f t="shared" si="0"/>
-        <v>Y</v>
-      </c>
-      <c r="H8" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I8" s="6">
@@ -3636,11 +4002,11 @@
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(J8="NS","N",IF($AH8&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="L8" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.71</v>
       </c>
       <c r="M8" s="6">
@@ -3648,11 +4014,11 @@
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N8="NS","N",IF($AH8&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="P8" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1.95</v>
       </c>
       <c r="Q8" s="6">
@@ -3660,11 +4026,11 @@
       </c>
       <c r="R8" s="2"/>
       <c r="S8" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(R8="NS","N",IF($AI8&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="T8" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1.68</v>
       </c>
       <c r="U8" s="6">
@@ -3672,57 +4038,94 @@
       </c>
       <c r="V8" s="2"/>
       <c r="W8" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(V8="NS","N",IF($AH8&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="X8" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>0.95</v>
       </c>
       <c r="Y8" s="6">
         <v>0.008</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="AA8" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(Z8="NS","N",IF($AJ8&gt;Parameters!$B$24,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="AB8" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0.008</v>
       </c>
       <c r="AC8" s="7">
         <v>7.6</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="AF8" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="AH8" s="14">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="AI8" s="14">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="AJ8" s="14">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="AK8" s="14">
+        <f t="shared" si="9"/>
+        <v>46161</v>
+      </c>
+      <c r="AL8" s="14">
+        <f t="shared" si="10"/>
+        <v>46168</v>
+      </c>
+      <c r="AM8" s="14">
+        <f t="shared" si="11"/>
+        <v>46168</v>
+      </c>
+      <c r="AN8" s="14">
+        <f t="shared" si="12"/>
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="E9" s="6">
         <v>0.019</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="str">
+        <f>IF(F9="NS","N",IF($AH9&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>Y</v>
+      </c>
+      <c r="H9" s="6">
         <f t="shared" si="0"/>
-        <v>Y</v>
-      </c>
-      <c r="H9" s="6">
-        <f t="shared" si="1"/>
         <v>0.019</v>
       </c>
       <c r="I9" s="6">
@@ -3730,11 +4133,11 @@
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(J9="NS","N",IF($AH9&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="L9" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.55</v>
       </c>
       <c r="M9" s="6">
@@ -3742,11 +4145,11 @@
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N9="NS","N",IF($AH9&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="P9" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2.4</v>
       </c>
       <c r="Q9" s="6">
@@ -3754,11 +4157,11 @@
       </c>
       <c r="R9" s="2"/>
       <c r="S9" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(R9="NS","N",IF($AI9&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="T9" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1.05</v>
       </c>
       <c r="U9" s="6">
@@ -3766,11 +4169,11 @@
       </c>
       <c r="V9" s="2"/>
       <c r="W9" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(V9="NS","N",IF($AH9&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="X9" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1.31</v>
       </c>
       <c r="Y9" s="6">
@@ -3778,45 +4181,82 @@
       </c>
       <c r="Z9" s="2"/>
       <c r="AA9" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(Z9="NS","N",IF($AJ9&gt;Parameters!$B$24,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="AB9" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0.71</v>
       </c>
       <c r="AC9" s="7">
         <v>6.9</v>
       </c>
       <c r="AD9" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+        <v>209</v>
+      </c>
+      <c r="AE9" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="AF9" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="AH9" s="14">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="AI9" s="14">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="AJ9" s="14">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="AK9" s="14">
+        <f t="shared" si="9"/>
+        <v>46175</v>
+      </c>
+      <c r="AL9" s="14">
+        <f t="shared" si="10"/>
+        <v>46181</v>
+      </c>
+      <c r="AM9" s="14">
+        <f t="shared" si="11"/>
+        <v>46181</v>
+      </c>
+      <c r="AN9" s="14">
+        <f t="shared" si="12"/>
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="E10" s="6">
         <v>0.005</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="G10" s="2" t="str">
+        <f>IF(F10="NS","N",IF($AH10&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>Y</v>
+      </c>
+      <c r="H10" s="6">
         <f t="shared" si="0"/>
-        <v>Y</v>
-      </c>
-      <c r="H10" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I10" s="6">
@@ -3824,35 +4264,35 @@
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(J10="NS","N",IF($AH10&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="L10" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.93</v>
       </c>
       <c r="M10" s="6">
-        <v>4.08</v>
+        <v>3.97</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N10="NS","N",IF($AH10&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="P10" s="6">
-        <f t="shared" si="5"/>
-        <v>4.08</v>
+        <f t="shared" si="2"/>
+        <v>3.97</v>
       </c>
       <c r="Q10" s="6">
         <v>0.83</v>
       </c>
       <c r="R10" s="2"/>
       <c r="S10" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(R10="NS","N",IF($AI10&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="T10" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0.83</v>
       </c>
       <c r="U10" s="6">
@@ -3860,11 +4300,11 @@
       </c>
       <c r="V10" s="2"/>
       <c r="W10" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(V10="NS","N",IF($AH10&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="X10" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>0.82</v>
       </c>
       <c r="Y10" s="6">
@@ -3872,45 +4312,82 @@
       </c>
       <c r="Z10" s="2"/>
       <c r="AA10" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(Z10="NS","N",IF($AJ10&gt;Parameters!$B$24,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="AB10" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0.44</v>
       </c>
       <c r="AC10" s="7">
         <v>7.8</v>
       </c>
       <c r="AD10" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+      <c r="AE10" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF10" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="AH10" s="14">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="AI10" s="14">
+        <f t="shared" si="7"/>
+        <v>27</v>
+      </c>
+      <c r="AJ10" s="14">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="AK10" s="14">
+        <f t="shared" si="9"/>
+        <v>46189</v>
+      </c>
+      <c r="AL10" s="14">
+        <f t="shared" si="10"/>
+        <v>46216</v>
+      </c>
+      <c r="AM10" s="14">
+        <f t="shared" si="11"/>
+        <v>46216</v>
+      </c>
+      <c r="AN10" s="14">
+        <f t="shared" si="12"/>
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E11" s="6">
         <v>0.005</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="G11" s="2" t="str">
+        <f>IF(F11="NS","N",IF($AH11&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>N</v>
+      </c>
+      <c r="H11" s="6">
         <f t="shared" si="0"/>
-        <v>Y</v>
-      </c>
-      <c r="H11" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I11" s="6">
@@ -3918,11 +4395,11 @@
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Y</v>
+        <f>IF(J11="NS","N",IF($AH11&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>N</v>
       </c>
       <c r="L11" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.87</v>
       </c>
       <c r="M11" s="6">
@@ -3930,11 +4407,11 @@
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Y</v>
+        <f>IF(N11="NS","N",IF($AH11&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>N</v>
       </c>
       <c r="P11" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1.77</v>
       </c>
       <c r="Q11" s="6">
@@ -3942,11 +4419,11 @@
       </c>
       <c r="R11" s="2"/>
       <c r="S11" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Y</v>
+        <f>IF(R11="NS","N",IF($AI11&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>N</v>
       </c>
       <c r="T11" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1.22</v>
       </c>
       <c r="U11" s="6">
@@ -3954,11 +4431,11 @@
       </c>
       <c r="V11" s="2"/>
       <c r="W11" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>Y</v>
+        <f>IF(V11="NS","N",IF($AH11&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>N</v>
       </c>
       <c r="X11" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1.06</v>
       </c>
       <c r="Y11" s="6">
@@ -3966,45 +4443,82 @@
       </c>
       <c r="Z11" s="2"/>
       <c r="AA11" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(Z11="NS","N",IF($AJ11&gt;Parameters!$B$24,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="AB11" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0.27</v>
       </c>
       <c r="AC11" s="7">
         <v>7.2</v>
       </c>
       <c r="AD11" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+        <v>220</v>
+      </c>
+      <c r="AE11" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="AF11" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="AH11" s="14">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+      <c r="AI11" s="14">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="AJ11" s="14">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="AK11" s="14">
+        <f t="shared" si="9"/>
+        <v>46210</v>
+      </c>
+      <c r="AL11" s="14">
+        <f t="shared" si="10"/>
+        <v>46240</v>
+      </c>
+      <c r="AM11" s="14">
+        <f t="shared" si="11"/>
+        <v>46240</v>
+      </c>
+      <c r="AN11" s="14">
+        <f t="shared" si="12"/>
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E12" s="6">
         <v>0.005</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="G12" s="2" t="str">
+        <f>IF(F12="NS","N",IF($AH12&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>Y</v>
+      </c>
+      <c r="H12" s="6">
         <f t="shared" si="0"/>
-        <v>Y</v>
-      </c>
-      <c r="H12" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I12" s="6">
@@ -4012,11 +4526,11 @@
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(J12="NS","N",IF($AH12&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="L12" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.21</v>
       </c>
       <c r="M12" s="6">
@@ -4024,11 +4538,11 @@
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N12="NS","N",IF($AH12&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="P12" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>4.09</v>
       </c>
       <c r="Q12" s="6">
@@ -4036,11 +4550,11 @@
       </c>
       <c r="R12" s="2"/>
       <c r="S12" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(R12="NS","N",IF($AI12&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="T12" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1.57</v>
       </c>
       <c r="U12" s="6">
@@ -4048,11 +4562,11 @@
       </c>
       <c r="V12" s="2"/>
       <c r="W12" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(V12="NS","N",IF($AH12&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="X12" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1.27</v>
       </c>
       <c r="Y12" s="6">
@@ -4060,43 +4574,80 @@
       </c>
       <c r="Z12" s="2"/>
       <c r="AA12" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(Z12="NS","N",IF($AJ12&gt;Parameters!$B$24,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="AB12" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0.35</v>
       </c>
       <c r="AC12" s="7">
         <v>8.4</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+        <v>223</v>
+      </c>
+      <c r="AE12" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="AF12" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="AH12" s="14">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="AI12" s="14">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="AJ12" s="14">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="AK12" s="14">
+        <f t="shared" si="9"/>
+        <v>46224</v>
+      </c>
+      <c r="AL12" s="14">
+        <f t="shared" si="10"/>
+        <v>46229</v>
+      </c>
+      <c r="AM12" s="14">
+        <f t="shared" si="11"/>
+        <v>46229</v>
+      </c>
+      <c r="AN12" s="14">
+        <f t="shared" si="12"/>
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E13" s="6">
         <v>0.014</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="str">
+        <f>IF(F13="NS","N",IF($AH13&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>Y</v>
+      </c>
+      <c r="H13" s="6">
         <f t="shared" si="0"/>
-        <v>Y</v>
-      </c>
-      <c r="H13" s="6">
-        <f t="shared" si="1"/>
         <v>0.014</v>
       </c>
       <c r="I13" s="6">
@@ -4104,11 +4655,11 @@
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(J13="NS","N",IF($AH13&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="L13" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.66</v>
       </c>
       <c r="M13" s="6">
@@ -4116,11 +4667,11 @@
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N13="NS","N",IF($AH13&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="P13" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>4.33</v>
       </c>
       <c r="Q13" s="6">
@@ -4128,11 +4679,11 @@
       </c>
       <c r="R13" s="2"/>
       <c r="S13" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(R13="NS","N",IF($AI13&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="T13" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2.61</v>
       </c>
       <c r="U13" s="6">
@@ -4140,11 +4691,11 @@
       </c>
       <c r="V13" s="2"/>
       <c r="W13" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(V13="NS","N",IF($AH13&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="X13" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>0.89</v>
       </c>
       <c r="Y13" s="6">
@@ -4152,45 +4703,82 @@
       </c>
       <c r="Z13" s="2"/>
       <c r="AA13" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(Z13="NS","N",IF($AJ13&gt;Parameters!$B$24,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="AB13" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0.19</v>
       </c>
       <c r="AC13" s="7">
         <v>6.8</v>
       </c>
       <c r="AD13" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+      <c r="AE13" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="AF13" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="AG13" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH13" s="14">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AI13" s="14">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="AJ13" s="14">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="AK13" s="14">
+        <f t="shared" si="9"/>
+        <v>46245</v>
+      </c>
+      <c r="AL13" s="14">
+        <f t="shared" si="10"/>
+        <v>46249</v>
+      </c>
+      <c r="AM13" s="14">
+        <f t="shared" si="11"/>
+        <v>46249</v>
+      </c>
+      <c r="AN13" s="14">
+        <f t="shared" si="12"/>
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E14" s="6">
         <v>0.005</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="G14" s="2" t="str">
+        <f>IF(F14="NS","N",IF($AH14&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>Y</v>
+      </c>
+      <c r="H14" s="6">
         <f t="shared" si="0"/>
-        <v>Y</v>
-      </c>
-      <c r="H14" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="6">
@@ -4198,11 +4786,11 @@
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(J14="NS","N",IF($AH14&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="L14" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.74</v>
       </c>
       <c r="M14" s="6">
@@ -4210,25 +4798,23 @@
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N14="NS","N",IF($AH14&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="P14" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>4.15</v>
       </c>
       <c r="Q14" s="6">
         <v>1.9</v>
       </c>
-      <c r="R14" s="2" t="s">
-        <v>199</v>
-      </c>
+      <c r="R14" s="2"/>
       <c r="S14" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(R14="NS","N",IF($AI14&gt;Parameters!$B$23,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="T14" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1.9</v>
       </c>
       <c r="U14" s="6">
@@ -4236,11 +4822,11 @@
       </c>
       <c r="V14" s="2"/>
       <c r="W14" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(V14="NS","N",IF($AH14&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="X14" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>1.18</v>
       </c>
       <c r="Y14" s="6">
@@ -4248,43 +4834,80 @@
       </c>
       <c r="Z14" s="2"/>
       <c r="AA14" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(Z14="NS","N",IF($AJ14&gt;Parameters!$B$24,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="AB14" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0.29</v>
       </c>
       <c r="AC14" s="7">
         <v>7.5</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+        <v>232</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="AF14" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="AH14" s="14">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="AI14" s="14">
+        <f t="shared" si="7"/>
+        <v>34</v>
+      </c>
+      <c r="AJ14" s="14">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="AK14" s="14">
+        <f t="shared" si="9"/>
+        <v>46259</v>
+      </c>
+      <c r="AL14" s="14">
+        <f t="shared" si="10"/>
+        <v>46263</v>
+      </c>
+      <c r="AM14" s="14">
+        <f t="shared" si="11"/>
+        <v>46293</v>
+      </c>
+      <c r="AN14" s="14">
+        <f t="shared" si="12"/>
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E15" s="6">
         <v>0.012</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="str">
+        <f>IF(F15="NS","N",IF($AH15&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>Y</v>
+      </c>
+      <c r="H15" s="6">
         <f t="shared" si="0"/>
-        <v>Y</v>
-      </c>
-      <c r="H15" s="6">
-        <f t="shared" si="1"/>
         <v>0.012</v>
       </c>
       <c r="I15" s="6">
@@ -4292,11 +4915,11 @@
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(J15="NS","N",IF($AH15&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="L15" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.02</v>
       </c>
       <c r="M15" s="6">
@@ -4304,11 +4927,11 @@
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N15="NS","N",IF($AH15&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="P15" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>2.96</v>
       </c>
       <c r="Q15" s="6">
@@ -4316,11 +4939,11 @@
       </c>
       <c r="R15" s="2"/>
       <c r="S15" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(R15="NS","N",IF($AI15&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="T15" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1.36</v>
       </c>
       <c r="U15" s="6">
@@ -4328,11 +4951,11 @@
       </c>
       <c r="V15" s="2"/>
       <c r="W15" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(V15="NS","N",IF($AH15&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="X15" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>3.14</v>
       </c>
       <c r="Y15" s="6">
@@ -4340,45 +4963,82 @@
       </c>
       <c r="Z15" s="2"/>
       <c r="AA15" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(Z15="NS","N",IF($AJ15&gt;Parameters!$B$24,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="AB15" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0.41</v>
       </c>
       <c r="AC15" s="7">
         <v>7.9</v>
       </c>
       <c r="AD15" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+        <v>238</v>
+      </c>
+      <c r="AE15" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="AF15" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="AG15" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="AH15" s="14">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AI15" s="14">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="AJ15" s="14">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+      <c r="AK15" s="14">
+        <f t="shared" si="9"/>
+        <v>46274</v>
+      </c>
+      <c r="AL15" s="14">
+        <f t="shared" si="10"/>
+        <v>46277</v>
+      </c>
+      <c r="AM15" s="14">
+        <f t="shared" si="11"/>
+        <v>46277</v>
+      </c>
+      <c r="AN15" s="14">
+        <f t="shared" si="12"/>
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E16" s="6">
         <v>0.005</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="G16" s="2" t="str">
+        <f>IF(F16="NS","N",IF($AH16&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>Y</v>
+      </c>
+      <c r="H16" s="6">
         <f t="shared" si="0"/>
-        <v>Y</v>
-      </c>
-      <c r="H16" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I16" s="6">
@@ -4386,11 +5046,11 @@
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(J16="NS","N",IF($AH16&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="L16" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.58</v>
       </c>
       <c r="M16" s="6">
@@ -4398,11 +5058,11 @@
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N16="NS","N",IF($AH16&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="P16" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1.68</v>
       </c>
       <c r="Q16" s="6">
@@ -4410,11 +5070,11 @@
       </c>
       <c r="R16" s="2"/>
       <c r="S16" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(R16="NS","N",IF($AI16&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="T16" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0.98</v>
       </c>
       <c r="U16" s="6">
@@ -4422,11 +5082,11 @@
       </c>
       <c r="V16" s="2"/>
       <c r="W16" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(V16="NS","N",IF($AH16&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="X16" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>0.94</v>
       </c>
       <c r="Y16" s="6">
@@ -4434,45 +5094,82 @@
       </c>
       <c r="Z16" s="2"/>
       <c r="AA16" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(Z16="NS","N",IF($AJ16&gt;Parameters!$B$24,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="AB16" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0.24</v>
       </c>
       <c r="AC16" s="7">
         <v>7.3</v>
       </c>
       <c r="AD16" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+      <c r="AE16" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="AF16" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="AG16" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="AH16" s="14">
+        <f t="shared" si="6"/>
+        <v>8</v>
+      </c>
+      <c r="AI16" s="14">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="AJ16" s="14">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="AK16" s="14">
+        <f t="shared" si="9"/>
+        <v>46287</v>
+      </c>
+      <c r="AL16" s="14">
+        <f t="shared" si="10"/>
+        <v>46295</v>
+      </c>
+      <c r="AM16" s="14">
+        <f t="shared" si="11"/>
+        <v>46295</v>
+      </c>
+      <c r="AN16" s="14">
+        <f t="shared" si="12"/>
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="17" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>207</v>
+        <v>244</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>208</v>
+        <v>245</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="E17" s="6">
         <v>0.005</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="G17" s="2" t="str">
+        <f>IF(F17="NS","N",IF($AH17&gt;Parameters!$B$23,"N","Y"))</f>
+        <v>Y</v>
+      </c>
+      <c r="H17" s="6">
         <f t="shared" si="0"/>
-        <v>Y</v>
-      </c>
-      <c r="H17" s="6">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I17" s="6">
@@ -4480,11 +5177,11 @@
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(J17="NS","N",IF($AH17&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="L17" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0.49</v>
       </c>
       <c r="M17" s="6">
@@ -4492,11 +5189,11 @@
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(N17="NS","N",IF($AH17&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="P17" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>1.52</v>
       </c>
       <c r="Q17" s="6">
@@ -4504,11 +5201,11 @@
       </c>
       <c r="R17" s="2"/>
       <c r="S17" s="2" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(R17="NS","N",IF($AI17&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="T17" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>1.11</v>
       </c>
       <c r="U17" s="6">
@@ -4516,29 +5213,64 @@
       </c>
       <c r="V17" s="2"/>
       <c r="W17" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(V17="NS","N",IF($AH17&gt;Parameters!$B$23,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="X17" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>0.88</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="AA17" s="2" t="str">
-        <f t="shared" si="10"/>
+        <f>IF(Z17="NS","N",IF($AJ17&gt;Parameters!$B$24,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="AB17" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC17" s="7">
         <v>7.4</v>
       </c>
       <c r="AD17" s="2" t="s">
-        <v>206</v>
+        <v>242</v>
+      </c>
+      <c r="AE17" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="AF17" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="AG17" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="AH17" s="14">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="AI17" s="14">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="AJ17" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="AK17" s="14">
+        <f t="shared" si="9"/>
+        <v>46288</v>
+      </c>
+      <c r="AL17" s="14">
+        <f>DATE(VALUE(RIGHT(AE17,4)),VALUE(LEFT(AE17,2)),VALUE(MID(AE17,4,2)))</f>
+        <v>46291</v>
+      </c>
+      <c r="AM17" s="14">
+        <f>DATE(VALUE(RIGHT(AF17,4)),VALUE(LEFT(AF17,2)),VALUE(MID(AF17,4,2)))</f>
+        <v>46291</v>
+      </c>
+      <c r="AN17" s="14" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -4559,28 +5291,28 @@
     <col min="9" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>212</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>8</v>
@@ -4589,24 +5321,24 @@
         <v>9</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>217</v>
+        <v>256</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
@@ -4650,7 +5382,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -4694,7 +5426,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>17</v>
@@ -4738,7 +5470,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>18</v>
@@ -4782,7 +5514,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>19</v>
@@ -4826,7 +5558,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>20</v>
@@ -4870,7 +5602,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
@@ -4914,7 +5646,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -4958,7 +5690,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>17</v>
@@ -5002,7 +5734,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>18</v>
@@ -5046,7 +5778,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>19</v>
@@ -5090,7 +5822,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>20</v>
@@ -5134,7 +5866,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
@@ -5178,7 +5910,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -5222,7 +5954,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>17</v>
@@ -5245,11 +5977,11 @@
       </c>
       <c r="G19" s="6">
         <f>ROUND(AVERAGEIFS('Lab Data'!$P$5:$P$17,'Lab Data'!$C$5:$C$17,"Jun",'Lab Data'!$O$5:$O$17,"Y"),3)</f>
-        <v>3.24</v>
+        <v>3.185</v>
       </c>
       <c r="H19" s="6">
         <f>_xlfn.MAXIFS('Lab Data'!$P$5:$P$17,'Lab Data'!$C$5:$C$17,"Jun",'Lab Data'!$O$5:$O$17,"Y")</f>
-        <v>4.08</v>
+        <v>3.97</v>
       </c>
       <c r="I19" s="2" t="str">
         <f t="shared" si="0"/>
@@ -5266,7 +5998,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>18</v>
@@ -5310,7 +6042,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>19</v>
@@ -5354,7 +6086,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>20</v>
@@ -5398,7 +6130,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -5413,7 +6145,7 @@
       </c>
       <c r="E23" s="2">
         <f>COUNTIFS('Lab Data'!$C$5:$C$17,"Jul",'Lab Data'!$G$5:$G$17,"Y")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2">
         <f>Parameters!$B$15</f>
@@ -5437,12 +6169,12 @@
       </c>
       <c r="K23" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>Met</v>
+        <v>Below frequency</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -5457,7 +6189,7 @@
       </c>
       <c r="E24" s="2">
         <f>COUNTIFS('Lab Data'!$C$5:$C$17,"Jul",'Lab Data'!$K$5:$K$17,"Y")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="2">
         <f>Parameters!$B$15</f>
@@ -5465,7 +6197,7 @@
       </c>
       <c r="G24" s="6">
         <f>ROUND(AVERAGEIFS('Lab Data'!$L$5:$L$17,'Lab Data'!$C$5:$C$17,"Jul",'Lab Data'!$K$5:$K$17,"Y"),3)</f>
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="H24" s="6">
         <f>_xlfn.MAXIFS('Lab Data'!$L$5:$L$17,'Lab Data'!$C$5:$C$17,"Jul",'Lab Data'!$K$5:$K$17,"Y")</f>
@@ -5481,12 +6213,12 @@
       </c>
       <c r="K24" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>Met</v>
+        <v>Below frequency</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>17</v>
@@ -5501,7 +6233,7 @@
       </c>
       <c r="E25" s="2">
         <f>COUNTIFS('Lab Data'!$C$5:$C$17,"Jul",'Lab Data'!$O$5:$O$17,"Y")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2">
         <f>Parameters!$B$15</f>
@@ -5509,7 +6241,7 @@
       </c>
       <c r="G25" s="6">
         <f>ROUND(AVERAGEIFS('Lab Data'!$P$5:$P$17,'Lab Data'!$C$5:$C$17,"Jul",'Lab Data'!$O$5:$O$17,"Y"),3)</f>
-        <v>2.93</v>
+        <v>4.09</v>
       </c>
       <c r="H25" s="6">
         <f>_xlfn.MAXIFS('Lab Data'!$P$5:$P$17,'Lab Data'!$C$5:$C$17,"Jul",'Lab Data'!$O$5:$O$17,"Y")</f>
@@ -5525,12 +6257,12 @@
       </c>
       <c r="K25" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>Met</v>
+        <v>Below frequency</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>18</v>
@@ -5545,7 +6277,7 @@
       </c>
       <c r="E26" s="2">
         <f>COUNTIFS('Lab Data'!$C$5:$C$17,"Jul",'Lab Data'!$S$5:$S$17,"Y")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2">
         <f>Parameters!$B$15</f>
@@ -5553,7 +6285,7 @@
       </c>
       <c r="G26" s="6">
         <f>ROUND(AVERAGEIFS('Lab Data'!$T$5:$T$17,'Lab Data'!$C$5:$C$17,"Jul",'Lab Data'!$S$5:$S$17,"Y"),3)</f>
-        <v>1.395</v>
+        <v>1.57</v>
       </c>
       <c r="H26" s="6">
         <f>_xlfn.MAXIFS('Lab Data'!$T$5:$T$17,'Lab Data'!$C$5:$C$17,"Jul",'Lab Data'!$S$5:$S$17,"Y")</f>
@@ -5569,12 +6301,12 @@
       </c>
       <c r="K26" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>Met</v>
+        <v>Below frequency</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>19</v>
@@ -5589,7 +6321,7 @@
       </c>
       <c r="E27" s="2">
         <f>COUNTIFS('Lab Data'!$C$5:$C$17,"Jul",'Lab Data'!$W$5:$W$17,"Y")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" s="2">
         <f>Parameters!$B$15</f>
@@ -5597,7 +6329,7 @@
       </c>
       <c r="G27" s="6">
         <f>ROUND(AVERAGEIFS('Lab Data'!$X$5:$X$17,'Lab Data'!$C$5:$C$17,"Jul",'Lab Data'!$W$5:$W$17,"Y"),3)</f>
-        <v>1.165</v>
+        <v>1.27</v>
       </c>
       <c r="H27" s="6">
         <f>_xlfn.MAXIFS('Lab Data'!$X$5:$X$17,'Lab Data'!$C$5:$C$17,"Jul",'Lab Data'!$W$5:$W$17,"Y")</f>
@@ -5613,12 +6345,12 @@
       </c>
       <c r="K27" s="2" t="str">
         <f t="shared" si="2"/>
-        <v>Met</v>
+        <v>Below frequency</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>20</v>
@@ -5662,7 +6394,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -5706,7 +6438,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -5750,7 +6482,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>17</v>
@@ -5794,7 +6526,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>18</v>
@@ -5838,7 +6570,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>19</v>
@@ -5882,7 +6614,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>20</v>
@@ -5926,7 +6658,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -5970,7 +6702,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -6014,7 +6746,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>17</v>
@@ -6058,7 +6790,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>18</v>
@@ -6102,7 +6834,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>19</v>
@@ -6146,7 +6878,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>20</v>
@@ -6195,7 +6927,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -6212,14 +6944,14 @@
     <col min="13" max="14" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>221</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -6227,43 +6959,43 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>222</v>
+        <v>261</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>223</v>
+        <v>262</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>224</v>
+        <v>263</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>225</v>
+        <v>264</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>231</v>
+        <v>270</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>232</v>
+        <v>271</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>233</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -6272,7 +7004,7 @@
       </c>
       <c r="B5" s="2">
         <f>COUNTIFS('Lab Data'!$G$5:$G$17,"Y")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="5">
         <f>Parameters!$B$4</f>
@@ -6329,7 +7061,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIFS('Lab Data'!$K$5:$K$17,"Y")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="5">
         <f>Parameters!$B$5</f>
@@ -6386,7 +7118,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIFS('Lab Data'!$O$5:$O$17,"Y")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="5">
         <f>Parameters!$B$6</f>
@@ -6406,15 +7138,15 @@
       </c>
       <c r="G7" s="7">
         <f t="shared" si="1"/>
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="H7" s="2">
         <f>COUNTIFS('Lab Data'!$P$5:$P$17,"&gt;"&amp;E7,'Lab Data'!$O$5:$O$17,"Y")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" si="2"/>
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="J7" s="2" t="str">
         <f>IF(G7&gt;=Parameters!$B$17,"Yes","No")</f>
@@ -6443,7 +7175,7 @@
       </c>
       <c r="B8" s="2">
         <f>COUNTIFS('Lab Data'!$S$5:$S$17,"Y")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="5">
         <f>Parameters!$B$7</f>
@@ -6500,7 +7232,7 @@
       </c>
       <c r="B9" s="2">
         <f>COUNTIFS('Lab Data'!$W$5:$W$17,"Y")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="5">
         <f>Parameters!$B$8</f>
@@ -6520,7 +7252,7 @@
       </c>
       <c r="G9" s="7">
         <f t="shared" si="1"/>
-        <v>7.7</v>
+        <v>8.3</v>
       </c>
       <c r="H9" s="2">
         <f>COUNTIFS('Lab Data'!$X$5:$X$17,"&gt;"&amp;E9,'Lab Data'!$W$5:$W$17,"Y")</f>
@@ -6528,7 +7260,7 @@
       </c>
       <c r="I9" s="7">
         <f t="shared" si="2"/>
-        <v>7.7</v>
+        <v>8.3</v>
       </c>
       <c r="J9" s="2" t="str">
         <f>IF(G9&gt;=Parameters!$B$17,"Yes","No")</f>
@@ -6610,7 +7342,40 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>234</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -6620,414 +7385,565 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>236</v>
+        <v>285</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>286</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B4" s="8">
+        <v>6418255</v>
+      </c>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="8">
+        <v>6450959</v>
+      </c>
+      <c r="C5" s="8">
+        <f t="shared" ref="C5:C34" si="0">B5-B4</f>
+        <v>32704</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <f>IF(C5&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B6" s="8">
+        <v>6491552</v>
+      </c>
+      <c r="C6" s="8">
+        <f t="shared" si="0"/>
+        <v>40593</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <f>IF(C6&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B7" s="8">
+        <v>6523848</v>
+      </c>
+      <c r="C7" s="8">
+        <f t="shared" si="0"/>
+        <v>32296</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <f>IF(C7&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B8" s="8">
+        <v>6561503</v>
+      </c>
+      <c r="C8" s="8">
+        <f t="shared" si="0"/>
+        <v>37655</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <f>IF(C8&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="8">
+        <v>6565112</v>
+      </c>
+      <c r="C9" s="8">
+        <f t="shared" si="0"/>
+        <v>3609</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <f>IF(C9&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B10" s="8">
+        <v>6567087</v>
+      </c>
+      <c r="C10" s="8">
+        <f t="shared" si="0"/>
+        <v>1975</v>
+      </c>
+      <c r="D10" s="2" t="str">
+        <f>IF(C10&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B11" s="8">
+        <v>6567087</v>
+      </c>
+      <c r="C11" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="str">
+        <f>IF(C11&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B12" s="8">
+        <v>6601769</v>
+      </c>
+      <c r="C12" s="8">
+        <f t="shared" si="0"/>
+        <v>34682</v>
+      </c>
+      <c r="D12" s="2" t="str">
+        <f>IF(C12&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="8">
+        <v>6649069</v>
+      </c>
+      <c r="C13" s="8">
+        <f t="shared" si="0"/>
+        <v>47300</v>
+      </c>
+      <c r="D13" s="2" t="str">
+        <f>IF(C13&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="8">
+        <v>6680799</v>
+      </c>
+      <c r="C14" s="8">
+        <f t="shared" si="0"/>
+        <v>31730</v>
+      </c>
+      <c r="D14" s="2" t="str">
+        <f>IF(C14&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B15" s="8">
+        <v>6709642</v>
+      </c>
+      <c r="C15" s="8">
+        <f t="shared" si="0"/>
+        <v>28843</v>
+      </c>
+      <c r="D15" s="2" t="str">
+        <f>IF(C15&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B16" s="8">
+        <v>6712444</v>
+      </c>
+      <c r="C16" s="8">
+        <f t="shared" si="0"/>
+        <v>2802</v>
+      </c>
+      <c r="D16" s="2" t="str">
+        <f>IF(C16&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B17" s="8">
+        <v>6716224</v>
+      </c>
+      <c r="C17" s="8">
+        <f t="shared" si="0"/>
+        <v>3780</v>
+      </c>
+      <c r="D17" s="2" t="str">
+        <f>IF(C17&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B18" s="8">
+        <v>6753533</v>
+      </c>
+      <c r="C18" s="8">
+        <f t="shared" si="0"/>
+        <v>37309</v>
+      </c>
+      <c r="D18" s="2" t="str">
+        <f>IF(C18&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B4" s="8">
-        <v>32704</v>
-      </c>
-      <c r="C4" s="2" t="str">
-        <f>IF(B4&gt;Parameters!$B$12,"Yes","No")</f>
+      <c r="B19" s="8">
+        <v>6788370</v>
+      </c>
+      <c r="C19" s="8">
+        <f t="shared" si="0"/>
+        <v>34837</v>
+      </c>
+      <c r="D19" s="2" t="str">
+        <f>IF(C19&gt;Parameters!$B$12,"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B5" s="8">
-        <v>40593</v>
-      </c>
-      <c r="C5" s="2" t="str">
-        <f>IF(B5&gt;Parameters!$B$12,"Yes","No")</f>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B20" s="8">
+        <v>6828334</v>
+      </c>
+      <c r="C20" s="8">
+        <f t="shared" si="0"/>
+        <v>39964</v>
+      </c>
+      <c r="D20" s="2" t="str">
+        <f>IF(C20&gt;Parameters!$B$12,"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="8">
+        <v>6856644</v>
+      </c>
+      <c r="C21" s="8">
+        <f t="shared" si="0"/>
+        <v>28310</v>
+      </c>
+      <c r="D21" s="2" t="str">
+        <f>IF(C21&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B22" s="8">
+        <v>6890079</v>
+      </c>
+      <c r="C22" s="8">
+        <f t="shared" si="0"/>
+        <v>33435</v>
+      </c>
+      <c r="D22" s="2" t="str">
+        <f>IF(C22&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B23" s="8">
+        <v>6894233</v>
+      </c>
+      <c r="C23" s="8">
+        <f t="shared" si="0"/>
+        <v>4154</v>
+      </c>
+      <c r="D23" s="2" t="str">
+        <f>IF(C23&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B24" s="8">
+        <v>6898105</v>
+      </c>
+      <c r="C24" s="8">
+        <f t="shared" si="0"/>
+        <v>3872</v>
+      </c>
+      <c r="D24" s="2" t="str">
+        <f>IF(C24&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B25" s="8">
+        <v>6938636</v>
+      </c>
+      <c r="C25" s="8">
+        <f t="shared" si="0"/>
+        <v>40531</v>
+      </c>
+      <c r="D25" s="2" t="str">
+        <f>IF(C25&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B6" s="8">
-        <v>32296</v>
-      </c>
-      <c r="C6" s="2" t="str">
-        <f>IF(B6&gt;Parameters!$B$12,"Yes","No")</f>
+      <c r="B26" s="8">
+        <v>6972764</v>
+      </c>
+      <c r="C26" s="8">
+        <f t="shared" si="0"/>
+        <v>34128</v>
+      </c>
+      <c r="D26" s="2" t="str">
+        <f>IF(C26&gt;Parameters!$B$12,"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="8">
-        <v>37655</v>
-      </c>
-      <c r="C7" s="2" t="str">
-        <f>IF(B7&gt;Parameters!$B$12,"Yes","No")</f>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B27" s="8">
+        <v>7000793</v>
+      </c>
+      <c r="C27" s="8">
+        <f t="shared" si="0"/>
+        <v>28029</v>
+      </c>
+      <c r="D27" s="2" t="str">
+        <f>IF(C27&gt;Parameters!$B$12,"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8" s="8">
-        <v>3609</v>
-      </c>
-      <c r="C8" s="2" t="str">
-        <f>IF(B8&gt;Parameters!$B$12,"Yes","No")</f>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B28" s="8">
+        <v>7028709</v>
+      </c>
+      <c r="C28" s="8">
+        <f t="shared" si="0"/>
+        <v>27916</v>
+      </c>
+      <c r="D28" s="2" t="str">
+        <f>IF(C28&gt;Parameters!$B$12,"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B9" s="8">
-        <v>1975</v>
-      </c>
-      <c r="C9" s="2" t="str">
-        <f>IF(B9&gt;Parameters!$B$12,"Yes","No")</f>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B29" s="8">
+        <v>7067653</v>
+      </c>
+      <c r="C29" s="8">
+        <f t="shared" si="0"/>
+        <v>38944</v>
+      </c>
+      <c r="D29" s="2" t="str">
+        <f>IF(C29&gt;Parameters!$B$12,"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B10" s="8">
-        <v>0</v>
-      </c>
-      <c r="C10" s="2" t="str">
-        <f>IF(B10&gt;Parameters!$B$12,"Yes","No")</f>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B30" s="8">
+        <v>7071331</v>
+      </c>
+      <c r="C30" s="8">
+        <f t="shared" si="0"/>
+        <v>3678</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f>IF(C30&gt;Parameters!$B$12,"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B31" s="8">
+        <v>7074075</v>
+      </c>
+      <c r="C31" s="8">
+        <f t="shared" si="0"/>
+        <v>2744</v>
+      </c>
+      <c r="D31" s="2" t="str">
+        <f>IF(C31&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B32" s="8">
+        <v>7108801</v>
+      </c>
+      <c r="C32" s="8">
+        <f t="shared" si="0"/>
+        <v>34726</v>
+      </c>
+      <c r="D32" s="2" t="str">
+        <f>IF(C32&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B33" s="8">
+        <v>7139484</v>
+      </c>
+      <c r="C33" s="8">
+        <f t="shared" si="0"/>
+        <v>30683</v>
+      </c>
+      <c r="D33" s="2" t="str">
+        <f>IF(C33&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B11" s="8">
-        <v>34682</v>
-      </c>
-      <c r="C11" s="2" t="str">
-        <f>IF(B11&gt;Parameters!$B$12,"Yes","No")</f>
+      <c r="B34" s="8">
+        <v>7173975</v>
+      </c>
+      <c r="C34" s="8">
+        <f t="shared" si="0"/>
+        <v>34491</v>
+      </c>
+      <c r="D34" s="2" t="str">
+        <f>IF(C34&gt;Parameters!$B$12,"Yes","No")</f>
         <v>No</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="8">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="B36" s="15">
+        <f>MAX(C5:C34)</f>
         <v>47300</v>
       </c>
-      <c r="C12" s="2" t="str">
-        <f>IF(B12&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="8">
-        <v>31730</v>
-      </c>
-      <c r="C13" s="2" t="str">
-        <f>IF(B13&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B14" s="8">
-        <v>28843</v>
-      </c>
-      <c r="C14" s="2" t="str">
-        <f>IF(B14&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="B15" s="8">
-        <v>2802</v>
-      </c>
-      <c r="C15" s="2" t="str">
-        <f>IF(B15&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B16" s="8">
-        <v>3780</v>
-      </c>
-      <c r="C16" s="2" t="str">
-        <f>IF(B16&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B17" s="8">
-        <v>37309</v>
-      </c>
-      <c r="C17" s="2" t="str">
-        <f>IF(B17&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B18" s="8">
-        <v>34837</v>
-      </c>
-      <c r="C18" s="2" t="str">
-        <f>IF(B18&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B19" s="8">
-        <v>39964</v>
-      </c>
-      <c r="C19" s="2" t="str">
-        <f>IF(B19&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" s="8">
-        <v>28310</v>
-      </c>
-      <c r="C20" s="2" t="str">
-        <f>IF(B20&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B21" s="8">
-        <v>33435</v>
-      </c>
-      <c r="C21" s="2" t="str">
-        <f>IF(B21&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B22" s="8">
-        <v>4154</v>
-      </c>
-      <c r="C22" s="2" t="str">
-        <f>IF(B22&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B23" s="8">
-        <v>3872</v>
-      </c>
-      <c r="C23" s="2" t="str">
-        <f>IF(B23&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B24" s="8">
-        <v>40531</v>
-      </c>
-      <c r="C24" s="2" t="str">
-        <f>IF(B24&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B25" s="8">
-        <v>34128</v>
-      </c>
-      <c r="C25" s="2" t="str">
-        <f>IF(B25&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B26" s="8">
-        <v>28029</v>
-      </c>
-      <c r="C26" s="2" t="str">
-        <f>IF(B26&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B27" s="8">
-        <v>27916</v>
-      </c>
-      <c r="C27" s="2" t="str">
-        <f>IF(B27&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B28" s="8">
-        <v>38944</v>
-      </c>
-      <c r="C28" s="2" t="str">
-        <f>IF(B28&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="B29" s="8">
-        <v>3678</v>
-      </c>
-      <c r="C29" s="2" t="str">
-        <f>IF(B29&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B30" s="8">
-        <v>2744</v>
-      </c>
-      <c r="C30" s="2" t="str">
-        <f>IF(B30&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="B31" s="8">
-        <v>34726</v>
-      </c>
-      <c r="C31" s="2" t="str">
-        <f>IF(B31&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="B32" s="8">
-        <v>30683</v>
-      </c>
-      <c r="C32" s="2" t="str">
-        <f>IF(B32&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B33" s="8">
-        <v>34491</v>
-      </c>
-      <c r="C33" s="2" t="str">
-        <f>IF(B33&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="B34" s="15">
-        <f>MAX(B4:B33)</f>
-        <v>47300</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="B35" s="2">
-        <f>COUNTIF(C4:C33,"Yes")</f>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="B37" s="16">
+        <f>COUNTIF(D5:D34,"Yes")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B36" s="8">
-        <f>SUM(B4:B33)</f>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="B38" s="15">
+        <f>B34-B4</f>
+        <v>755720</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="B39" s="15">
+        <f>SUM(C5:C34)</f>
         <v>755720</v>
       </c>
     </row>
@@ -7038,7 +7954,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -7050,216 +7966,285 @@
     <col min="7" max="7" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>263</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>264</v>
+        <v>312</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>265</v>
+        <v>313</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>266</v>
+        <v>314</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>268</v>
+        <v>315</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>270</v>
+        <v>317</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>271</v>
+        <v>318</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>273</v>
+        <v>320</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>274</v>
+        <v>321</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>275</v>
+        <v>322</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>277</v>
+        <v>324</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>278</v>
+        <v>325</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>279</v>
+        <v>326</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>280</v>
+        <v>86</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>281</v>
+        <v>327</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>283</v>
+        <v>328</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>284</v>
+        <v>329</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>285</v>
+        <v>330</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>280</v>
+        <v>86</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>286</v>
+        <v>88</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>290</v>
+        <v>331</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>280</v>
+        <v>332</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>291</v>
+        <v>333</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>250</v>
+        <v>335</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>292</v>
+        <v>336</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>280</v>
+        <v>332</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>294</v>
+        <v>338</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>287</v>
+        <v>339</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>295</v>
+        <v>233</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>296</v>
+        <v>340</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>299</v>
+        <v>339</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>300</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>301</v>
+        <v>343</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>304</v>
+        <v>332</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>305</v>
+        <v>345</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>283</v>
+        <v>346</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>307</v>
+        <v>347</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>308</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -7269,7 +8254,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
@@ -7277,57 +8262,62 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>309</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>310</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
-        <v>311</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>316</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
+        <v>376</v>
       </c>
     </row>
   </sheetData>

--- a/submissions/03-pretreatment-smr-q3-2026/solution/vandeveer_smr_q3_2026.xlsx
+++ b/submissions/03-pretreatment-smr-q3-2026/solution/vandeveer_smr_q3_2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7102B0D2-22D9-AF4A-A743-BA70419E34A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2CAD89-09F3-8742-B2B8-72FF6B3BF629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SMR Q3" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Lab Data" sheetId="3" r:id="rId3"/>
     <sheet name="Monthly Stats" sheetId="4" r:id="rId4"/>
     <sheet name="SNC Review" sheetId="5" r:id="rId5"/>
-    <sheet name="Flow Sep" sheetId="6" r:id="rId6"/>
+    <sheet name="Flow Q3" sheetId="6" r:id="rId6"/>
     <sheet name="Notifications" sheetId="7" r:id="rId7"/>
     <sheet name="Note to Gordon" sheetId="8" r:id="rId8"/>
   </sheets>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="432">
   <si>
     <t>SELF-MONITORING REPORT, THIRD QUARTER 2026 (JULY 1 THROUGH SEPTEMBER 30, 2026)</t>
   </si>
@@ -109,7 +109,7 @@
     <t>not applicable</t>
   </si>
   <si>
-    <t>In-line meter: none reported</t>
+    <t>In-line meter: no excursion; the 9.0 high of 07/22/2026 is inside the range</t>
   </si>
   <si>
     <t>Met</t>
@@ -121,21 +121,21 @@
     <t>daily</t>
   </si>
   <si>
-    <t>no day above the limit per the plant manager's review of the operator logs</t>
-  </si>
-  <si>
     <t>AUGUST 2026</t>
   </si>
   <si>
+    <t>In-line meter: one excursion, 08/20/2026, high reading 9.2</t>
+  </si>
+  <si>
+    <t>Exceeded</t>
+  </si>
+  <si>
     <t>SEPTEMBER 2026</t>
   </si>
   <si>
     <t>In-line meter: one excursion, 09/17/2026; the 6.0 low of 09/11/2026 is inside the range</t>
   </si>
   <si>
-    <t>Exceeded</t>
-  </si>
-  <si>
     <t>VIOLATIONS IN THE QUARTER</t>
   </si>
   <si>
@@ -235,6 +235,33 @@
     <t>Nickel of sample VP-260825 analyzed 09/28/2026, outside the 28-day holding period; no replacement before month end</t>
   </si>
   <si>
+    <t>08/13/2026</t>
+  </si>
+  <si>
+    <t>Flow, daily, worked from the totalizer register</t>
+  </si>
+  <si>
+    <t>45,000 gallons per day</t>
+  </si>
+  <si>
+    <t>Zinc line on two shifts with overtime per the log; the plant manager's note read the month as inside the limit</t>
+  </si>
+  <si>
+    <t>08/20/2026</t>
+  </si>
+  <si>
+    <t>pH, in-line meter, high reading for the day</t>
+  </si>
+  <si>
+    <t>9.2</t>
+  </si>
+  <si>
+    <t>Section 2.4 and Section 4.2</t>
+  </si>
+  <si>
+    <t>Caustic feed valve serviced at 11:00 per the log; the duration is on the chart in the binder and not in the log</t>
+  </si>
+  <si>
     <t>09/09/2026</t>
   </si>
   <si>
@@ -259,12 +286,6 @@
     <t>The 09/09/2026 result carries the month</t>
   </si>
   <si>
-    <t>Flow, daily, worked from the totalizer register</t>
-  </si>
-  <si>
-    <t>45,000 gallons per day</t>
-  </si>
-  <si>
     <t>Rinse tank RT-4 overflow, about 2,900 gallons to the sewer around treatment</t>
   </si>
   <si>
@@ -310,9 +331,6 @@
     <t>5.8</t>
   </si>
   <si>
-    <t>Section 2.4 and Section 4.2</t>
-  </si>
-  <si>
     <t>Acid dump from the pickle tank; caustic feed increased, pH 6.9 by 15:00; called in at 15:20 and reported in writing 09/21/2026</t>
   </si>
   <si>
@@ -721,9 +739,6 @@
     <t>Aug</t>
   </si>
   <si>
-    <t>08/20/2026</t>
-  </si>
-  <si>
     <t>08/15/2026</t>
   </si>
   <si>
@@ -886,10 +901,10 @@
     <t>The received date is the Pretreatment Coordinator's, from her note of September 30, 2026.</t>
   </si>
   <si>
-    <t>Daily flow, September 2026, gallons, worked from the totalizer register readings in the operator log</t>
-  </si>
-  <si>
-    <t>The log carries the register at 07:00 the following morning; a day's flow is that reading less the one before it. The month's total is the end register less the start register.</t>
+    <t>Daily flow, July through September 2026, gallons, worked from the totalizer register readings in the operator logs</t>
+  </si>
+  <si>
+    <t>Each log carries the register at 07:00 the following morning; a day's flow is that reading less the one before it. The quarter's total is the end register less the start register.</t>
   </si>
   <si>
     <t>REGISTER AT 07:00 NEXT DAY, GAL</t>
@@ -901,7 +916,133 @@
     <t>ABOVE LIMIT</t>
   </si>
   <si>
-    <t>Register at 07:00 on 09/01/2026</t>
+    <t>Register at 07:00 on 07/01/2026</t>
+  </si>
+  <si>
+    <t>07/01/2026</t>
+  </si>
+  <si>
+    <t>07/02/2026</t>
+  </si>
+  <si>
+    <t>07/03/2026</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>07/05/2026</t>
+  </si>
+  <si>
+    <t>07/06/2026</t>
+  </si>
+  <si>
+    <t>07/08/2026</t>
+  </si>
+  <si>
+    <t>07/09/2026</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
+    <t>07/11/2026</t>
+  </si>
+  <si>
+    <t>07/12/2026</t>
+  </si>
+  <si>
+    <t>07/16/2026</t>
+  </si>
+  <si>
+    <t>07/17/2026</t>
+  </si>
+  <si>
+    <t>07/18/2026</t>
+  </si>
+  <si>
+    <t>07/19/2026</t>
+  </si>
+  <si>
+    <t>07/20/2026</t>
+  </si>
+  <si>
+    <t>07/22/2026</t>
+  </si>
+  <si>
+    <t>07/23/2026</t>
+  </si>
+  <si>
+    <t>07/24/2026</t>
+  </si>
+  <si>
+    <t>07/27/2026</t>
+  </si>
+  <si>
+    <t>07/28/2026</t>
+  </si>
+  <si>
+    <t>07/29/2026</t>
+  </si>
+  <si>
+    <t>08/01/2026</t>
+  </si>
+  <si>
+    <t>08/02/2026</t>
+  </si>
+  <si>
+    <t>08/03/2026</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>08/05/2026</t>
+  </si>
+  <si>
+    <t>08/08/2026</t>
+  </si>
+  <si>
+    <t>08/09/2026</t>
+  </si>
+  <si>
+    <t>08/10/2026</t>
+  </si>
+  <si>
+    <t>08/12/2026</t>
+  </si>
+  <si>
+    <t>08/16/2026</t>
+  </si>
+  <si>
+    <t>08/17/2026</t>
+  </si>
+  <si>
+    <t>08/18/2026</t>
+  </si>
+  <si>
+    <t>08/19/2026</t>
+  </si>
+  <si>
+    <t>08/22/2026</t>
+  </si>
+  <si>
+    <t>08/23/2026</t>
+  </si>
+  <si>
+    <t>08/24/2026</t>
+  </si>
+  <si>
+    <t>08/26/2026</t>
+  </si>
+  <si>
+    <t>08/28/2026</t>
+  </si>
+  <si>
+    <t>08/30/2026</t>
+  </si>
+  <si>
+    <t>08/31/2026</t>
   </si>
   <si>
     <t>09/01/2026</t>
@@ -958,13 +1099,16 @@
     <t>09/29/2026</t>
   </si>
   <si>
-    <t>Highest daily flow in September</t>
-  </si>
-  <si>
-    <t>Days above the daily flow limit</t>
-  </si>
-  <si>
-    <t>Total for the month, the end register less the start register</t>
+    <t>HIGHEST DAILY FLOW, GAL</t>
+  </si>
+  <si>
+    <t>DAYS ABOVE THE LIMIT</t>
+  </si>
+  <si>
+    <t>TOTAL, GAL</t>
+  </si>
+  <si>
+    <t>Quarter total, the end register less the start register</t>
   </si>
   <si>
     <t>Sum of the daily flows, which ties to the register total</t>
@@ -1099,6 +1243,24 @@
     <t>Not made</t>
   </si>
   <si>
+    <t>Daily flow of 08/13/2026 above the limit, which Part I writes as a daily maximum</t>
+  </si>
+  <si>
+    <t>08/14/2026 07:00 (register read)</t>
+  </si>
+  <si>
+    <t>Telephone notice within 24 hours, where the City reads the flow limit as a daily maximum limitation</t>
+  </si>
+  <si>
+    <t>08/15/2026 07:00</t>
+  </si>
+  <si>
+    <t>None in the City's telephone log</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
     <t>Second quarter self-monitoring report</t>
   </si>
   <si>
@@ -1154,6 +1316,9 @@
   </si>
   <si>
     <t>The pH reading of 5.8 on the in-line meter on September 17, from 14:10 to 14:55 during the pickle tank acid dump, is a violation under Section 2.4 and Section 4.2 even though every grab at sampling was inside the range, and it is listed with its duration and cause. Luis's call to Renee at 15:20 the same afternoon and the written report of September 21 meet Section 3.2 on that event. The meter's low of 6.0 on the morning of September 11 is inside the range and is not a violation.</t>
+  </si>
+  <si>
+    <t>Your note says no day in July or August ran above the flow limit and that the in-line pH stayed inside the range both months. Luis's logs say otherwise on two counts. The register difference for August 13 is 46,150 gallons, above the 45,000 gallon daily limit, and the meter chart for August 20 reached 9.2 while the caustic feed valve was being serviced, above the 9.0 top of the range. Both are reported as violations. July is clean: its highest day is 44,880 gallons, and its highest meter reading is 9.0, both inside the limits. Whether the August 13 flow needed a telephone notice under Section 3.2 is left open in the notifications tab, since Part I writes the flow limit as a daily maximum and no call is in Renee's log.</t>
   </si>
   <si>
     <t>Nickel has a reporting problem in August. The August 25 nickel result is not valid under Section 2.3, so the August nickel average rests on the August 11 result alone, 2.61 mg/L against the 2.38 mg/L monthly limit, and August is reported as monitored below the required frequency for nickel, since no replacement sample was collected before the month ended. Not-detected results are carried at zero in the averages, as Section 2.2 directs, which is why the September cadmium average reads 0.004 mg/L rather than the detection limit.</t>
@@ -1569,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -1938,14 +2103,16 @@
       <c r="E15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>28</v>
+      <c r="G15" s="8">
+        <f>'Flow Q3'!$B$99</f>
+        <v>44880</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>25</v>
+      <c r="I15" s="2" t="str">
+        <f>IF(G15&gt;B15,"Exceeded","Met")</f>
+        <v>Met</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>25</v>
@@ -1953,7 +2120,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -2261,10 +2428,10 @@
         <v>7.5</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>25</v>
@@ -2287,14 +2454,16 @@
       <c r="E26" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>28</v>
+      <c r="G26" s="8">
+        <f>'Flow Q3'!$B$100</f>
+        <v>46150</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>25</v>
+      <c r="I26" s="2" t="str">
+        <f>IF(G26&gt;B26,"Exceeded","Met")</f>
+        <v>Exceeded</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>25</v>
@@ -2302,7 +2471,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -2610,10 +2779,10 @@
         <v>7.9</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>25</v>
@@ -2637,7 +2806,7 @@
         <v>27</v>
       </c>
       <c r="G37" s="8">
-        <f>'Flow Sep'!$B$36</f>
+        <f>'Flow Q3'!$B$101</f>
         <v>47300</v>
       </c>
       <c r="H37" s="2" t="s">
@@ -2844,167 +3013,168 @@
         <v>65</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
         <v>66</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="10">
+      <c r="C49" s="12">
+        <f>'Flow Q3'!$B$100</f>
+        <v>46150</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C51" s="10">
         <f>'Monthly Stats'!H39</f>
         <v>3.14</v>
       </c>
-      <c r="D49" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E49" s="9" t="s">
+      <c r="D51" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C50" s="10">
+      <c r="F51" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C52" s="10">
         <f>'Monthly Stats'!G39</f>
         <v>1.653</v>
       </c>
-      <c r="D50" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E50" s="9" t="s">
+      <c r="D52" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E52" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F50" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="70" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" s="12">
-        <f>'Flow Sep'!$B$36</f>
-        <v>47300</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="F52" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="70" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B53" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C53" s="12">
+        <f>'Flow Q3'!$B$101</f>
+        <v>47300</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C53" s="9" t="s">
+    </row>
+    <row r="54" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="C54" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="D54" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="E54" s="9" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="9" t="s">
+      <c r="F54" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B54" s="9" t="s">
+    </row>
+    <row r="55" spans="1:6" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="B55" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D54" s="9" t="s">
+      <c r="C55" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D56" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E54" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="98" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="98" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B56" s="9" t="s">
+      <c r="E56" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F56" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="98" customHeight="1" x14ac:dyDescent="0.2">
@@ -3015,108 +3185,148 @@
         <v>100</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="3"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C58" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="B59" s="2"/>
+      <c r="D58" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B60" s="2">
+      <c r="A60" s="3"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B61" s="2"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B62" s="2">
         <f>'SNC Review'!B7</f>
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B61" s="2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B63" s="2">
         <f>'SNC Review'!H7</f>
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B62" s="7">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B64" s="7">
         <f>'SNC Review'!I7</f>
         <v>33.3</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B63" s="2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B65" s="2">
         <f>Parameters!$B$18</f>
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B64" s="13" t="str">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B66" s="13" t="str">
         <f>'SNC Review'!L7</f>
         <v>Significant noncompliance</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" s="3"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="3"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3138,7 +3348,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -3152,10 +3362,10 @@
         <v>10</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -3172,7 +3382,7 @@
         <v>0.005</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -3189,7 +3399,7 @@
         <v>0.01</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -3206,7 +3416,7 @@
         <v>0.01</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -3223,7 +3433,7 @@
         <v>0.02</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -3240,7 +3450,7 @@
         <v>0.02</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -3257,12 +3467,12 @@
         <v>0.005</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>36</v>
@@ -3270,150 +3480,150 @@
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B12" s="8">
         <v>45000</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B13" s="7">
         <v>6</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="B14" s="7">
         <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B15" s="14">
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B16" s="7">
         <v>1.2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B17" s="14">
         <v>66</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B18" s="14">
         <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B19" s="14">
         <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B20" s="14">
         <v>5</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B21" s="14">
         <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B22" s="14">
         <v>15</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B23" s="14">
         <v>28</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B24" s="14">
         <v>14</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3449,154 +3659,154 @@
   <sheetData>
     <row r="1" spans="1:40" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AA4" s="4" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AB4" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AC4" s="4" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AD4" s="4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="AE4" s="4" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="AF4" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AG4" s="4" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="AH4" s="4" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="AI4" s="4" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AJ4" s="4" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="AK4" s="4" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="AL4" s="4" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="AM4" s="4" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="AN4" s="4" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E5" s="6">
         <v>0.005</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G5" s="2" t="str">
         <f>IF(F5="NS","N",IF($AH5&gt;Parameters!$B$23,"N","Y"))</f>
@@ -3670,16 +3880,16 @@
         <v>7.4</v>
       </c>
       <c r="AD5" s="2" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="AH5" s="14">
         <f t="shared" ref="AH5:AH17" si="6">_xlfn.DAYS(AL5,AK5)</f>
@@ -3712,16 +3922,16 @@
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="E6" s="6">
         <v>0.012</v>
@@ -3799,16 +4009,16 @@
         <v>7.1</v>
       </c>
       <c r="AD6" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="AG6" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="AH6" s="14">
         <f t="shared" si="6"/>
@@ -3841,22 +4051,22 @@
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E7" s="6">
         <v>0.005</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G7" s="2" t="str">
         <f>IF(F7="NS","N",IF($AH7&gt;Parameters!$B$23,"N","Y"))</f>
@@ -3930,16 +4140,16 @@
         <v>8.2</v>
       </c>
       <c r="AD7" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="AH7" s="14">
         <f t="shared" si="6"/>
@@ -3972,22 +4182,22 @@
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E8" s="6">
         <v>0.005</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G8" s="2" t="str">
         <f>IF(F8="NS","N",IF($AH8&gt;Parameters!$B$23,"N","Y"))</f>
@@ -4049,7 +4259,7 @@
         <v>0.008</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="AA8" s="2" t="str">
         <f>IF(Z8="NS","N",IF($AJ8&gt;Parameters!$B$24,"N","Y"))</f>
@@ -4063,16 +4273,16 @@
         <v>7.6</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="AH8" s="14">
         <f t="shared" si="6"/>
@@ -4105,16 +4315,16 @@
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E9" s="6">
         <v>0.019</v>
@@ -4192,16 +4402,16 @@
         <v>6.9</v>
       </c>
       <c r="AD9" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AH9" s="14">
         <f t="shared" si="6"/>
@@ -4234,22 +4444,22 @@
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E10" s="6">
         <v>0.005</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G10" s="2" t="str">
         <f>IF(F10="NS","N",IF($AH10&gt;Parameters!$B$23,"N","Y"))</f>
@@ -4323,16 +4533,16 @@
         <v>7.8</v>
       </c>
       <c r="AD10" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="AE10" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="AH10" s="14">
         <f t="shared" si="6"/>
@@ -4365,22 +4575,22 @@
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E11" s="6">
         <v>0.005</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G11" s="2" t="str">
         <f>IF(F11="NS","N",IF($AH11&gt;Parameters!$B$23,"N","Y"))</f>
@@ -4454,16 +4664,16 @@
         <v>7.2</v>
       </c>
       <c r="AD11" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="AE11" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="AF11" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="AG11" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="AF11" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="AG11" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="AH11" s="14">
         <f t="shared" si="6"/>
@@ -4496,22 +4706,22 @@
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E12" s="6">
         <v>0.005</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G12" s="2" t="str">
         <f>IF(F12="NS","N",IF($AH12&gt;Parameters!$B$23,"N","Y"))</f>
@@ -4585,16 +4795,16 @@
         <v>8.4</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="AH12" s="14">
         <f t="shared" si="6"/>
@@ -4627,16 +4837,16 @@
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E13" s="6">
         <v>0.014</v>
@@ -4714,16 +4924,16 @@
         <v>6.8</v>
       </c>
       <c r="AD13" s="2" t="s">
-        <v>228</v>
+        <v>70</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AH13" s="14">
         <f t="shared" si="6"/>
@@ -4756,22 +4966,22 @@
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E14" s="6">
         <v>0.005</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G14" s="2" t="str">
         <f>IF(F14="NS","N",IF($AH14&gt;Parameters!$B$23,"N","Y"))</f>
@@ -4845,16 +5055,16 @@
         <v>7.5</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AH14" s="14">
         <f t="shared" si="6"/>
@@ -4887,16 +5097,16 @@
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E15" s="6">
         <v>0.012</v>
@@ -4974,16 +5184,16 @@
         <v>7.9</v>
       </c>
       <c r="AD15" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="AH15" s="14">
         <f t="shared" si="6"/>
@@ -5016,22 +5226,22 @@
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E16" s="6">
         <v>0.005</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G16" s="2" t="str">
         <f>IF(F16="NS","N",IF($AH16&gt;Parameters!$B$23,"N","Y"))</f>
@@ -5105,16 +5315,16 @@
         <v>7.3</v>
       </c>
       <c r="AD16" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AG16" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AH16" s="14">
         <f t="shared" si="6"/>
@@ -5147,22 +5357,22 @@
     </row>
     <row r="17" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E17" s="6">
         <v>0.005</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G17" s="2" t="str">
         <f>IF(F17="NS","N",IF($AH17&gt;Parameters!$B$23,"N","Y"))</f>
@@ -5221,7 +5431,7 @@
         <v>0.88</v>
       </c>
       <c r="Z17" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="AA17" s="2" t="str">
         <f>IF(Z17="NS","N",IF($AJ17&gt;Parameters!$B$24,"N","Y"))</f>
@@ -5235,16 +5445,16 @@
         <v>7.4</v>
       </c>
       <c r="AD17" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AE17" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="AG17" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AH17" s="14">
         <f t="shared" si="6"/>
@@ -5255,7 +5465,7 @@
         <v>3</v>
       </c>
       <c r="AJ17" s="14" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AK17" s="14">
         <f t="shared" si="9"/>
@@ -5270,7 +5480,7 @@
         <v>46291</v>
       </c>
       <c r="AN17" s="14" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -5293,26 +5503,26 @@
   <sheetData>
     <row r="1" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>8</v>
@@ -5321,24 +5531,24 @@
         <v>9</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
@@ -5382,7 +5592,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -5426,7 +5636,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>17</v>
@@ -5470,7 +5680,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>18</v>
@@ -5514,7 +5724,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>19</v>
@@ -5558,7 +5768,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>20</v>
@@ -5602,7 +5812,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
@@ -5646,7 +5856,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -5690,7 +5900,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>17</v>
@@ -5734,7 +5944,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>18</v>
@@ -5778,7 +5988,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>19</v>
@@ -5822,7 +6032,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>20</v>
@@ -5866,7 +6076,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
@@ -5910,7 +6120,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -5954,7 +6164,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>17</v>
@@ -5998,7 +6208,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>18</v>
@@ -6042,7 +6252,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>19</v>
@@ -6086,7 +6296,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>20</v>
@@ -6130,7 +6340,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -6174,7 +6384,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -6218,7 +6428,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>17</v>
@@ -6262,7 +6472,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>18</v>
@@ -6306,7 +6516,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>19</v>
@@ -6350,7 +6560,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>20</v>
@@ -6394,7 +6604,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -6438,7 +6648,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -6482,7 +6692,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>17</v>
@@ -6526,7 +6736,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>18</v>
@@ -6570,7 +6780,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>19</v>
@@ -6614,7 +6824,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>20</v>
@@ -6658,7 +6868,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -6702,7 +6912,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -6746,7 +6956,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>17</v>
@@ -6790,7 +7000,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>18</v>
@@ -6834,7 +7044,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>19</v>
@@ -6878,7 +7088,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>20</v>
@@ -6946,12 +7156,12 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -6959,43 +7169,43 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -7342,40 +7552,40 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -7385,566 +7595,1880 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>285</v>
+        <v>149</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>291</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="B4" s="8">
-        <v>6418255</v>
-      </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>293</v>
+      </c>
+      <c r="C4" s="8">
+        <v>4850733</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B5" s="8">
-        <v>6450959</v>
+        <v>294</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:C34" si="0">B5-B4</f>
-        <v>32704</v>
-      </c>
-      <c r="D5" s="2" t="str">
-        <f>IF(C5&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>4888995</v>
+      </c>
+      <c r="D5" s="8">
+        <f t="shared" ref="D5:D36" si="0">C5-C4</f>
+        <v>38262</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <f>IF(D5&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="B6" s="8">
-        <v>6491552</v>
+        <v>295</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="C6" s="8">
+        <v>4928908</v>
+      </c>
+      <c r="D6" s="8">
         <f t="shared" si="0"/>
-        <v>40593</v>
-      </c>
-      <c r="D6" s="2" t="str">
-        <f>IF(C6&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+        <v>39913</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <f>IF(D6&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B7" s="8">
-        <v>6523848</v>
+        <v>296</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="C7" s="8">
-        <f t="shared" si="0"/>
-        <v>32296</v>
-      </c>
-      <c r="D7" s="2" t="str">
-        <f>IF(C7&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B8" s="8">
-        <v>6561503</v>
-      </c>
-      <c r="C8" s="8">
-        <f t="shared" si="0"/>
-        <v>37655</v>
-      </c>
-      <c r="D8" s="2" t="str">
-        <f>IF(C8&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B9" s="8">
-        <v>6565112</v>
-      </c>
-      <c r="C9" s="8">
-        <f t="shared" si="0"/>
-        <v>3609</v>
-      </c>
-      <c r="D9" s="2" t="str">
-        <f>IF(C9&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B10" s="8">
-        <v>6567087</v>
-      </c>
-      <c r="C10" s="8">
-        <f t="shared" si="0"/>
-        <v>1975</v>
-      </c>
-      <c r="D10" s="2" t="str">
-        <f>IF(C10&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="B11" s="8">
-        <v>6567087</v>
-      </c>
-      <c r="C11" s="8">
+        <v>4928908</v>
+      </c>
+      <c r="D7" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D11" s="2" t="str">
-        <f>IF(C11&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7" s="2" t="str">
+        <f>IF(D7&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C8" s="8">
+        <v>4930795</v>
+      </c>
+      <c r="D8" s="8">
+        <f t="shared" si="0"/>
+        <v>1887</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <f>IF(D8&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" s="8">
+        <v>4934115</v>
+      </c>
+      <c r="D9" s="8">
+        <f t="shared" si="0"/>
+        <v>3320</v>
+      </c>
+      <c r="E9" s="2" t="str">
+        <f>IF(D9&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C10" s="8">
+        <v>4966879</v>
+      </c>
+      <c r="D10" s="8">
+        <f t="shared" si="0"/>
+        <v>32764</v>
+      </c>
+      <c r="E10" s="2" t="str">
+        <f>IF(D10&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C11" s="8">
+        <v>5005480</v>
+      </c>
+      <c r="D11" s="8">
+        <f t="shared" si="0"/>
+        <v>38601</v>
+      </c>
+      <c r="E11" s="2" t="str">
+        <f>IF(D11&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="B12" s="8">
+        <v>300</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C12" s="8">
+        <v>5040060</v>
+      </c>
+      <c r="D12" s="8">
+        <f t="shared" si="0"/>
+        <v>34580</v>
+      </c>
+      <c r="E12" s="2" t="str">
+        <f>IF(D12&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C13" s="8">
+        <v>5073651</v>
+      </c>
+      <c r="D13" s="8">
+        <f t="shared" si="0"/>
+        <v>33591</v>
+      </c>
+      <c r="E13" s="2" t="str">
+        <f>IF(D13&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C14" s="8">
+        <v>5109294</v>
+      </c>
+      <c r="D14" s="8">
+        <f t="shared" si="0"/>
+        <v>35643</v>
+      </c>
+      <c r="E14" s="2" t="str">
+        <f>IF(D14&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" s="8">
+        <v>5111030</v>
+      </c>
+      <c r="D15" s="8">
+        <f t="shared" si="0"/>
+        <v>1736</v>
+      </c>
+      <c r="E15" s="2" t="str">
+        <f>IF(D15&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C16" s="8">
+        <v>5113301</v>
+      </c>
+      <c r="D16" s="8">
+        <f t="shared" si="0"/>
+        <v>2271</v>
+      </c>
+      <c r="E16" s="2" t="str">
+        <f>IF(D16&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C17" s="8">
+        <v>5144730</v>
+      </c>
+      <c r="D17" s="8">
+        <f t="shared" si="0"/>
+        <v>31429</v>
+      </c>
+      <c r="E17" s="2" t="str">
+        <f>IF(D17&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C18" s="8">
+        <v>5182044</v>
+      </c>
+      <c r="D18" s="8">
+        <f t="shared" si="0"/>
+        <v>37314</v>
+      </c>
+      <c r="E18" s="2" t="str">
+        <f>IF(D18&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C19" s="8">
+        <v>5214542</v>
+      </c>
+      <c r="D19" s="8">
+        <f t="shared" si="0"/>
+        <v>32498</v>
+      </c>
+      <c r="E19" s="2" t="str">
+        <f>IF(D19&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C20" s="8">
+        <v>5244482</v>
+      </c>
+      <c r="D20" s="8">
+        <f t="shared" si="0"/>
+        <v>29940</v>
+      </c>
+      <c r="E20" s="2" t="str">
+        <f>IF(D20&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C21" s="8">
+        <v>5275429</v>
+      </c>
+      <c r="D21" s="8">
+        <f t="shared" si="0"/>
+        <v>30947</v>
+      </c>
+      <c r="E21" s="2" t="str">
+        <f>IF(D21&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C22" s="8">
+        <v>5277959</v>
+      </c>
+      <c r="D22" s="8">
+        <f t="shared" si="0"/>
+        <v>2530</v>
+      </c>
+      <c r="E22" s="2" t="str">
+        <f>IF(D22&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C23" s="8">
+        <v>5281200</v>
+      </c>
+      <c r="D23" s="8">
+        <f t="shared" si="0"/>
+        <v>3241</v>
+      </c>
+      <c r="E23" s="2" t="str">
+        <f>IF(D23&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C24" s="8">
+        <v>5308225</v>
+      </c>
+      <c r="D24" s="8">
+        <f t="shared" si="0"/>
+        <v>27025</v>
+      </c>
+      <c r="E24" s="2" t="str">
+        <f>IF(D24&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C25" s="8">
+        <v>5348104</v>
+      </c>
+      <c r="D25" s="8">
+        <f t="shared" si="0"/>
+        <v>39879</v>
+      </c>
+      <c r="E25" s="2" t="str">
+        <f>IF(D25&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C26" s="8">
+        <v>5380807</v>
+      </c>
+      <c r="D26" s="8">
+        <f t="shared" si="0"/>
+        <v>32703</v>
+      </c>
+      <c r="E26" s="2" t="str">
+        <f>IF(D26&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C27" s="8">
+        <v>5420993</v>
+      </c>
+      <c r="D27" s="8">
+        <f t="shared" si="0"/>
+        <v>40186</v>
+      </c>
+      <c r="E27" s="2" t="str">
+        <f>IF(D27&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C28" s="8">
+        <v>5460838</v>
+      </c>
+      <c r="D28" s="8">
+        <f t="shared" si="0"/>
+        <v>39845</v>
+      </c>
+      <c r="E28" s="2" t="str">
+        <f>IF(D28&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C29" s="8">
+        <v>5464817</v>
+      </c>
+      <c r="D29" s="8">
+        <f t="shared" si="0"/>
+        <v>3979</v>
+      </c>
+      <c r="E29" s="2" t="str">
+        <f>IF(D29&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C30" s="8">
+        <v>5468274</v>
+      </c>
+      <c r="D30" s="8">
+        <f t="shared" si="0"/>
+        <v>3457</v>
+      </c>
+      <c r="E30" s="2" t="str">
+        <f>IF(D30&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C31" s="8">
+        <v>5507185</v>
+      </c>
+      <c r="D31" s="8">
+        <f t="shared" si="0"/>
+        <v>38911</v>
+      </c>
+      <c r="E31" s="2" t="str">
+        <f>IF(D31&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C32" s="8">
+        <v>5552065</v>
+      </c>
+      <c r="D32" s="8">
+        <f t="shared" si="0"/>
+        <v>44880</v>
+      </c>
+      <c r="E32" s="2" t="str">
+        <f>IF(D32&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C33" s="8">
+        <v>5580546</v>
+      </c>
+      <c r="D33" s="8">
+        <f t="shared" si="0"/>
+        <v>28481</v>
+      </c>
+      <c r="E33" s="2" t="str">
+        <f>IF(D33&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C34" s="8">
+        <v>5609655</v>
+      </c>
+      <c r="D34" s="8">
+        <f t="shared" si="0"/>
+        <v>29109</v>
+      </c>
+      <c r="E34" s="2" t="str">
+        <f>IF(D34&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C35" s="8">
+        <v>5647349</v>
+      </c>
+      <c r="D35" s="8">
+        <f t="shared" si="0"/>
+        <v>37694</v>
+      </c>
+      <c r="E35" s="2" t="str">
+        <f>IF(D35&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C36" s="8">
+        <v>5650305</v>
+      </c>
+      <c r="D36" s="8">
+        <f t="shared" si="0"/>
+        <v>2956</v>
+      </c>
+      <c r="E36" s="2" t="str">
+        <f>IF(D36&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C37" s="8">
+        <v>5653319</v>
+      </c>
+      <c r="D37" s="8">
+        <f t="shared" ref="D37:D68" si="1">C37-C36</f>
+        <v>3014</v>
+      </c>
+      <c r="E37" s="2" t="str">
+        <f>IF(D37&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C38" s="8">
+        <v>5691413</v>
+      </c>
+      <c r="D38" s="8">
+        <f t="shared" si="1"/>
+        <v>38094</v>
+      </c>
+      <c r="E38" s="2" t="str">
+        <f>IF(D38&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C39" s="8">
+        <v>5719903</v>
+      </c>
+      <c r="D39" s="8">
+        <f t="shared" si="1"/>
+        <v>28490</v>
+      </c>
+      <c r="E39" s="2" t="str">
+        <f>IF(D39&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C40" s="8">
+        <v>5760268</v>
+      </c>
+      <c r="D40" s="8">
+        <f t="shared" si="1"/>
+        <v>40365</v>
+      </c>
+      <c r="E40" s="2" t="str">
+        <f>IF(D40&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C41" s="8">
+        <v>5787532</v>
+      </c>
+      <c r="D41" s="8">
+        <f t="shared" si="1"/>
+        <v>27264</v>
+      </c>
+      <c r="E41" s="2" t="str">
+        <f>IF(D41&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C42" s="8">
+        <v>5816134</v>
+      </c>
+      <c r="D42" s="8">
+        <f t="shared" si="1"/>
+        <v>28602</v>
+      </c>
+      <c r="E42" s="2" t="str">
+        <f>IF(D42&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C43" s="8">
+        <v>5819499</v>
+      </c>
+      <c r="D43" s="8">
+        <f t="shared" si="1"/>
+        <v>3365</v>
+      </c>
+      <c r="E43" s="2" t="str">
+        <f>IF(D43&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C44" s="8">
+        <v>5821187</v>
+      </c>
+      <c r="D44" s="8">
+        <f t="shared" si="1"/>
+        <v>1688</v>
+      </c>
+      <c r="E44" s="2" t="str">
+        <f>IF(D44&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C45" s="8">
+        <v>5862271</v>
+      </c>
+      <c r="D45" s="8">
+        <f t="shared" si="1"/>
+        <v>41084</v>
+      </c>
+      <c r="E45" s="2" t="str">
+        <f>IF(D45&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C46" s="8">
+        <v>5902081</v>
+      </c>
+      <c r="D46" s="8">
+        <f t="shared" si="1"/>
+        <v>39810</v>
+      </c>
+      <c r="E46" s="2" t="str">
+        <f>IF(D46&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C47" s="8">
+        <v>5930718</v>
+      </c>
+      <c r="D47" s="8">
+        <f t="shared" si="1"/>
+        <v>28637</v>
+      </c>
+      <c r="E47" s="2" t="str">
+        <f>IF(D47&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="8">
+        <v>5976868</v>
+      </c>
+      <c r="D48" s="8">
+        <f t="shared" si="1"/>
+        <v>46150</v>
+      </c>
+      <c r="E48" s="2" t="str">
+        <f>IF(D48&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C49" s="8">
+        <v>6015134</v>
+      </c>
+      <c r="D49" s="8">
+        <f t="shared" si="1"/>
+        <v>38266</v>
+      </c>
+      <c r="E49" s="2" t="str">
+        <f>IF(D49&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C50" s="8">
+        <v>6017717</v>
+      </c>
+      <c r="D50" s="8">
+        <f t="shared" si="1"/>
+        <v>2583</v>
+      </c>
+      <c r="E50" s="2" t="str">
+        <f>IF(D50&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C51" s="8">
+        <v>6020261</v>
+      </c>
+      <c r="D51" s="8">
+        <f t="shared" si="1"/>
+        <v>2544</v>
+      </c>
+      <c r="E51" s="2" t="str">
+        <f>IF(D51&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C52" s="8">
+        <v>6060365</v>
+      </c>
+      <c r="D52" s="8">
+        <f t="shared" si="1"/>
+        <v>40104</v>
+      </c>
+      <c r="E52" s="2" t="str">
+        <f>IF(D52&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C53" s="8">
+        <v>6091072</v>
+      </c>
+      <c r="D53" s="8">
+        <f t="shared" si="1"/>
+        <v>30707</v>
+      </c>
+      <c r="E53" s="2" t="str">
+        <f>IF(D53&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C54" s="8">
+        <v>6125201</v>
+      </c>
+      <c r="D54" s="8">
+        <f t="shared" si="1"/>
+        <v>34129</v>
+      </c>
+      <c r="E54" s="2" t="str">
+        <f>IF(D54&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C55" s="8">
+        <v>6158723</v>
+      </c>
+      <c r="D55" s="8">
+        <f t="shared" si="1"/>
+        <v>33522</v>
+      </c>
+      <c r="E55" s="2" t="str">
+        <f>IF(D55&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C56" s="8">
+        <v>6192248</v>
+      </c>
+      <c r="D56" s="8">
+        <f t="shared" si="1"/>
+        <v>33525</v>
+      </c>
+      <c r="E56" s="2" t="str">
+        <f>IF(D56&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C57" s="8">
+        <v>6195516</v>
+      </c>
+      <c r="D57" s="8">
+        <f t="shared" si="1"/>
+        <v>3268</v>
+      </c>
+      <c r="E57" s="2" t="str">
+        <f>IF(D57&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C58" s="8">
+        <v>6198538</v>
+      </c>
+      <c r="D58" s="8">
+        <f t="shared" si="1"/>
+        <v>3022</v>
+      </c>
+      <c r="E58" s="2" t="str">
+        <f>IF(D58&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C59" s="8">
+        <v>6238836</v>
+      </c>
+      <c r="D59" s="8">
+        <f t="shared" si="1"/>
+        <v>40298</v>
+      </c>
+      <c r="E59" s="2" t="str">
+        <f>IF(D59&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C60" s="8">
+        <v>6274976</v>
+      </c>
+      <c r="D60" s="8">
+        <f t="shared" si="1"/>
+        <v>36140</v>
+      </c>
+      <c r="E60" s="2" t="str">
+        <f>IF(D60&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C61" s="8">
+        <v>6308839</v>
+      </c>
+      <c r="D61" s="8">
+        <f t="shared" si="1"/>
+        <v>33863</v>
+      </c>
+      <c r="E61" s="2" t="str">
+        <f>IF(D61&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C62" s="8">
+        <v>6344299</v>
+      </c>
+      <c r="D62" s="8">
+        <f t="shared" si="1"/>
+        <v>35460</v>
+      </c>
+      <c r="E62" s="2" t="str">
+        <f>IF(D62&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C63" s="8">
+        <v>6378369</v>
+      </c>
+      <c r="D63" s="8">
+        <f t="shared" si="1"/>
+        <v>34070</v>
+      </c>
+      <c r="E63" s="2" t="str">
+        <f>IF(D63&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C64" s="8">
+        <v>6381430</v>
+      </c>
+      <c r="D64" s="8">
+        <f t="shared" si="1"/>
+        <v>3061</v>
+      </c>
+      <c r="E64" s="2" t="str">
+        <f>IF(D64&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C65" s="8">
+        <v>6383657</v>
+      </c>
+      <c r="D65" s="8">
+        <f t="shared" si="1"/>
+        <v>2227</v>
+      </c>
+      <c r="E65" s="2" t="str">
+        <f>IF(D65&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C66" s="8">
+        <v>6418255</v>
+      </c>
+      <c r="D66" s="8">
+        <f t="shared" si="1"/>
+        <v>34598</v>
+      </c>
+      <c r="E66" s="2" t="str">
+        <f>IF(D66&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C67" s="8">
+        <v>6450959</v>
+      </c>
+      <c r="D67" s="8">
+        <f t="shared" si="1"/>
+        <v>32704</v>
+      </c>
+      <c r="E67" s="2" t="str">
+        <f>IF(D67&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C68" s="8">
+        <v>6491552</v>
+      </c>
+      <c r="D68" s="8">
+        <f t="shared" si="1"/>
+        <v>40593</v>
+      </c>
+      <c r="E68" s="2" t="str">
+        <f>IF(D68&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C69" s="8">
+        <v>6523848</v>
+      </c>
+      <c r="D69" s="8">
+        <f t="shared" ref="D69:D100" si="2">C69-C68</f>
+        <v>32296</v>
+      </c>
+      <c r="E69" s="2" t="str">
+        <f>IF(D69&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C70" s="8">
+        <v>6561503</v>
+      </c>
+      <c r="D70" s="8">
+        <f t="shared" si="2"/>
+        <v>37655</v>
+      </c>
+      <c r="E70" s="2" t="str">
+        <f>IF(D70&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C71" s="8">
+        <v>6565112</v>
+      </c>
+      <c r="D71" s="8">
+        <f t="shared" si="2"/>
+        <v>3609</v>
+      </c>
+      <c r="E71" s="2" t="str">
+        <f>IF(D71&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C72" s="8">
+        <v>6567087</v>
+      </c>
+      <c r="D72" s="8">
+        <f t="shared" si="2"/>
+        <v>1975</v>
+      </c>
+      <c r="E72" s="2" t="str">
+        <f>IF(D72&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C73" s="8">
+        <v>6567087</v>
+      </c>
+      <c r="D73" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E73" s="2" t="str">
+        <f>IF(D73&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C74" s="8">
         <v>6601769</v>
       </c>
-      <c r="C12" s="8">
-        <f t="shared" si="0"/>
+      <c r="D74" s="8">
+        <f t="shared" si="2"/>
         <v>34682</v>
       </c>
-      <c r="D12" s="2" t="str">
-        <f>IF(C12&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="8">
+      <c r="E74" s="2" t="str">
+        <f>IF(D74&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C75" s="8">
         <v>6649069</v>
       </c>
-      <c r="C13" s="8">
-        <f t="shared" si="0"/>
+      <c r="D75" s="8">
+        <f t="shared" si="2"/>
         <v>47300</v>
       </c>
-      <c r="D13" s="2" t="str">
-        <f>IF(C13&gt;Parameters!$B$12,"Yes","No")</f>
+      <c r="E75" s="2" t="str">
+        <f>IF(D75&gt;Parameters!$B$12,"Yes","No")</f>
         <v>Yes</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" s="8">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C76" s="8">
         <v>6680799</v>
       </c>
-      <c r="C14" s="8">
-        <f t="shared" si="0"/>
+      <c r="D76" s="8">
+        <f t="shared" si="2"/>
         <v>31730</v>
       </c>
-      <c r="D14" s="2" t="str">
-        <f>IF(C14&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B15" s="8">
+      <c r="E76" s="2" t="str">
+        <f>IF(D76&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C77" s="8">
         <v>6709642</v>
       </c>
-      <c r="C15" s="8">
-        <f t="shared" si="0"/>
+      <c r="D77" s="8">
+        <f t="shared" si="2"/>
         <v>28843</v>
       </c>
-      <c r="D15" s="2" t="str">
-        <f>IF(C15&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="E77" s="2" t="str">
+        <f>IF(D77&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C78" s="8">
+        <v>6712444</v>
+      </c>
+      <c r="D78" s="8">
+        <f t="shared" si="2"/>
+        <v>2802</v>
+      </c>
+      <c r="E78" s="2" t="str">
+        <f>IF(D78&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C79" s="8">
+        <v>6716224</v>
+      </c>
+      <c r="D79" s="8">
+        <f t="shared" si="2"/>
+        <v>3780</v>
+      </c>
+      <c r="E79" s="2" t="str">
+        <f>IF(D79&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C80" s="8">
+        <v>6753533</v>
+      </c>
+      <c r="D80" s="8">
+        <f t="shared" si="2"/>
+        <v>37309</v>
+      </c>
+      <c r="E80" s="2" t="str">
+        <f>IF(D80&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C81" s="8">
+        <v>6788370</v>
+      </c>
+      <c r="D81" s="8">
+        <f t="shared" si="2"/>
+        <v>34837</v>
+      </c>
+      <c r="E81" s="2" t="str">
+        <f>IF(D81&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C82" s="8">
+        <v>6828334</v>
+      </c>
+      <c r="D82" s="8">
+        <f t="shared" si="2"/>
+        <v>39964</v>
+      </c>
+      <c r="E82" s="2" t="str">
+        <f>IF(D82&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C83" s="8">
+        <v>6856644</v>
+      </c>
+      <c r="D83" s="8">
+        <f t="shared" si="2"/>
+        <v>28310</v>
+      </c>
+      <c r="E83" s="2" t="str">
+        <f>IF(D83&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C84" s="8">
+        <v>6890079</v>
+      </c>
+      <c r="D84" s="8">
+        <f t="shared" si="2"/>
+        <v>33435</v>
+      </c>
+      <c r="E84" s="2" t="str">
+        <f>IF(D84&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C85" s="8">
+        <v>6894233</v>
+      </c>
+      <c r="D85" s="8">
+        <f t="shared" si="2"/>
+        <v>4154</v>
+      </c>
+      <c r="E85" s="2" t="str">
+        <f>IF(D85&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C86" s="8">
+        <v>6898105</v>
+      </c>
+      <c r="D86" s="8">
+        <f t="shared" si="2"/>
+        <v>3872</v>
+      </c>
+      <c r="E86" s="2" t="str">
+        <f>IF(D86&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C87" s="8">
+        <v>6938636</v>
+      </c>
+      <c r="D87" s="8">
+        <f t="shared" si="2"/>
+        <v>40531</v>
+      </c>
+      <c r="E87" s="2" t="str">
+        <f>IF(D87&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C88" s="8">
+        <v>6972764</v>
+      </c>
+      <c r="D88" s="8">
+        <f t="shared" si="2"/>
+        <v>34128</v>
+      </c>
+      <c r="E88" s="2" t="str">
+        <f>IF(D88&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C89" s="8">
+        <v>7000793</v>
+      </c>
+      <c r="D89" s="8">
+        <f t="shared" si="2"/>
+        <v>28029</v>
+      </c>
+      <c r="E89" s="2" t="str">
+        <f>IF(D89&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C90" s="8">
+        <v>7028709</v>
+      </c>
+      <c r="D90" s="8">
+        <f t="shared" si="2"/>
+        <v>27916</v>
+      </c>
+      <c r="E90" s="2" t="str">
+        <f>IF(D90&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C91" s="8">
+        <v>7067653</v>
+      </c>
+      <c r="D91" s="8">
+        <f t="shared" si="2"/>
+        <v>38944</v>
+      </c>
+      <c r="E91" s="2" t="str">
+        <f>IF(D91&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C92" s="8">
+        <v>7071331</v>
+      </c>
+      <c r="D92" s="8">
+        <f t="shared" si="2"/>
+        <v>3678</v>
+      </c>
+      <c r="E92" s="2" t="str">
+        <f>IF(D92&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C93" s="8">
+        <v>7074075</v>
+      </c>
+      <c r="D93" s="8">
+        <f t="shared" si="2"/>
+        <v>2744</v>
+      </c>
+      <c r="E93" s="2" t="str">
+        <f>IF(D93&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B16" s="8">
-        <v>6712444</v>
-      </c>
-      <c r="C16" s="8">
-        <f t="shared" si="0"/>
-        <v>2802</v>
-      </c>
-      <c r="D16" s="2" t="str">
-        <f>IF(C16&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B17" s="8">
-        <v>6716224</v>
-      </c>
-      <c r="C17" s="8">
-        <f t="shared" si="0"/>
-        <v>3780</v>
-      </c>
-      <c r="D17" s="2" t="str">
-        <f>IF(C17&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="B18" s="8">
-        <v>6753533</v>
-      </c>
-      <c r="C18" s="8">
-        <f t="shared" si="0"/>
-        <v>37309</v>
-      </c>
-      <c r="D18" s="2" t="str">
-        <f>IF(C18&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B19" s="8">
-        <v>6788370</v>
-      </c>
-      <c r="C19" s="8">
-        <f t="shared" si="0"/>
-        <v>34837</v>
-      </c>
-      <c r="D19" s="2" t="str">
-        <f>IF(C19&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B20" s="8">
-        <v>6828334</v>
-      </c>
-      <c r="C20" s="8">
-        <f t="shared" si="0"/>
-        <v>39964</v>
-      </c>
-      <c r="D20" s="2" t="str">
-        <f>IF(C20&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" s="8">
-        <v>6856644</v>
-      </c>
-      <c r="C21" s="8">
-        <f t="shared" si="0"/>
-        <v>28310</v>
-      </c>
-      <c r="D21" s="2" t="str">
-        <f>IF(C21&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="B22" s="8">
-        <v>6890079</v>
-      </c>
-      <c r="C22" s="8">
-        <f t="shared" si="0"/>
-        <v>33435</v>
-      </c>
-      <c r="D22" s="2" t="str">
-        <f>IF(C22&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B23" s="8">
-        <v>6894233</v>
-      </c>
-      <c r="C23" s="8">
-        <f t="shared" si="0"/>
-        <v>4154</v>
-      </c>
-      <c r="D23" s="2" t="str">
-        <f>IF(C23&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="B24" s="8">
-        <v>6898105</v>
-      </c>
-      <c r="C24" s="8">
-        <f t="shared" si="0"/>
-        <v>3872</v>
-      </c>
-      <c r="D24" s="2" t="str">
-        <f>IF(C24&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="B25" s="8">
-        <v>6938636</v>
-      </c>
-      <c r="C25" s="8">
-        <f t="shared" si="0"/>
-        <v>40531</v>
-      </c>
-      <c r="D25" s="2" t="str">
-        <f>IF(C25&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B26" s="8">
-        <v>6972764</v>
-      </c>
-      <c r="C26" s="8">
-        <f t="shared" si="0"/>
-        <v>34128</v>
-      </c>
-      <c r="D26" s="2" t="str">
-        <f>IF(C26&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="B27" s="8">
-        <v>7000793</v>
-      </c>
-      <c r="C27" s="8">
-        <f t="shared" si="0"/>
-        <v>28029</v>
-      </c>
-      <c r="D27" s="2" t="str">
-        <f>IF(C27&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="B28" s="8">
-        <v>7028709</v>
-      </c>
-      <c r="C28" s="8">
-        <f t="shared" si="0"/>
-        <v>27916</v>
-      </c>
-      <c r="D28" s="2" t="str">
-        <f>IF(C28&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B29" s="8">
-        <v>7067653</v>
-      </c>
-      <c r="C29" s="8">
-        <f t="shared" si="0"/>
-        <v>38944</v>
-      </c>
-      <c r="D29" s="2" t="str">
-        <f>IF(C29&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
+      <c r="B94" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C94" s="8">
+        <v>7108801</v>
+      </c>
+      <c r="D94" s="8">
+        <f t="shared" si="2"/>
+        <v>34726</v>
+      </c>
+      <c r="E94" s="2" t="str">
+        <f>IF(D94&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C95" s="8">
+        <v>7139484</v>
+      </c>
+      <c r="D95" s="8">
+        <f t="shared" si="2"/>
+        <v>30683</v>
+      </c>
+      <c r="E95" s="2" t="str">
+        <f>IF(D95&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B30" s="8">
-        <v>7071331</v>
-      </c>
-      <c r="C30" s="8">
-        <f t="shared" si="0"/>
-        <v>3678</v>
-      </c>
-      <c r="D30" s="2" t="str">
-        <f>IF(C30&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B31" s="8">
-        <v>7074075</v>
-      </c>
-      <c r="C31" s="8">
-        <f t="shared" si="0"/>
-        <v>2744</v>
-      </c>
-      <c r="D31" s="2" t="str">
-        <f>IF(C31&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B32" s="8">
-        <v>7108801</v>
-      </c>
-      <c r="C32" s="8">
-        <f t="shared" si="0"/>
-        <v>34726</v>
-      </c>
-      <c r="D32" s="2" t="str">
-        <f>IF(C32&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="B33" s="8">
-        <v>7139484</v>
-      </c>
-      <c r="C33" s="8">
-        <f t="shared" si="0"/>
-        <v>30683</v>
-      </c>
-      <c r="D33" s="2" t="str">
-        <f>IF(C33&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B34" s="8">
+      <c r="B96" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C96" s="8">
         <v>7173975</v>
       </c>
-      <c r="C34" s="8">
-        <f t="shared" si="0"/>
+      <c r="D96" s="8">
+        <f t="shared" si="2"/>
         <v>34491</v>
       </c>
-      <c r="D34" s="2" t="str">
-        <f>IF(C34&gt;Parameters!$B$12,"Yes","No")</f>
-        <v>No</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="B36" s="15">
-        <f>MAX(C5:C34)</f>
+      <c r="E96" s="2" t="str">
+        <f>IF(D96&gt;Parameters!$B$12,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B99" s="15">
+        <f>_xlfn.MAXIFS($D$5:$D$96,$B$5:$B$96,"Jul")</f>
+        <v>44880</v>
+      </c>
+      <c r="C99" s="16">
+        <f>COUNTIFS($B$5:$B$96,"Jul",$E$5:$E$96,"Yes")</f>
+        <v>0</v>
+      </c>
+      <c r="D99" s="15">
+        <f>SUMIFS($D$5:$D$96,$B$5:$B$96,"Jul")</f>
+        <v>796616</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B100" s="15">
+        <f>_xlfn.MAXIFS($D$5:$D$96,$B$5:$B$96,"Aug")</f>
+        <v>46150</v>
+      </c>
+      <c r="C100" s="16">
+        <f>COUNTIFS($B$5:$B$96,"Aug",$E$5:$E$96,"Yes")</f>
+        <v>1</v>
+      </c>
+      <c r="D100" s="15">
+        <f>SUMIFS($D$5:$D$96,$B$5:$B$96,"Aug")</f>
+        <v>770906</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B101" s="15">
+        <f>_xlfn.MAXIFS($D$5:$D$96,$B$5:$B$96,"Sep")</f>
         <v>47300</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="B37" s="16">
-        <f>COUNTIF(D5:D34,"Yes")</f>
+      <c r="C101" s="16">
+        <f>COUNTIFS($B$5:$B$96,"Sep",$E$5:$E$96,"Yes")</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="B38" s="15">
-        <f>B34-B4</f>
+      <c r="D101" s="15">
+        <f>SUMIFS($D$5:$D$96,$B$5:$B$96,"Sep")</f>
         <v>755720</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="B39" s="15">
-        <f>SUM(C5:C34)</f>
-        <v>755720</v>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="D102" s="15">
+        <f>C96-C4</f>
+        <v>2323242</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="D103" s="15">
+        <f>SUM(D5:D96)</f>
+        <v>2323242</v>
       </c>
     </row>
   </sheetData>
@@ -7954,7 +9478,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -7968,73 +9492,73 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>311</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>312</v>
+        <v>360</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>313</v>
+        <v>361</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>314</v>
+        <v>362</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>315</v>
+        <v>363</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>316</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>317</v>
+        <v>365</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>318</v>
+        <v>366</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>319</v>
+        <v>367</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>321</v>
+        <v>369</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>322</v>
+        <v>370</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>323</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>324</v>
+        <v>372</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>25</v>
@@ -8042,22 +9566,22 @@
     </row>
     <row r="6" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>326</v>
+        <v>374</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>327</v>
+        <v>375</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>329</v>
+        <v>377</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>25</v>
@@ -8065,22 +9589,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>330</v>
+        <v>378</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>325</v>
+        <v>373</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>302</v>
+        <v>349</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>25</v>
@@ -8088,22 +9612,22 @@
     </row>
     <row r="8" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>331</v>
+        <v>379</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>332</v>
+        <v>380</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>333</v>
+        <v>381</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>334</v>
+        <v>382</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>335</v>
+        <v>383</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>336</v>
+        <v>384</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>25</v>
@@ -8111,22 +9635,22 @@
     </row>
     <row r="9" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>337</v>
+        <v>385</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>332</v>
+        <v>380</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>338</v>
+        <v>386</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>340</v>
+        <v>388</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>25</v>
@@ -8134,22 +9658,22 @@
     </row>
     <row r="10" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>341</v>
+        <v>389</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>332</v>
+        <v>380</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>342</v>
+        <v>390</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>300</v>
+        <v>347</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>343</v>
+        <v>391</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>25</v>
@@ -8157,22 +9681,22 @@
     </row>
     <row r="11" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>344</v>
+        <v>392</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>332</v>
+        <v>380</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>345</v>
+        <v>393</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>346</v>
+        <v>394</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>347</v>
+        <v>395</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>25</v>
@@ -8180,71 +9704,94 @@
     </row>
     <row r="12" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>348</v>
+        <v>396</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>350</v>
+        <v>398</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>351</v>
+        <v>399</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>352</v>
+        <v>400</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>355</v>
+        <v>93</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>356</v>
+        <v>403</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>357</v>
+        <v>404</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>279</v>
+        <v>405</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>358</v>
+        <v>406</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>25</v>
+        <v>407</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>359</v>
+        <v>408</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>360</v>
+        <v>409</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>361</v>
+        <v>410</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>362</v>
+        <v>411</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>335</v>
+        <v>284</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>363</v>
+        <v>412</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>364</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -8254,7 +9801,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
@@ -8262,62 +9809,67 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>365</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>366</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
-        <v>367</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>368</v>
+        <v>422</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
-        <v>369</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
-        <v>370</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
-        <v>371</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>376</v>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="9" t="s">
+        <v>431</v>
       </c>
     </row>
   </sheetData>

--- a/submissions/03-pretreatment-smr-q3-2026/solution/vandeveer_smr_q3_2026.xlsx
+++ b/submissions/03-pretreatment-smr-q3-2026/solution/vandeveer_smr_q3_2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0264311B-AF3B-724C-AC7C-977B44DD0F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F25910F-3CEC-F14B-86A3-58B981756A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="741">
   <si>
     <t>SELF-MONITORING REPORT, THIRD QUARTER 2026 (JULY 1 THROUGH SEPTEMBER 30, 2026)</t>
   </si>
@@ -202,6 +202,30 @@
     <t>The 07/07/2026 composite was not valid, and the laboratory has rejected the zinc result of 07/21/2026 after a failed calibration verification</t>
   </si>
   <si>
+    <t>Cyanide, monitoring frequency, one valid sample</t>
+  </si>
+  <si>
+    <t>The 07/21/2026 cyanide was analyzed 08/04/2026 at 10:20, 339.8 hours after the 06:30 grab and outside the 14-day holding time by 3 hours 50 minutes</t>
+  </si>
+  <si>
+    <t>07/31/2026</t>
+  </si>
+  <si>
+    <t>Replacement samples not collected in July after the 07/21/2026 zinc and cyanide results fell</t>
+  </si>
+  <si>
+    <t>none collected</t>
+  </si>
+  <si>
+    <t>Within the calendar month</t>
+  </si>
+  <si>
+    <t>Section 2.3</t>
+  </si>
+  <si>
+    <t>The 07/21/2026 zinc was rejected, and its cyanide fell outside the holding time on the report of 07/30/2026 with a day of the month left. The 07/21/2026 routine composite stands as the replacement for the 07/07/2026 composite for cadmium, chromium, copper and nickel, and zinc had no valid result in July after the 7th.</t>
+  </si>
+  <si>
     <t>07/26/2026</t>
   </si>
   <si>
@@ -322,6 +346,15 @@
     <t>Cyanide of sample VP-260811 analyzed 08/26/2026, 15 days after collection, outside the 14-day holding time; the valid grabs are those of 08/19/2026 and 08/25/2026</t>
   </si>
   <si>
+    <t>08/31/2026</t>
+  </si>
+  <si>
+    <t>Replacement cyanide sample not collected in August after the 08/11/2026 result fell</t>
+  </si>
+  <si>
+    <t>Report GLA-26-1742 issued 08/27/2026 at 09:30 with four days of the month left; the 08/19 and 08/25 grabs were collected before it</t>
+  </si>
+  <si>
     <t>08/27/2026</t>
   </si>
   <si>
@@ -355,7 +388,7 @@
     <t>2.61 mg/L</t>
   </si>
   <si>
-    <t>Rinse tank RT-4 overflow during the composite</t>
+    <t>Not established in the file; the composite period ended at 06:40 per the chain of custody, before the 07:50 overflow, so the log's note that the composite ran through the event does not hold</t>
   </si>
   <si>
     <t>September 2026</t>
@@ -370,6 +403,18 @@
     <t>The 09/09/2026 result carries the month</t>
   </si>
   <si>
+    <t>The laboratory rejected the 09/09/2026 cyanide in Revision 1 of 09/25/2026, and the 09/23/2026 resample carried no cyanide grab</t>
+  </si>
+  <si>
+    <t>09/30/2026</t>
+  </si>
+  <si>
+    <t>Replacement cyanide sample not collected in September after the 09/09/2026 result was rejected</t>
+  </si>
+  <si>
+    <t>Revision 1 issued 09/25/2026 at 09:40 with five days of the month left</t>
+  </si>
+  <si>
     <t>Flow, daily discharge, metered flow plus the volume around the meter</t>
   </si>
   <si>
@@ -454,13 +499,13 @@
     <t>Threshold for the technical review criterion test, percent</t>
   </si>
   <si>
-    <t>First quarter report, days received after its due date</t>
+    <t>Second quarter report, days received after its due date</t>
   </si>
   <si>
     <t>Plant status for the six-month period</t>
   </si>
   <si>
-    <t>No parameter reaches either percentage threshold; the evaluation tab carries every parameter. The first quarter report reached the City on 06/04/2026 against its 04/15/2026 due date, and the forty-fifth day fell inside the period, so the report arm of Section 3.4 is met. The second quarter report reached the City on 07/14/2026 against its 07/15/2026 due date.</t>
+    <t>No parameter reaches either percentage threshold; the evaluation tab carries every parameter. The second quarter report reached the City on 08/31/2026 against its 07/15/2026 due date, 47 days late, and the forty-fifth day, 08/29/2026, fell inside the period, so the report arm of Section 3.4 is met. The first quarter report reached the City on 05/28/2026, 43 days after 04/15/2026 and inside the 45.</t>
   </si>
   <si>
     <t>CERTIFICATION</t>
@@ -574,9 +619,6 @@
     <t>Six-month evaluation period, last day</t>
   </si>
   <si>
-    <t>09/30/2026</t>
-  </si>
-  <si>
     <t>First day of the period as a serial</t>
   </si>
   <si>
@@ -592,13 +634,19 @@
     <t>Days apart required between the valid samples of a month, at least</t>
   </si>
   <si>
+    <t>Holding time, total cyanide, hours from the grab</t>
+  </si>
+  <si>
+    <t>Section 2.3 of the permit, elapsed hours from the time shown as collected on the chain of custody</t>
+  </si>
+  <si>
     <t>Laboratory results April through September 2026 as reported (lab_results_apr_sep2026.xlsx), with the City's two composites from the Coordinator's note</t>
   </si>
   <si>
     <t>RESULT and QUAL are the laboratory's figures as printed. REVISED carries a figure from a revised report, and the revised result replaces the result first reported (Section 2.2). REJECTED is Y where the laboratory has rejected the result in its case narrative. ALIQUOTS is from the operator logs. COLLECTED is the day on which the composite is pulled (Section 2.2), taken from the operator logs where they show it. VALID marks a valid sample result collected by the permittee for the monthly figures. MEASUREMENT marks a valid result from Outfall 001 inside the six-month period, whether the sample was collected by the permittee or by the City (Section 3.4). TREATED carries a U result at zero for averaging (Section 2.2). DAY VALUE averages the valid results of the same calendar day, and DAY COUNTED marks the one measurement for that day (Section 3.4).</t>
   </si>
   <si>
-    <t>A result is not valid where the composite held fewer than twelve aliquots across the 24 hours, where the analysis fell outside the holding time (6 months for total metals, 14 days for cyanide, an analysis on the fourteenth day being inside it), or where the laboratory has rejected it (Section 2.3). A sample taken anywhere but Outfall 001 is process control information (Section 2.5). A grab is one dip and not a composite of twelve aliquots, so a metals grab, the City's included, is not collected as Section 2.1 requires (Section 2.3).</t>
+    <t>A result is not valid where the composite held fewer than twelve aliquots across the 24 hours, where the analysis started outside the holding time in elapsed hours from the time shown as collected (6 months for total metals, 336 hours for cyanide), or where the laboratory has rejected it, a revision included (Section 2.3). A sample taken anywhere but Outfall 001 is process control information (Section 2.5). A grab is one dip and not a composite of twelve aliquots, so a metals grab, the City's included, is not collected as Section 2.1 requires (Section 2.3).</t>
   </si>
   <si>
     <t>SAMPLE ID</t>
@@ -835,6 +883,18 @@
     <t>CYANIDE ANALYZED, SERIAL</t>
   </si>
   <si>
+    <t>COLLECTED TIME</t>
+  </si>
+  <si>
+    <t>METALS ANALYZED TIME</t>
+  </si>
+  <si>
+    <t>CYANIDE ANALYZED TIME</t>
+  </si>
+  <si>
+    <t>CYANIDE HOLD HOURS</t>
+  </si>
+  <si>
     <t>VP-260331</t>
   </si>
   <si>
@@ -868,6 +928,15 @@
     <t>Collected before April 1, outside the six-month period</t>
   </si>
   <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
     <t>VP-260407</t>
   </si>
   <si>
@@ -895,6 +964,15 @@
     <t>Metals analyzed at 37 days, inside the 6 months</t>
   </si>
   <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
     <t>VP-260421</t>
   </si>
   <si>
@@ -913,6 +991,15 @@
     <t>04/30/2026 15:05</t>
   </si>
   <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
     <t>VP-260505</t>
   </si>
   <si>
@@ -937,7 +1024,16 @@
     <t>05/20/2026 09:15</t>
   </si>
   <si>
-    <t>Chromium reported as measured per the narrative; cyanide analyzed on the fourteenth day</t>
+    <t>Cyanide analyzed 05/19/2026 at 06:30, 335.7 hours after the 06:50 grab, inside the 14-day holding time by 20 minutes</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>06:30</t>
   </si>
   <si>
     <t>VP-260519</t>
@@ -961,6 +1057,12 @@
     <t>Cyanide J value used as reported</t>
   </si>
   <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
     <t>City, first</t>
   </si>
   <si>
@@ -1006,6 +1108,12 @@
     <t>06/12/2026 11:10</t>
   </si>
   <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
     <t>VP-260616</t>
   </si>
   <si>
@@ -1024,6 +1132,15 @@
     <t>06/26/2026 09:50</t>
   </si>
   <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
     <t>City, grab</t>
   </si>
   <si>
@@ -1060,537 +1177,603 @@
     <t>Sampler stopped at 15:10 on 07/06 with 9 aliquots (July log); the cyanide grab stands</t>
   </si>
   <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
     <t>VP-260721</t>
   </si>
   <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>GLA-26-1668</t>
+  </si>
+  <si>
+    <t>07/30/2026 14:05</t>
+  </si>
+  <si>
+    <t>Zinc rejected by the laboratory in the narrative for GLA-26-1668; cyanide analyzed 08/04/2026 at 10:20, 339.8 hours after the 06:30 grab, outside the 14-day holding time by 3 hours 50 minutes</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>VP-260811</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>08/15/2026</t>
+  </si>
+  <si>
+    <t>08/26/2026</t>
+  </si>
+  <si>
+    <t>GLA-26-1742</t>
+  </si>
+  <si>
+    <t>08/27/2026 09:30</t>
+  </si>
+  <si>
+    <t>Copper reported from the dilution; cyanide analyzed at 15 days</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>VP-260818</t>
+  </si>
+  <si>
+    <t>Additional</t>
+  </si>
+  <si>
+    <t>08/23/2026</t>
+  </si>
+  <si>
+    <t>08/24/2026</t>
+  </si>
+  <si>
+    <t>GLA-26-1771</t>
+  </si>
+  <si>
+    <t>08/26/2026 15:40</t>
+  </si>
+  <si>
+    <t>08/18/2026</t>
+  </si>
+  <si>
+    <t>Additional composite, a sample under Section 2.5; started 08/18 and pulled 08/19 at 06:40 (August log)</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>VP-260819</t>
+  </si>
+  <si>
+    <t>Clar. weir</t>
+  </si>
+  <si>
+    <t>not collected</t>
+  </si>
+  <si>
+    <t>GLA-26-1772</t>
+  </si>
+  <si>
+    <t>Grab at the clarifier weir, process control information under Section 2.5</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>City, second</t>
+  </si>
+  <si>
+    <t>Sampler set 08/18, composite pulled 08/19 at 08:20 (Coordinator's note and August log)</t>
+  </si>
+  <si>
+    <t>VP-260825</t>
+  </si>
+  <si>
+    <t>08/29/2026</t>
+  </si>
+  <si>
+    <t>GLA-26-1789</t>
+  </si>
+  <si>
+    <t>09/04/2026 13:15</t>
+  </si>
+  <si>
+    <t>Copper corrected to 4.15 by Revision 1, issued 09/14/2026 at 10:15; 19 aliquots across the 24 hours</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>VP-260909</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>09/12/2026</t>
+  </si>
+  <si>
+    <t>09/14/2026</t>
+  </si>
+  <si>
+    <t>GLA-26-1811</t>
+  </si>
+  <si>
+    <t>09/15/2026 11:20</t>
+  </si>
+  <si>
+    <t>Composite period ended at 06:40 per the chain of custody, before the 07:50 overflow; cyanide rejected by the laboratory in Revision 1 of 09/25/2026</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>VP-260922</t>
+  </si>
+  <si>
+    <t>09/22/2026</t>
+  </si>
+  <si>
+    <t>09/29/2026</t>
+  </si>
+  <si>
+    <t>09/28/2026</t>
+  </si>
+  <si>
+    <t>GLA-26-1897</t>
+  </si>
+  <si>
+    <t>10/01/2026 10:05</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>VP-260923</t>
+  </si>
+  <si>
+    <t>09/23/2026</t>
+  </si>
+  <si>
+    <t>Resample</t>
+  </si>
+  <si>
+    <t>09/26/2026</t>
+  </si>
+  <si>
+    <t>GLA-26-1904</t>
+  </si>
+  <si>
+    <t>Resample after the 09/09 zinc result, metals only</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>Monthly averages and daily maximums by parameter, July through September 2026</t>
+  </si>
+  <si>
+    <t>Monthly average is the arithmetic mean of the valid results collected by the permittee in the month, with non-detects carried at zero (Section 2.2). A resample or an additional Outfall 001 sample counts in the month's average. Daily maximum is the highest valid result in the month. The monitoring frequency is met where the valid results of the month come from two days at least ten days apart (Section 2.1), and a month that does not meet it is monitored below frequency (Section 2.3). The City's composites are not carried here (Section 2.5).</t>
+  </si>
+  <si>
+    <t>DAILY MAXIMUM LIMIT</t>
+  </si>
+  <si>
+    <t>MONTHLY AVERAGE LIMIT</t>
+  </si>
+  <si>
+    <t>MONTHLY AVERAGE</t>
+  </si>
+  <si>
+    <t>DAILY MAXIMUM</t>
+  </si>
+  <si>
+    <t>MONTHLY AVERAGE STATUS</t>
+  </si>
+  <si>
+    <t>DAILY MAXIMUM STATUS</t>
+  </si>
+  <si>
+    <t>FREQUENCY STATUS</t>
+  </si>
+  <si>
+    <t>DAYS FIRST TO LAST VALID SAMPLE</t>
+  </si>
+  <si>
+    <t>Significant noncompliance evaluation, April 1 through September 30, 2026, Section 3.4 of the permit</t>
+  </si>
+  <si>
+    <t>Every valid result from a sample collected at Outfall 001 in the period is a measurement, whether the sample was collected by the permittee or by the City, with resamples and additional samples included. Valid results of the same calendar day are averaged into the one measurement for that day. Each measurement is compared with the daily maximum limitation and with the limitation multiplied by the technical review criterion of 1.2.</t>
+  </si>
+  <si>
+    <t>MEASUREMENTS</t>
+  </si>
+  <si>
+    <t>TRC MULTIPLIER</t>
+  </si>
+  <si>
+    <t>TRC THRESHOLD MG/L</t>
+  </si>
+  <si>
+    <t>ABOVE THE LIMIT</t>
+  </si>
+  <si>
+    <t>SHARE ABOVE THE LIMIT PCT</t>
+  </si>
+  <si>
+    <t>ABOVE THE TRC THRESHOLD</t>
+  </si>
+  <si>
+    <t>SHARE ABOVE THE TRC THRESHOLD PCT</t>
+  </si>
+  <si>
+    <t>CHRONIC AT 66 PCT</t>
+  </si>
+  <si>
+    <t>TRC AT 33 PCT</t>
+  </si>
+  <si>
+    <t>SIGNIFICANT NONCOMPLIANCE</t>
+  </si>
+  <si>
+    <t>CHRONIC THRESHOLD PCT</t>
+  </si>
+  <si>
+    <t>TRC THRESHOLD PCT</t>
+  </si>
+  <si>
+    <t>No parameter reaches the percentage tests. Copper stands at 4 of its 14 measurements over the threshold and zinc at 4 of its 13, so each is one result short of the 33 percent test, and the City's grab of June 23 would be that result if it were a sample. The plant is in significant noncompliance for the period on the report arm below, on the second quarter report.</t>
+  </si>
+  <si>
+    <t>RECORD LEFT OUT</t>
+  </si>
+  <si>
+    <t>RESULTS LEFT OUT</t>
+  </si>
+  <si>
+    <t>WHY</t>
+  </si>
+  <si>
+    <t>WHERE THE FILE SHOWS IT</t>
+  </si>
+  <si>
+    <t>VP-260331, collected 03/31/2026</t>
+  </si>
+  <si>
+    <t>All six parameters</t>
+  </si>
+  <si>
+    <t>Laboratory results, collection date</t>
+  </si>
+  <si>
+    <t>VP-260707, collected 07/07/2026</t>
+  </si>
+  <si>
+    <t>Cadmium, chromium, copper, nickel, zinc</t>
+  </si>
+  <si>
+    <t>Composite of 9 aliquots, stopped at 15:10 on 07/06, against at least twelve across the 24 hours</t>
+  </si>
+  <si>
+    <t>July operator log, 07/07; permit Section 2.1</t>
+  </si>
+  <si>
+    <t>VP-260721, collected 07/21/2026</t>
+  </si>
+  <si>
+    <t>Zinc, printed at 3.48 mg/L</t>
+  </si>
+  <si>
+    <t>Rejected by the laboratory after a failed calibration verification</t>
+  </si>
+  <si>
+    <t>Case narrative for GLA-26-1668; permit Section 2.3</t>
+  </si>
+  <si>
+    <t>VP-260811, collected 08/11/2026</t>
+  </si>
+  <si>
+    <t>Cyanide</t>
+  </si>
+  <si>
+    <t>Analyzed 08/26/2026, 15 days after collection, outside the 14-day holding time</t>
+  </si>
+  <si>
+    <t>Chain of custody log and Methods tab; permit Section 2.3</t>
+  </si>
+  <si>
+    <t>VP-260819, collected 08/19/2026</t>
+  </si>
+  <si>
+    <t>All five metals and its pH of 9.4</t>
+  </si>
+  <si>
+    <t>Grab at the clarifier weir, not at Outfall 001</t>
+  </si>
+  <si>
+    <t>Chain of custody log and August operator log, 08/19; permit Section 2.5</t>
+  </si>
+  <si>
+    <t>City grab, dipped 06/23/2026</t>
+  </si>
+  <si>
+    <t>Copper 4.71 and zinc 1.36</t>
+  </si>
+  <si>
+    <t>A grab dipped at 10:40, not a 24-hour composite of at least twelve aliquots, so not collected as Section 2.1 requires; counted, copper would stand at 5 of 15, which is 33.3 percent</t>
+  </si>
+  <si>
+    <t>Coordinator's note of September 30; permit Sections 2.1, 2.3 and 3.4</t>
+  </si>
+  <si>
+    <t>Test kit reading, 09/24/2026</t>
+  </si>
+  <si>
+    <t>Copper, about 3.9</t>
+  </si>
+  <si>
+    <t>Read on a field test kit, not a method approved under 40 CFR Part 136, so process control information and not a sample</t>
+  </si>
+  <si>
+    <t>September operator log, 09/24; permit Section 2.5</t>
+  </si>
+  <si>
+    <t>Analyzed 08/04/2026 at 10:20, 339.8 hours after the 06:30 grab, outside the 14-day holding time by 3 hours 50 minutes</t>
+  </si>
+  <si>
+    <t>VP-260909, collected 09/09/2026</t>
+  </si>
+  <si>
+    <t>Rejected by the laboratory in Revision 1 of 09/25/2026 after a failed matrix spike</t>
+  </si>
+  <si>
+    <t>Case narrative for GLA-26-1811; permit Section 2.3</t>
+  </si>
+  <si>
+    <t>RECORD COUNTED</t>
+  </si>
+  <si>
+    <t>RESULTS COUNTED</t>
+  </si>
+  <si>
+    <t>City composite pulled 05/27/2026</t>
+  </si>
+  <si>
+    <t>Copper 2.26, zinc 0.97, and cadmium, chromium, nickel under their limits</t>
+  </si>
+  <si>
+    <t>Collected by the City at manhole 44-118, which is Outfall 001; sampler set 05/26 and pulled the next morning</t>
+  </si>
+  <si>
+    <t>Coordinator's note of September 30; permit Section 3.4</t>
+  </si>
+  <si>
+    <t>City composite pulled 08/19/2026 with VP-260818</t>
+  </si>
+  <si>
+    <t>Copper 4.27 and 3.45 averaged to 3.86; zinc 1.08 and 1.21 averaged to 1.145</t>
+  </si>
+  <si>
+    <t>Two valid Outfall 001 results of the same calendar day are the one measurement for that day</t>
+  </si>
+  <si>
+    <t>August operator log, 08/19, and the Coordinator's note; permit Sections 2.2 and 3.4</t>
+  </si>
+  <si>
+    <t>VP-260818, pulled 08/19/2026</t>
+  </si>
+  <si>
+    <t>Five metals and cyanide</t>
+  </si>
+  <si>
+    <t>Additional composite at Outfall 001, 25 aliquots; the laboratory's file carries 08/18/2026, the day it was started</t>
+  </si>
+  <si>
+    <t>August operator log, 08/18 and 08/19; permit Sections 2.2 and 2.5</t>
+  </si>
+  <si>
+    <t>VP-260825, collected 08/25/2026</t>
+  </si>
+  <si>
+    <t>Copper at 4.15 mg/L in place of the 3.15 mg/L printed</t>
+  </si>
+  <si>
+    <t>Revision 1 of 09/14/2026 corrected a keying error</t>
+  </si>
+  <si>
+    <t>Case narrative for GLA-26-1789; permit Section 2.2</t>
+  </si>
+  <si>
+    <t>Five metals</t>
+  </si>
+  <si>
+    <t>Composite of 19 aliquots across the 24 hours</t>
+  </si>
+  <si>
+    <t>August operator log, 08/25; permit Section 2.1</t>
+  </si>
+  <si>
+    <t>VP-260407, collected 04/07/2026</t>
+  </si>
+  <si>
+    <t>Analyzed at 37 days against a holding time of 6 months</t>
+  </si>
+  <si>
+    <t>Chain of custody log and Methods tab</t>
+  </si>
+  <si>
+    <t>VP-260505, collected 05/05/2026</t>
+  </si>
+  <si>
+    <t>Cyanide and chromium</t>
+  </si>
+  <si>
+    <t>Cyanide analyzed 05/19/2026 at 06:30, 335.7 hours after the grab and inside the 14-day holding time by 20 minutes; chromium reported as measured after a low matrix spike</t>
+  </si>
+  <si>
+    <t>Chain of custody log; case narrative for GLA-26-1329</t>
+  </si>
+  <si>
+    <t>REPORT</t>
+  </si>
+  <si>
+    <t>DUE</t>
+  </si>
+  <si>
+    <t>RECEIVED BY THE CITY</t>
+  </si>
+  <si>
+    <t>45-DAY ARM OF SECTION 3.4</t>
+  </si>
+  <si>
+    <t>FORTY-FIFTH DAY</t>
+  </si>
+  <si>
+    <t>DAYS AFTER THE DUE DATE</t>
+  </si>
+  <si>
+    <t>First quarter self-monitoring report (Section 3.1)</t>
+  </si>
+  <si>
+    <t>04/15/2026</t>
+  </si>
+  <si>
+    <t>05/28/2026</t>
+  </si>
+  <si>
+    <t>Not counted</t>
+  </si>
+  <si>
+    <t>05/30/2026</t>
+  </si>
+  <si>
+    <t>Second quarter self-monitoring report (Section 3.1)</t>
+  </si>
+  <si>
+    <t>07/15/2026</t>
+  </si>
+  <si>
+    <t>Significant noncompliance</t>
+  </si>
+  <si>
+    <t>The second quarter report reached the City on 08/31/2026 by the Coordinator's note of September 30, 47 days after its 07/15/2026 due date under Section 3.1; the forty-fifth day fell on 08/29/2026, inside the period, so Section 3.4 counts the failure in this review. The first quarter report reached the City on 05/28/2026 by the plant manager's email of October 5, 43 days after 04/15/2026 and inside the 45, so it is not counted even though the City noticed a violation of Section 3.1 on it.</t>
+  </si>
+  <si>
+    <t>Daily flow, July through September 2026, gallons, worked from the totalizer register readings in the operator logs</t>
+  </si>
+  <si>
+    <t>Each log carries the register at 07:00 the following morning; a day's flow is that reading less the one before it. The register was replaced at 07:05 on 07/17/2026 and the new one started at zero, so the 07/17 flow is read against zero and not against the old register's last reading. The totalizer sits ahead of the sewer connection, so the volume that went to the sewer around the meter on 09/09/2026 is added to that day's discharge. The August 31 line of the log carries two digits transposed, and the register the September log opens on is used for that day.</t>
+  </si>
+  <si>
+    <t>REGISTER AT 07:00 NEXT DAY, GAL</t>
+  </si>
+  <si>
+    <t>DAILY FLOW, GAL</t>
+  </si>
+  <si>
+    <t>ABOVE LIMIT</t>
+  </si>
+  <si>
+    <t>BASIS</t>
+  </si>
+  <si>
+    <t>Register at 07:00 on 07/01/2026</t>
+  </si>
+  <si>
+    <t>07/01/2026</t>
+  </si>
+  <si>
+    <t>07/02/2026</t>
+  </si>
+  <si>
+    <t>07/03/2026</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>07/05/2026</t>
+  </si>
+  <si>
+    <t>07/06/2026</t>
+  </si>
+  <si>
+    <t>07/08/2026</t>
+  </si>
+  <si>
+    <t>07/09/2026</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
+    <t>07/12/2026</t>
+  </si>
+  <si>
+    <t>07/14/2026</t>
+  </si>
+  <si>
+    <t>07/16/2026</t>
+  </si>
+  <si>
+    <t>New register installed at 07:05 on 07/17/2026, after the 07:00 read</t>
+  </si>
+  <si>
+    <t>07/17/2026</t>
+  </si>
+  <si>
+    <t>07/18/2026</t>
+  </si>
+  <si>
+    <t>07/19/2026</t>
+  </si>
+  <si>
+    <t>07/20/2026</t>
+  </si>
+  <si>
+    <t>07/22/2026</t>
+  </si>
+  <si>
+    <t>07/23/2026</t>
+  </si>
+  <si>
+    <t>07/24/2026</t>
+  </si>
+  <si>
     <t>07/25/2026</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>GLA-26-1668</t>
-  </si>
-  <si>
-    <t>07/30/2026 14:05</t>
-  </si>
-  <si>
-    <t>Zinc rejected by the laboratory in the narrative for GLA-26-1668</t>
-  </si>
-  <si>
-    <t>VP-260811</t>
-  </si>
-  <si>
-    <t>Aug</t>
-  </si>
-  <si>
-    <t>08/15/2026</t>
-  </si>
-  <si>
-    <t>08/26/2026</t>
-  </si>
-  <si>
-    <t>GLA-26-1742</t>
-  </si>
-  <si>
-    <t>08/27/2026 09:30</t>
-  </si>
-  <si>
-    <t>Copper reported from the dilution; cyanide analyzed at 15 days</t>
-  </si>
-  <si>
-    <t>VP-260818</t>
-  </si>
-  <si>
-    <t>Additional</t>
-  </si>
-  <si>
-    <t>08/23/2026</t>
-  </si>
-  <si>
-    <t>08/24/2026</t>
-  </si>
-  <si>
-    <t>GLA-26-1771</t>
-  </si>
-  <si>
-    <t>08/26/2026 15:40</t>
-  </si>
-  <si>
-    <t>08/18/2026</t>
-  </si>
-  <si>
-    <t>Additional composite, a sample under Section 2.5; started 08/18 and pulled 08/19 at 06:40 (August log)</t>
-  </si>
-  <si>
-    <t>VP-260819</t>
-  </si>
-  <si>
-    <t>Clar. weir</t>
-  </si>
-  <si>
-    <t>not collected</t>
-  </si>
-  <si>
-    <t>GLA-26-1772</t>
-  </si>
-  <si>
-    <t>Grab at the clarifier weir, process control information under Section 2.5</t>
-  </si>
-  <si>
-    <t>City, second</t>
-  </si>
-  <si>
-    <t>Sampler set 08/18, composite pulled 08/19 at 08:20 (Coordinator's note and August log)</t>
-  </si>
-  <si>
-    <t>VP-260825</t>
-  </si>
-  <si>
-    <t>08/29/2026</t>
-  </si>
-  <si>
-    <t>GLA-26-1789</t>
-  </si>
-  <si>
-    <t>09/04/2026 13:15</t>
-  </si>
-  <si>
-    <t>Copper corrected to 4.15 by Revision 1, issued 09/14/2026 at 10:15; 19 aliquots across the 24 hours</t>
-  </si>
-  <si>
-    <t>VP-260909</t>
-  </si>
-  <si>
-    <t>Sep</t>
-  </si>
-  <si>
-    <t>09/12/2026</t>
-  </si>
-  <si>
-    <t>09/14/2026</t>
-  </si>
-  <si>
-    <t>GLA-26-1811</t>
-  </si>
-  <si>
-    <t>09/15/2026 11:20</t>
-  </si>
-  <si>
-    <t>Composite ran through the RT-4 overflow</t>
-  </si>
-  <si>
-    <t>VP-260922</t>
-  </si>
-  <si>
-    <t>09/22/2026</t>
-  </si>
-  <si>
-    <t>09/29/2026</t>
-  </si>
-  <si>
-    <t>09/28/2026</t>
-  </si>
-  <si>
-    <t>GLA-26-1897</t>
-  </si>
-  <si>
-    <t>10/01/2026 10:05</t>
-  </si>
-  <si>
-    <t>VP-260923</t>
-  </si>
-  <si>
-    <t>09/23/2026</t>
-  </si>
-  <si>
-    <t>Resample</t>
-  </si>
-  <si>
-    <t>09/26/2026</t>
-  </si>
-  <si>
-    <t>GLA-26-1904</t>
-  </si>
-  <si>
-    <t>Resample after the 09/09 zinc result, metals only</t>
-  </si>
-  <si>
-    <t>Monthly averages and daily maximums by parameter, July through September 2026</t>
-  </si>
-  <si>
-    <t>Monthly average is the arithmetic mean of the valid results collected by the permittee in the month, with non-detects carried at zero (Section 2.2). A resample or an additional Outfall 001 sample counts in the month's average. Daily maximum is the highest valid result in the month. The monitoring frequency is met where the valid results of the month come from two days at least ten days apart (Section 2.1), and a month that does not meet it is monitored below frequency (Section 2.3). The City's composites are not carried here (Section 2.5).</t>
-  </si>
-  <si>
-    <t>DAILY MAXIMUM LIMIT</t>
-  </si>
-  <si>
-    <t>MONTHLY AVERAGE LIMIT</t>
-  </si>
-  <si>
-    <t>MONTHLY AVERAGE</t>
-  </si>
-  <si>
-    <t>DAILY MAXIMUM</t>
-  </si>
-  <si>
-    <t>MONTHLY AVERAGE STATUS</t>
-  </si>
-  <si>
-    <t>DAILY MAXIMUM STATUS</t>
-  </si>
-  <si>
-    <t>FREQUENCY STATUS</t>
-  </si>
-  <si>
-    <t>DAYS FIRST TO LAST VALID SAMPLE</t>
-  </si>
-  <si>
-    <t>Significant noncompliance evaluation, April 1 through September 30, 2026, Section 3.4 of the permit</t>
-  </si>
-  <si>
-    <t>Every valid result from a sample collected at Outfall 001 in the period is a measurement, whether the sample was collected by the permittee or by the City, with resamples and additional samples included. Valid results of the same calendar day are averaged into the one measurement for that day. Each measurement is compared with the daily maximum limitation and with the limitation multiplied by the technical review criterion of 1.2.</t>
-  </si>
-  <si>
-    <t>MEASUREMENTS</t>
-  </si>
-  <si>
-    <t>TRC MULTIPLIER</t>
-  </si>
-  <si>
-    <t>TRC THRESHOLD MG/L</t>
-  </si>
-  <si>
-    <t>ABOVE THE LIMIT</t>
-  </si>
-  <si>
-    <t>SHARE ABOVE THE LIMIT PCT</t>
-  </si>
-  <si>
-    <t>ABOVE THE TRC THRESHOLD</t>
-  </si>
-  <si>
-    <t>SHARE ABOVE THE TRC THRESHOLD PCT</t>
-  </si>
-  <si>
-    <t>CHRONIC AT 66 PCT</t>
-  </si>
-  <si>
-    <t>TRC AT 33 PCT</t>
-  </si>
-  <si>
-    <t>SIGNIFICANT NONCOMPLIANCE</t>
-  </si>
-  <si>
-    <t>CHRONIC THRESHOLD PCT</t>
-  </si>
-  <si>
-    <t>TRC THRESHOLD PCT</t>
-  </si>
-  <si>
-    <t>No parameter reaches the percentage tests. Copper stands at 4 of its 14 measurements over the threshold and zinc at 4 of its 13, so each is one result short of the 33 percent test, and the City's grab of June 23 would be that result if it were a sample. The plant is in significant noncompliance for the period on the report arm below.</t>
-  </si>
-  <si>
-    <t>RECORD LEFT OUT</t>
-  </si>
-  <si>
-    <t>RESULTS LEFT OUT</t>
-  </si>
-  <si>
-    <t>WHY</t>
-  </si>
-  <si>
-    <t>WHERE THE FILE SHOWS IT</t>
-  </si>
-  <si>
-    <t>VP-260331, collected 03/31/2026</t>
-  </si>
-  <si>
-    <t>All six parameters</t>
-  </si>
-  <si>
-    <t>Laboratory results, collection date</t>
-  </si>
-  <si>
-    <t>VP-260707, collected 07/07/2026</t>
-  </si>
-  <si>
-    <t>Cadmium, chromium, copper, nickel, zinc</t>
-  </si>
-  <si>
-    <t>Composite of 9 aliquots, stopped at 15:10 on 07/06, against at least twelve across the 24 hours</t>
-  </si>
-  <si>
-    <t>July operator log, 07/07; permit Section 2.1</t>
-  </si>
-  <si>
-    <t>VP-260721, collected 07/21/2026</t>
-  </si>
-  <si>
-    <t>Zinc, printed at 3.48 mg/L</t>
-  </si>
-  <si>
-    <t>Rejected by the laboratory after a failed calibration verification</t>
-  </si>
-  <si>
-    <t>Case narrative for GLA-26-1668; permit Section 2.3</t>
-  </si>
-  <si>
-    <t>VP-260811, collected 08/11/2026</t>
-  </si>
-  <si>
-    <t>Cyanide</t>
-  </si>
-  <si>
-    <t>Analyzed 08/26/2026, 15 days after collection, outside the 14-day holding time</t>
-  </si>
-  <si>
-    <t>Chain of custody log and Methods tab; permit Section 2.3</t>
-  </si>
-  <si>
-    <t>VP-260819, collected 08/19/2026</t>
-  </si>
-  <si>
-    <t>All five metals and its pH of 9.4</t>
-  </si>
-  <si>
-    <t>Grab at the clarifier weir, not at Outfall 001</t>
-  </si>
-  <si>
-    <t>Chain of custody log and August operator log, 08/19; permit Section 2.5</t>
-  </si>
-  <si>
-    <t>City grab, dipped 06/23/2026</t>
-  </si>
-  <si>
-    <t>Copper 4.71 and zinc 1.36</t>
-  </si>
-  <si>
-    <t>A grab dipped at 10:40, not a 24-hour composite of at least twelve aliquots, so not collected as Section 2.1 requires; counted, copper would stand at 5 of 15, which is 33.3 percent</t>
-  </si>
-  <si>
-    <t>Coordinator's note of September 30; permit Sections 2.1, 2.3 and 3.4</t>
-  </si>
-  <si>
-    <t>Test kit reading, 09/24/2026</t>
-  </si>
-  <si>
-    <t>Copper, about 3.9</t>
-  </si>
-  <si>
-    <t>Read on a field test kit, not a method approved under 40 CFR Part 136, so process control information and not a sample</t>
-  </si>
-  <si>
-    <t>September operator log, 09/24; permit Section 2.5</t>
-  </si>
-  <si>
-    <t>City composite pulled 05/27/2026</t>
-  </si>
-  <si>
-    <t>Copper 2.26, zinc 0.97, and cadmium, chromium, nickel under their limits</t>
-  </si>
-  <si>
-    <t>Collected by the City at manhole 44-118, which is Outfall 001; sampler set 05/26 and pulled the next morning</t>
-  </si>
-  <si>
-    <t>Coordinator's note of September 30; permit Section 3.4</t>
-  </si>
-  <si>
-    <t>RECORD COUNTED</t>
-  </si>
-  <si>
-    <t>RESULTS COUNTED</t>
-  </si>
-  <si>
-    <t>City composite pulled 08/19/2026 with VP-260818</t>
-  </si>
-  <si>
-    <t>Copper 4.27 and 3.45 averaged to 3.86; zinc 1.08 and 1.21 averaged to 1.145</t>
-  </si>
-  <si>
-    <t>Two valid Outfall 001 results of the same calendar day are the one measurement for that day</t>
-  </si>
-  <si>
-    <t>August operator log, 08/19, and the Coordinator's note; permit Sections 2.2 and 3.4</t>
-  </si>
-  <si>
-    <t>VP-260818, pulled 08/19/2026</t>
-  </si>
-  <si>
-    <t>Five metals and cyanide</t>
-  </si>
-  <si>
-    <t>Additional composite at Outfall 001, 25 aliquots; the laboratory's file carries 08/18/2026, the day it was started</t>
-  </si>
-  <si>
-    <t>August operator log, 08/18 and 08/19; permit Sections 2.2 and 2.5</t>
-  </si>
-  <si>
-    <t>VP-260825, collected 08/25/2026</t>
-  </si>
-  <si>
-    <t>Copper at 4.15 mg/L in place of the 3.15 mg/L printed</t>
-  </si>
-  <si>
-    <t>Revision 1 of 09/14/2026 corrected a keying error</t>
-  </si>
-  <si>
-    <t>Case narrative for GLA-26-1789; permit Section 2.2</t>
-  </si>
-  <si>
-    <t>Five metals</t>
-  </si>
-  <si>
-    <t>Composite of 19 aliquots across the 24 hours</t>
-  </si>
-  <si>
-    <t>August operator log, 08/25; permit Section 2.1</t>
-  </si>
-  <si>
-    <t>VP-260407, collected 04/07/2026</t>
-  </si>
-  <si>
-    <t>Analyzed at 37 days against a holding time of 6 months</t>
-  </si>
-  <si>
-    <t>Chain of custody log and Methods tab</t>
-  </si>
-  <si>
-    <t>VP-260505, collected 05/05/2026</t>
-  </si>
-  <si>
-    <t>Cyanide and chromium</t>
-  </si>
-  <si>
-    <t>Cyanide analyzed on the fourteenth day; chromium reported as measured after a low matrix spike</t>
-  </si>
-  <si>
-    <t>Chain of custody log; case narrative for GLA-26-1329</t>
-  </si>
-  <si>
-    <t>REPORT</t>
-  </si>
-  <si>
-    <t>DUE</t>
-  </si>
-  <si>
-    <t>RECEIVED BY THE CITY</t>
-  </si>
-  <si>
-    <t>45-DAY ARM OF SECTION 3.4</t>
-  </si>
-  <si>
-    <t>FORTY-FIFTH DAY</t>
-  </si>
-  <si>
-    <t>DAYS AFTER THE DUE DATE</t>
-  </si>
-  <si>
-    <t>First quarter self-monitoring report (Section 3.1)</t>
-  </si>
-  <si>
-    <t>04/15/2026</t>
-  </si>
-  <si>
-    <t>06/04/2026</t>
-  </si>
-  <si>
-    <t>Significant noncompliance</t>
-  </si>
-  <si>
-    <t>05/30/2026</t>
-  </si>
-  <si>
-    <t>Second quarter self-monitoring report (Section 3.1)</t>
-  </si>
-  <si>
-    <t>07/15/2026</t>
-  </si>
-  <si>
-    <t>07/14/2026</t>
-  </si>
-  <si>
-    <t>Not late</t>
-  </si>
-  <si>
-    <t>The first quarter report reached the City on June 4 by the plant manager's email of October 5, 50 days after its due date under Section 3.1. The forty-fifth day fell on 05/30/2026, inside the period, so Section 3.4 counts the failure in this review. The second quarter date is the Coordinator's, from her note of September 30, 2026.</t>
-  </si>
-  <si>
-    <t>Daily flow, July through September 2026, gallons, worked from the totalizer register readings in the operator logs</t>
-  </si>
-  <si>
-    <t>Each log carries the register at 07:00 the following morning; a day's flow is that reading less the one before it. The register was replaced at 07:05 on 07/17/2026 and the new one started at zero, so the 07/17 flow is read against zero and not against the old register's last reading. The totalizer sits ahead of the sewer connection, so the volume that went to the sewer around the meter on 09/09/2026 is added to that day's discharge.</t>
-  </si>
-  <si>
-    <t>REGISTER AT 07:00 NEXT DAY, GAL</t>
-  </si>
-  <si>
-    <t>DAILY FLOW, GAL</t>
-  </si>
-  <si>
-    <t>ABOVE LIMIT</t>
-  </si>
-  <si>
-    <t>Register at 07:00 on 07/01/2026</t>
-  </si>
-  <si>
-    <t>07/01/2026</t>
-  </si>
-  <si>
-    <t>07/02/2026</t>
-  </si>
-  <si>
-    <t>07/03/2026</t>
-  </si>
-  <si>
-    <t>07/04/2026</t>
-  </si>
-  <si>
-    <t>07/05/2026</t>
-  </si>
-  <si>
-    <t>07/06/2026</t>
-  </si>
-  <si>
-    <t>07/08/2026</t>
-  </si>
-  <si>
-    <t>07/09/2026</t>
-  </si>
-  <si>
-    <t>07/10/2026</t>
-  </si>
-  <si>
-    <t>07/12/2026</t>
-  </si>
-  <si>
-    <t>07/16/2026</t>
-  </si>
-  <si>
-    <t>New register installed at 07:05 on 07/17/2026, after the 07:00 read</t>
-  </si>
-  <si>
-    <t>07/17/2026</t>
-  </si>
-  <si>
-    <t>07/18/2026</t>
-  </si>
-  <si>
-    <t>07/19/2026</t>
-  </si>
-  <si>
-    <t>07/20/2026</t>
-  </si>
-  <si>
-    <t>07/22/2026</t>
-  </si>
-  <si>
-    <t>07/23/2026</t>
-  </si>
-  <si>
-    <t>07/24/2026</t>
-  </si>
-  <si>
     <t>07/27/2026</t>
   </si>
   <si>
@@ -1603,9 +1786,6 @@
     <t>07/30/2026</t>
   </si>
   <si>
-    <t>07/31/2026</t>
-  </si>
-  <si>
     <t>08/01/2026</t>
   </si>
   <si>
@@ -1615,9 +1795,6 @@
     <t>08/03/2026</t>
   </si>
   <si>
-    <t>08/04/2026</t>
-  </si>
-  <si>
     <t>08/05/2026</t>
   </si>
   <si>
@@ -1651,7 +1828,7 @@
     <t>08/30/2026</t>
   </si>
   <si>
-    <t>08/31/2026</t>
+    <t>The log line reads 1,137,773; the operator's month-end line and the September opening read 1,173,773, two digits transposed on the line</t>
   </si>
   <si>
     <t>09/01/2026</t>
@@ -1687,7 +1864,7 @@
     <t>09/16/2026</t>
   </si>
   <si>
-    <t>09/18/2026</t>
+    <t>09/25/2026</t>
   </si>
   <si>
     <t>09/19/2026</t>
@@ -1702,9 +1879,6 @@
     <t>09/24/2026</t>
   </si>
   <si>
-    <t>09/25/2026</t>
-  </si>
-  <si>
     <t>09/27/2026</t>
   </si>
   <si>
@@ -1801,6 +1975,18 @@
     <t>08/27/2026, sample VP-260811</t>
   </si>
   <si>
+    <t>Replacement samples in July, Section 2.3, after the 07/21 zinc and cyanide results fell</t>
+  </si>
+  <si>
+    <t>Replacement sample within the calendar month</t>
+  </si>
+  <si>
+    <t>None collected</t>
+  </si>
+  <si>
+    <t>Not made</t>
+  </si>
+  <si>
     <t>Flow of 46,150 gallons on 08/13/2026</t>
   </si>
   <si>
@@ -1810,9 +1996,6 @@
     <t>08/15/2026 07:00</t>
   </si>
   <si>
-    <t>Not made</t>
-  </si>
-  <si>
     <t>In-line pH of 9.2 on 08/20/2026, telephone notice</t>
   </si>
   <si>
@@ -1861,6 +2044,12 @@
     <t>Copper daily maximum exceedance, sample VP-260811, repeat sampling</t>
   </si>
   <si>
+    <t>Replacement cyanide sample in August, Section 2.3, after the 08/11 cyanide fell outside the holding time</t>
+  </si>
+  <si>
+    <t>None collected after the report</t>
+  </si>
+  <si>
     <t>Rinse tank RT-4 overflow, a bypass of the pretreatment system</t>
   </si>
   <si>
@@ -1918,13 +2107,19 @@
     <t>10/01/2026, samples VP-260922 and VP-260923</t>
   </si>
   <si>
+    <t>Replacement cyanide sample in September, Section 2.3, after the laboratory rejected the 09/09 cyanide</t>
+  </si>
+  <si>
+    <t>09/25/2026 09:40, Revision 1</t>
+  </si>
+  <si>
     <t>In-line pH of 5.8 on 09/17/2026, 14:10 to 14:55, telephone notice</t>
   </si>
   <si>
     <t>09/17/2026 14:10</t>
   </si>
   <si>
-    <t>09/18/2026 14:10</t>
+    <t>09/25/2026 14:10</t>
   </si>
   <si>
     <t>09/17/2026 15:20</t>
@@ -1945,7 +2140,7 @@
     <t>Report in the Attachment B format by the 15th</t>
   </si>
   <si>
-    <t>07/14/2026, received by the City</t>
+    <t>08/31/2026, received by the City, 47 days after the due date; the forty-fifth day fell on 08/29/2026</t>
   </si>
   <si>
     <t>Third quarter self-monitoring report</t>
@@ -1987,7 +2182,7 @@
     <t>Open</t>
   </si>
   <si>
-    <t>NOTICES AND REPEAT RESULTS BY STATUS</t>
+    <t>NOTICES, REPEAT RESULTS AND REPLACEMENTS BY STATUS</t>
   </si>
   <si>
     <t>LINES</t>
@@ -2017,7 +2212,7 @@
     <t>Re: Third quarter 2026 self-monitoring report, Permit IP-0421, before you sign</t>
   </si>
   <si>
-    <t>The overflow is not the quarter's only problem, and the six-month review will put the plant in significant noncompliance. It does so on the report arm of Section 3.4 and not on copper. Your email puts the first quarter report at Renee's office on June 4, 50 days after its April 15 due date, and Section 3.4 counts a report more than 45 days late in the period in which the forty-fifth day falls. That day was May 30, inside April through September. The notice of violation in June does not take it out of the review.</t>
+    <t>The overflow is not the quarter's only problem, and the six-month review will put the plant in significant noncompliance. It does so on the report arm of Section 3.4 and not on copper. Renee's note puts the second quarter report at her office on August 31, 47 days after its July 15 due date, and Section 3.4 counts a report more than 45 days late in the period in which the forty-fifth day falls. That day was August 29, inside April through September. Your email calls that report a little late but fine; the permit does not. The first quarter report, the one Renee wrote up, reached her on May 28, 43 days after April 15 and inside the 45, so it is not counted.</t>
   </si>
   <si>
     <t>Copper and zinc both fall short of the percentage tests, each by one result. Copper has 14 measurements in the period, and 4 of them exceed the daily maximum by more than the technical review criterion of 1.2, a threshold of 4.056 mg/L. That is 28.6 percent against the 33 percent test. Zinc has 13 measurements with 4 over its threshold of 3.132 mg/L, which is 30.8 percent.</t>
@@ -2044,16 +2239,19 @@
     <t>August copper exceeded the daily maximum three times, at 4.33 mg/L on August 11, 3.45 mg/L on the additional composite of August 19, and 4.15 mg/L on August 25. The additional composite is a sample under Section 2.5 and counts in the month's average, which is 3.977 mg/L on three valid samples. The City's results are not carried on the report. The other metals met their limits in August. The August 25 composite held 19 aliquots across the 24 hours and is valid. The metals on the April 7 sample were analyzed at 37 days against a holding time of 6 months for total metals, and they stand.</t>
   </si>
   <si>
-    <t>August is below the required frequency for cyanide even though it has two valid results. The August 11 cyanide was analyzed on August 26, 15 days after collection and outside the 14-day holding time. The valid grabs are those of August 19 and August 25, which are 6 days apart, and Section 2.1 counts the frequency as met only where valid results come from two days at least ten days apart. The May 5 cyanide was analyzed on the fourteenth day and stands.</t>
+    <t>August is below the required frequency for cyanide even though it has two valid results. The August 11 cyanide was analyzed on August 26, 15 days after collection and outside the 14-day holding time. The valid grabs are those of August 19 and August 25, which are 6 days apart, and Section 2.1 counts the frequency as met only where valid results come from two days at least ten days apart. The May 5 cyanide was analyzed on the fourteenth day and stands. July and September are also below frequency for cyanide. The July 21 cyanide was analyzed at 10:20 on August 4, 339.8 hours after the 06:30 grab, and the permit runs the holding time in elapsed hours from the time on the chain of custody, so it is outside 14 days by 3 hours 50 minutes. The laboratory rejected the September 9 cyanide in its revision of September 25, and the September 23 resample carried no cyanide grab. The May 5 cyanide was analyzed 335.7 hours after its grab and stands by 20 minutes.</t>
+  </si>
+  <si>
+    <t>Section 2.3 also required a replacement sample in the month each time a result was not valid while the month was open, and none was collected after the result was known. The July 21 routine composite stands as the replacement for the July 7 composite for cadmium, chromium, copper and nickel, and zinc had no valid result in July after the 7th. The July 21 zinc was rejected, and the July 21 cyanide fell outside its holding time, both on the July 30 report with a day of the month left. The August 11 cyanide fell outside its holding time on the August 27 report with four days left, and the September 9 cyanide was rejected on September 25 with five days left. Each month is listed as a violation of Section 2.3.</t>
   </si>
   <si>
     <t>Your note says no day in July or August ran above the flow limit and that the in-line pH stayed inside the range. Luis's logs say otherwise on two counts. The register difference for August 13 is 46,150 gallons against the 45,000 gallon limit, and the meter chart for August 20 reached 9.2. July is clean, with a highest day of 44,880 gallons and a highest reading of 9.0, which is inside the range. The pH of 9.4 on August 19 was read at the clarifier weir and is not an Outfall 001 reading. Two other July entries are not violations. The RT-2 float stuck on July 15, and the rinse tank went to the floor trench. The sump was valved to the equalization tank, and nothing reached the sewer connection. That is not a bypass under Section 4.1. The totalizer register was replaced at 07:05 on July 17, and the new one started at zero. The July 17 flow is 30,947 gallons read against zero, and the flow working carries the replacement as its own line.</t>
   </si>
   <si>
-    <t>September 9 is a flow violation as well as a bypass. The register shows 43,650 gallons for the day, which is under the limit, but the totalizer sits ahead of the sewer connection and the rinse water went to the sewer around the meter. The day's discharge is the metered flow plus about 2,900 gallons, or about 46,550 gallons against the 45,000 gallon limit. The call to Renee at 16:30 on September 10 came 32 hours 40 minutes after the 07:50 event.</t>
-  </si>
-  <si>
-    <t>Zinc at 3.14 mg/L on September 9 carries the September zinc average to 1.653 mg/L against the 1.48 mg/L limit. September copper averages 2.053 mg/L and meets the limit because the September 23 resample counts in the month's average. The 5.8 reading of September 17 is a violation that was called in and reported on time, and the 6.0 of September 11 is inside the range. Not-detected results are carried at zero in the averages, as Section 2.2 directs, which is why the September cadmium average reads 0.004 mg/L. The copper test kit reading of 3.9 mg/L on an Outfall 001 grab on September 24 is process control information under Section 2.5, since a test kit is not a method approved under 40 CFR Part 136, and it is not carried as a sample result.</t>
+    <t>September 9 is a flow violation as well as a bypass. The register shows 43,650 gallons for the day, which is under the limit, but the totalizer sits ahead of the sewer connection and the rinse water went to the sewer around the meter. The day's discharge is the metered flow plus about 2,900 gallons, or about 46,550 gallons against the 45,000 gallon limit. The call to Renee at 16:30 on September 10 came 32 hours 40 minutes after the 07:50 event. Luis's August 31 line reads 1,137,773, but his month-end line and the September opening read 1,173,773, two digits transposed, so the August 31 flow is 34,598 gallons and not a negative figure.</t>
+  </si>
+  <si>
+    <t>Zinc at 3.14 mg/L on September 9 carries the September zinc average to 1.653 mg/L against the 1.48 mg/L limit. Its cause is not established. The chain of custody puts the end of the composite period at 06:40, before the 07:50 overflow, so Luis's note that the composite ran through the event does not hold, and the report does not attribute the result to the overflow. September copper averages 2.053 mg/L and meets the limit because the September 23 resample counts in the month's average. The 5.8 reading of September 17 is a violation that was called in and reported on time, and the 6.0 of September 11 is inside the range. Not-detected results are carried at zero in the averages, as Section 2.2 directs, which is why the September cadmium average reads 0.004 mg/L. The copper test kit reading of 3.9 mg/L on an Outfall 001 grab on September 24 is process control information under Section 2.5, since a test kit is not a method approved under 40 CFR Part 136, and it is not carried as a sample result.</t>
   </si>
   <si>
     <t>You also wrote that you or Luis call Renee whenever a result comes back over a daily limit. Her telephone log shows the July 21 copper and the September 9 zinc called in on time. It shows the August 11 copper called in at 16:10 on August 28, which is 30 hours 40 minutes after the report was issued. It shows no call for the 3.45 mg/L copper reported August 26, and the voicemail Luis logged at 17:05 on August 27 came 25 hours 25 minutes after that report. It shows no call for the 4.15 mg/L copper in Revision 1, none for the August 13 flow, and none for the August 20 pH, which also has no written report. Each is listed as a violation of Section 3.2.</t>
@@ -2501,7 +2699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -2792,7 +2990,7 @@
       </c>
       <c r="D13" s="17">
         <f>'Monthly Stats'!E10</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="17">
         <f>'Monthly Stats'!F10</f>
@@ -2800,11 +2998,11 @@
       </c>
       <c r="F13" s="18">
         <f>'Monthly Stats'!G10</f>
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="G13" s="18">
         <f>'Monthly Stats'!H10</f>
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="H13" s="13" t="str">
         <f>'Monthly Stats'!I10</f>
@@ -2816,7 +3014,7 @@
       </c>
       <c r="J13" s="13" t="str">
         <f>'Monthly Stats'!K10</f>
-        <v>Met</v>
+        <v>Below frequency</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -3494,7 +3692,7 @@
       </c>
       <c r="D35" s="17">
         <f>'Monthly Stats'!E22</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" s="17">
         <f>'Monthly Stats'!F22</f>
@@ -3502,11 +3700,11 @@
       </c>
       <c r="F35" s="18">
         <f>'Monthly Stats'!G22</f>
-        <v>0.325</v>
+        <v>0.24</v>
       </c>
       <c r="G35" s="18">
         <f>'Monthly Stats'!H22</f>
-        <v>0.41</v>
+        <v>0.24</v>
       </c>
       <c r="H35" s="13" t="str">
         <f>'Monthly Stats'!I22</f>
@@ -3518,7 +3716,7 @@
       </c>
       <c r="J35" s="13" t="str">
         <f>'Monthly Stats'!K22</f>
-        <v>Met</v>
+        <v>Below frequency</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -3622,8 +3820,8 @@
         <v>41</v>
       </c>
       <c r="C41" s="22">
-        <f>'Lab Data'!AO14</f>
-        <v>1.77</v>
+        <f>'Lab Data'!AO15</f>
+        <v>4.09</v>
       </c>
       <c r="D41" s="21" t="s">
         <v>42</v>
@@ -3700,128 +3898,128 @@
     </row>
     <row r="45" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="C45" s="24">
+        <f>'Monthly Stats'!E10</f>
+        <v>1</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F45" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C45" s="21" t="s">
+    </row>
+    <row r="46" spans="1:10" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="B46" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="E45" s="21" t="s">
+      <c r="C46" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="21" t="s">
+      <c r="D46" s="21" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B46" s="21" t="s">
+      <c r="E46" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="F46" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="D46" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="E46" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="F46" s="21" t="s">
+    </row>
+    <row r="47" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="21" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="21" t="s">
+      <c r="B47" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="C47" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="C47" s="22">
-        <f>'Lab Data'!AO15</f>
-        <v>4.09</v>
-      </c>
       <c r="D47" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="22">
+        <f>'Lab Data'!AO16</f>
+        <v>4.33</v>
+      </c>
+      <c r="D49" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E47" s="21" t="s">
+      <c r="E49" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="F47" s="21" t="s">
+      <c r="F49" s="21" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="B48" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C48" s="25">
+    <row r="50" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="25">
         <f>'Flow Q3'!$B$101</f>
         <v>46150</v>
       </c>
-      <c r="D48" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="E48" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F48" s="21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B49" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="C49" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E49" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="F49" s="21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="21" t="s">
+      <c r="D50" s="21" t="s">
         <v>76</v>
-      </c>
-      <c r="B50" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C50" s="22">
-        <f>'Lab Data'!AO16</f>
-        <v>4.33</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>42</v>
       </c>
       <c r="E50" s="21" t="s">
         <v>43</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="21" t="s">
         <v>78</v>
       </c>
@@ -3832,418 +4030,520 @@
         <v>80</v>
       </c>
       <c r="D51" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C52" s="22">
+        <f>'Lab Data'!AO17</f>
+        <v>3.45</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F52" s="21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E51" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="F51" s="21" t="s">
+      <c r="E53" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E54" s="21" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B52" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C52" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="E52" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="F52" s="21" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B53" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" s="22">
-        <f>'Lab Data'!AO19</f>
-        <v>4.27</v>
-      </c>
-      <c r="D53" s="21" t="s">
+      <c r="F54" s="21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C55" s="22">
+        <f>'Lab Data'!AO20</f>
+        <v>4.15</v>
+      </c>
+      <c r="D55" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E53" s="21" t="s">
+      <c r="E55" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="F53" s="21" t="s">
+      <c r="F55" s="21" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="B54" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C54" s="23">
+    <row r="56" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" s="23">
         <f>'Monthly Stats'!G13</f>
         <v>3.977</v>
       </c>
-      <c r="D54" s="21" t="s">
+      <c r="D56" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="E54" s="21" t="s">
+      <c r="E56" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="F54" s="21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="B55" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="C55" s="24">
+      <c r="F56" s="21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C57" s="24">
         <f>'Monthly Stats'!L16</f>
         <v>6</v>
       </c>
-      <c r="D55" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="E55" s="21" t="s">
+      <c r="D57" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E57" s="21" t="s">
         <v>51</v>
-      </c>
-      <c r="F55" s="21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="70" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="B56" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="C56" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E56" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="F56" s="21" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="B57" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="C57" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E57" s="21" t="s">
-        <v>74</v>
       </c>
       <c r="F57" s="21" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="21" t="s">
         <v>103</v>
       </c>
       <c r="B58" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C58" s="22">
-        <f>'Lab Data'!BG20</f>
-        <v>1.18</v>
+      <c r="C58" s="24" t="s">
+        <v>59</v>
       </c>
       <c r="D58" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F58" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="E58" s="21" t="s">
+    </row>
+    <row r="59" spans="1:6" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F59" s="21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F60" s="21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="22">
+        <f>'Lab Data'!BG21</f>
+        <v>3.14</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E61" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="F58" s="21" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="B59" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="C59" s="23">
+      <c r="F61" s="21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" s="23">
         <f>'Monthly Stats'!G21</f>
         <v>1.653</v>
       </c>
-      <c r="D59" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="E59" s="21" t="s">
+      <c r="D62" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="E62" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="F59" s="21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="B60" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C60" s="25">
+      <c r="F62" s="21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C63" s="24">
+        <f>'Monthly Stats'!E22</f>
+        <v>1</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F63" s="21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F64" s="21" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C65" s="25">
         <f>'Flow Q3'!$B$109</f>
         <v>46550</v>
       </c>
-      <c r="D60" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="E60" s="21" t="s">
+      <c r="D65" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E65" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="F60" s="21" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="B61" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="C61" s="21" t="s">
+      <c r="F65" s="21" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="D61" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="E61" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="F61" s="21" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="B62" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="C62" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="D62" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E62" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="F62" s="21" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="B63" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C63" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D63" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E63" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="F63" s="21" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="B64" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="C64" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="D64" s="21" t="s">
+      <c r="B66" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E66" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="F66" s="21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E67" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F67" s="21" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B68" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E68" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F68" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B69" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D69" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E64" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="F64" s="21" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" s="14" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="B67" s="17">
+      <c r="E69" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F69" s="21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72" s="17">
         <f>'SNC Review'!B7</f>
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B68" s="17">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="B73" s="17">
         <f>'SNC Review'!H7</f>
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B69" s="19">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B74" s="19">
         <f>'SNC Review'!I7</f>
         <v>28.6</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="B70" s="26" t="str">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75" s="26" t="str">
         <f>'SNC Review'!L7</f>
         <v>Not in significant noncompliance</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="B71" s="17">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="B76" s="17">
         <f>'SNC Review'!B9</f>
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B72" s="17">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="B77" s="17">
         <f>'SNC Review'!H9</f>
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="B73" s="19">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B78" s="19">
         <f>'SNC Review'!I9</f>
         <v>30.8</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B74" s="26" t="str">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B79" s="26" t="str">
         <f>'SNC Review'!L9</f>
         <v>Not in significant noncompliance</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="B75" s="17">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="B80" s="17">
         <f>Parameters!$B$18</f>
         <v>33</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="B76" s="17">
-        <f>'SNC Review'!F33</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B77" s="26" t="str">
-        <f>'SNC Review'!B36</f>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B81" s="17">
+        <f>'SNC Review'!F36</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B82" s="26" t="str">
+        <f>'SNC Review'!B38</f>
         <v>Significant noncompliance</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A78" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A80" s="14" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" ht="150" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="21" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A82" s="13" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" s="13" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A84" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A85" s="13" t="s">
-        <v>147</v>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="150" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="13" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="13" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="13" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -4253,7 +4553,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
@@ -4265,7 +4565,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -4279,10 +4579,10 @@
         <v>10</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -4299,7 +4599,7 @@
         <v>0.005</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -4316,7 +4616,7 @@
         <v>0.01</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -4333,7 +4633,7 @@
         <v>0.01</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -4350,7 +4650,7 @@
         <v>0.02</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -4367,7 +4667,7 @@
         <v>0.02</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -4384,12 +4684,12 @@
         <v>0.005</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>36</v>
@@ -4397,218 +4697,230 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="B12" s="7">
         <v>45000</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="B13" s="6">
         <v>6</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="B14" s="6">
         <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B15" s="9">
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B16" s="6">
         <v>1.2</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B17" s="9">
         <v>66</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="B18" s="9">
         <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B19" s="9">
         <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="B20" s="9">
         <v>5</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B21" s="9">
         <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B22" s="9">
         <v>15</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B23" s="9">
         <v>6</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B24" s="9">
         <v>14</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B25" s="17">
         <v>12</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="13" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="13" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="13" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B28" s="17">
         <f>DATE(VALUE(RIGHT(B26,4)),VALUE(LEFT(B26,2)),VALUE(MID(B26,4,2)))</f>
         <v>46113</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="13" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B29" s="17">
         <f>DATE(VALUE(RIGHT(B27,4)),VALUE(LEFT(B27,2)),VALUE(MID(B27,4,2)))</f>
         <v>46295</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B30" s="17">
         <v>10</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>158</v>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="B31" s="17">
+        <f>B24*24</f>
+        <v>336</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -4618,7 +4930,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:BZ23"/>
+  <dimension ref="A1:CD23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -4682,277 +4994,290 @@
     <col min="74" max="74" width="14" customWidth="1"/>
     <col min="75" max="75" width="70" customWidth="1"/>
     <col min="76" max="78" width="12" customWidth="1"/>
+    <col min="79" max="82" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:78" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:82" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:78" x14ac:dyDescent="0.2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="2" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="3" spans="1:78" x14ac:dyDescent="0.2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:78" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="U4" s="15" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="V4" s="15" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="X4" s="15" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="Y4" s="15" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="Z4" s="15" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="AA4" s="15" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AC4" s="15" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="AD4" s="15" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="AE4" s="15" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="AF4" s="15" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="AG4" s="15" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="AH4" s="15" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="AI4" s="15" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="AJ4" s="15" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="AK4" s="15" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="AL4" s="15" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="AM4" s="15" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="AN4" s="15" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="AO4" s="15" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="AP4" s="15" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="AQ4" s="15" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="AR4" s="15" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="AS4" s="15" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="AT4" s="15" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="AU4" s="15" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="AV4" s="15" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="AW4" s="15" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="AX4" s="15" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="AY4" s="15" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="AZ4" s="15" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="BA4" s="15" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="BB4" s="15" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="BC4" s="15" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="BD4" s="15" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="BE4" s="15" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="BF4" s="15" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="BG4" s="15" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="BH4" s="15" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="BI4" s="15" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="BJ4" s="15" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="BK4" s="15" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="BL4" s="15" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="BM4" s="15" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="BN4" s="15" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="BO4" s="15" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="BP4" s="15" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="BQ4" s="15" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="BR4" s="15" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="BS4" s="15" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="BT4" s="15" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="BU4" s="15" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="BV4" s="15" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="BW4" s="15" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="BX4" s="15" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="BY4" s="15" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="BZ4" s="15" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="5" spans="1:78" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+      <c r="CA4" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="CB4" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="CC4" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="CD4" s="15" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G5" s="13" t="str">
         <f t="shared" ref="G5:G23" si="0">IF(OR(F5="OF-001",F5="manhole 44-118"),"Y","N")</f>
@@ -4967,10 +5292,10 @@
         <v>N</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="M5" s="17">
         <f t="shared" ref="M5:M23" si="1">IF(K5="","",_xlfn.DAYS(BY5,BX5))</f>
@@ -4985,7 +5310,7 @@
         <v>Y</v>
       </c>
       <c r="P5" s="13" t="str">
-        <f>IF(N5="","Y",IF(N5&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD5="","Y",IF(CD5&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="Q5" s="18">
@@ -5130,16 +5455,16 @@
         <v>7.7</v>
       </c>
       <c r="BT5" s="13" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="BU5" s="13" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="BV5" s="13" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="BW5" s="13" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="BX5" s="17">
         <f t="shared" ref="BX5:BX23" si="27">DATE(VALUE(RIGHT(B5,4)),VALUE(LEFT(B5,2)),VALUE(MID(B5,4,2)))</f>
@@ -5153,25 +5478,38 @@
         <f t="shared" si="28"/>
         <v>46116</v>
       </c>
-    </row>
-    <row r="6" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA5" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="CB5" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="CC5" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="CD5" s="19">
+        <f>IF(OR(L5="",L5="not collected",CC5=""),"",ROUND((BZ5+TIMEVALUE(CC5)-BX5-TIMEVALUE(CA5))*24,1))</f>
+        <v>98.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G6" s="13" t="str">
         <f t="shared" si="0"/>
@@ -5186,10 +5524,10 @@
         <v>Y</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="M6" s="17">
         <f t="shared" si="1"/>
@@ -5204,14 +5542,14 @@
         <v>Y</v>
       </c>
       <c r="P6" s="13" t="str">
-        <f>IF(N6="","Y",IF(N6&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD6="","Y",IF(CD6&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="Q6" s="18">
         <v>0.005</v>
       </c>
       <c r="R6" s="13" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="U6" s="13" t="str">
         <f t="shared" si="3"/>
@@ -5352,16 +5690,16 @@
         <v>7.4</v>
       </c>
       <c r="BT6" s="13" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="BU6" s="13" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="BV6" s="13" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="BW6" s="13" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="BX6" s="17">
         <f t="shared" si="27"/>
@@ -5375,25 +5713,38 @@
         <f t="shared" si="28"/>
         <v>46124</v>
       </c>
-    </row>
-    <row r="7" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA6" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="CB6" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="CC6" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="CD6" s="19">
+        <f>IF(OR(L6="",L6="not collected",CC6=""),"",ROUND((BZ6+TIMEVALUE(CC6)-BX6-TIMEVALUE(CA6))*24,1))</f>
+        <v>123.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G7" s="13" t="str">
         <f t="shared" si="0"/>
@@ -5408,10 +5759,10 @@
         <v>Y</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="M7" s="17">
         <f t="shared" si="1"/>
@@ -5426,7 +5777,7 @@
         <v>Y</v>
       </c>
       <c r="P7" s="13" t="str">
-        <f>IF(N7="","Y",IF(N7&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD7="","Y",IF(CD7&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="Q7" s="18">
@@ -5571,13 +5922,13 @@
         <v>7.1</v>
       </c>
       <c r="BT7" s="13" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="BU7" s="13" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="BV7" s="13" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="BX7" s="17">
         <f t="shared" si="27"/>
@@ -5591,25 +5942,38 @@
         <f t="shared" si="28"/>
         <v>46135</v>
       </c>
-    </row>
-    <row r="8" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA7" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="CB7" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="CC7" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="CD7" s="19">
+        <f>IF(OR(L7="",L7="not collected",CC7=""),"",ROUND((BZ7+TIMEVALUE(CC7)-BX7-TIMEVALUE(CA7))*24,1))</f>
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G8" s="13" t="str">
         <f t="shared" si="0"/>
@@ -5624,10 +5988,10 @@
         <v>Y</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="M8" s="17">
         <f t="shared" si="1"/>
@@ -5642,14 +6006,14 @@
         <v>Y</v>
       </c>
       <c r="P8" s="13" t="str">
-        <f>IF(N8="","Y",IF(N8&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD8="","Y",IF(CD8&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="Q8" s="18">
         <v>0.005</v>
       </c>
       <c r="R8" s="13" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="U8" s="13" t="str">
         <f t="shared" si="3"/>
@@ -5675,7 +6039,7 @@
         <v>1.13</v>
       </c>
       <c r="AA8" s="13" t="s">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="AD8" s="13" t="str">
         <f t="shared" si="7"/>
@@ -5793,16 +6157,16 @@
         <v>8.2</v>
       </c>
       <c r="BT8" s="13" t="s">
-        <v>298</v>
+        <v>327</v>
       </c>
       <c r="BU8" s="13" t="s">
-        <v>299</v>
+        <v>328</v>
       </c>
       <c r="BV8" s="13" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="BW8" s="13" t="s">
-        <v>300</v>
+        <v>329</v>
       </c>
       <c r="BX8" s="17">
         <f t="shared" si="27"/>
@@ -5816,25 +6180,38 @@
         <f t="shared" si="28"/>
         <v>46161</v>
       </c>
-    </row>
-    <row r="9" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA8" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="CB8" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="CC8" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="CD8" s="19">
+        <f>IF(OR(L8="",L8="not collected",CC8=""),"",ROUND((BZ8+TIMEVALUE(CC8)-BX8-TIMEVALUE(CA8))*24,1))</f>
+        <v>335.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G9" s="13" t="str">
         <f t="shared" si="0"/>
@@ -5849,10 +6226,10 @@
         <v>Y</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>302</v>
+        <v>334</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="M9" s="17">
         <f t="shared" si="1"/>
@@ -5867,14 +6244,14 @@
         <v>Y</v>
       </c>
       <c r="P9" s="13" t="str">
-        <f>IF(N9="","Y",IF(N9&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD9="","Y",IF(CD9&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="Q9" s="18">
         <v>0.005</v>
       </c>
       <c r="R9" s="13" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="U9" s="13" t="str">
         <f t="shared" si="3"/>
@@ -5992,7 +6369,7 @@
         <v>0.008</v>
       </c>
       <c r="BK9" s="13" t="s">
-        <v>304</v>
+        <v>336</v>
       </c>
       <c r="BN9" s="13" t="str">
         <f t="shared" si="23"/>
@@ -6018,16 +6395,16 @@
         <v>7.6</v>
       </c>
       <c r="BT9" s="13" t="s">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="BU9" s="13" t="s">
-        <v>306</v>
+        <v>338</v>
       </c>
       <c r="BV9" s="13" t="s">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="BW9" s="13" t="s">
-        <v>307</v>
+        <v>339</v>
       </c>
       <c r="BX9" s="17">
         <f t="shared" si="27"/>
@@ -6041,25 +6418,38 @@
         <f t="shared" si="28"/>
         <v>46167</v>
       </c>
-    </row>
-    <row r="10" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA9" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="CB9" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="CC9" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="CD9" s="19">
+        <f>IF(OR(L9="",L9="not collected",CC9=""),"",ROUND((BZ9+TIMEVALUE(CC9)-BX9-TIMEVALUE(CA9))*24,1))</f>
+        <v>146.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>309</v>
+        <v>343</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>310</v>
+        <v>344</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="G10" s="13" t="str">
         <f t="shared" si="0"/>
@@ -6090,7 +6480,7 @@
         <v>Y</v>
       </c>
       <c r="Q10" s="13" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="U10" s="13" t="str">
         <f t="shared" si="3"/>
@@ -6113,7 +6503,7 @@
         <v>Y</v>
       </c>
       <c r="Z10" s="13" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="AD10" s="13" t="str">
         <f t="shared" si="7"/>
@@ -6159,7 +6549,7 @@
         <v>Y</v>
       </c>
       <c r="AR10" s="13" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="AV10" s="13" t="str">
         <f t="shared" si="15"/>
@@ -6205,7 +6595,7 @@
         <v>Y</v>
       </c>
       <c r="BK10" s="13" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="BN10" s="13" t="str">
         <f t="shared" si="23"/>
@@ -6228,31 +6618,35 @@
         <v>N</v>
       </c>
       <c r="BW10" s="13" t="s">
-        <v>315</v>
+        <v>349</v>
       </c>
       <c r="BX10" s="17">
         <f t="shared" si="27"/>
         <v>46169</v>
       </c>
-    </row>
-    <row r="11" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA10" s="17"/>
+      <c r="CB10" s="17"/>
+      <c r="CC10" s="17"/>
+      <c r="CD10" s="17"/>
+    </row>
+    <row r="11" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
-        <v>316</v>
+        <v>350</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>318</v>
+        <v>352</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G11" s="13" t="str">
         <f t="shared" si="0"/>
@@ -6267,10 +6661,10 @@
         <v>Y</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>319</v>
+        <v>353</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="M11" s="17">
         <f t="shared" si="1"/>
@@ -6285,7 +6679,7 @@
         <v>Y</v>
       </c>
       <c r="P11" s="13" t="str">
-        <f>IF(N11="","Y",IF(N11&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD11="","Y",IF(CD11&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="Q11" s="18">
@@ -6430,13 +6824,13 @@
         <v>6.9</v>
       </c>
       <c r="BT11" s="13" t="s">
-        <v>321</v>
+        <v>355</v>
       </c>
       <c r="BU11" s="13" t="s">
-        <v>322</v>
+        <v>356</v>
       </c>
       <c r="BV11" s="13" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="BX11" s="17">
         <f t="shared" si="27"/>
@@ -6450,25 +6844,38 @@
         <f>DATE(VALUE(RIGHT(L11,4)),VALUE(LEFT(L11,2)),VALUE(MID(L11,4,2)))</f>
         <v>46180</v>
       </c>
-    </row>
-    <row r="12" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA11" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="CB11" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="CC11" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="CD11" s="19">
+        <f>IF(OR(L11="",L11="not collected",CC11=""),"",ROUND((BZ11+TIMEVALUE(CC11)-BX11-TIMEVALUE(CA11))*24,1))</f>
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>318</v>
+        <v>352</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G12" s="13" t="str">
         <f t="shared" si="0"/>
@@ -6483,10 +6890,10 @@
         <v>Y</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>326</v>
+        <v>362</v>
       </c>
       <c r="M12" s="17">
         <f t="shared" si="1"/>
@@ -6501,14 +6908,14 @@
         <v>Y</v>
       </c>
       <c r="P12" s="13" t="str">
-        <f>IF(N12="","Y",IF(N12&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD12="","Y",IF(CD12&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="Q12" s="18">
         <v>0.005</v>
       </c>
       <c r="R12" s="13" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="U12" s="13" t="str">
         <f t="shared" si="3"/>
@@ -6649,13 +7056,13 @@
         <v>7.8</v>
       </c>
       <c r="BT12" s="13" t="s">
-        <v>327</v>
+        <v>363</v>
       </c>
       <c r="BU12" s="13" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="BV12" s="13" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="BX12" s="17">
         <f t="shared" si="27"/>
@@ -6669,25 +7076,38 @@
         <f>DATE(VALUE(RIGHT(L12,4)),VALUE(LEFT(L12,2)),VALUE(MID(L12,4,2)))</f>
         <v>46191</v>
       </c>
-    </row>
-    <row r="13" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA12" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="CB12" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="CC12" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="CD12" s="19">
+        <f>IF(OR(L12="",L12="not collected",CC12=""),"",ROUND((BZ12+TIMEVALUE(CC12)-BX12-TIMEVALUE(CA12))*24,1))</f>
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
-        <v>329</v>
+        <v>368</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>318</v>
+        <v>352</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>331</v>
+        <v>370</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="G13" s="13" t="str">
         <f t="shared" si="0"/>
@@ -6721,7 +7141,7 @@
         <v>Y</v>
       </c>
       <c r="Q13" s="13" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="U13" s="13" t="str">
         <f t="shared" si="3"/>
@@ -6744,7 +7164,7 @@
         <v>N</v>
       </c>
       <c r="Z13" s="13" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="AD13" s="13" t="str">
         <f t="shared" si="7"/>
@@ -6790,7 +7210,7 @@
         <v>N</v>
       </c>
       <c r="AR13" s="13" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="AV13" s="13" t="str">
         <f t="shared" si="15"/>
@@ -6836,7 +7256,7 @@
         <v>N</v>
       </c>
       <c r="BK13" s="13" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="BN13" s="13" t="str">
         <f t="shared" si="23"/>
@@ -6859,34 +7279,38 @@
         <v>N</v>
       </c>
       <c r="BV13" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
       <c r="BW13" s="13" t="s">
-        <v>332</v>
+        <v>371</v>
       </c>
       <c r="BX13" s="17">
         <f t="shared" si="27"/>
         <v>46196</v>
       </c>
-    </row>
-    <row r="14" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA13" s="17"/>
+      <c r="CB13" s="17"/>
+      <c r="CC13" s="17"/>
+      <c r="CD13" s="17"/>
+    </row>
+    <row r="14" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
-        <v>333</v>
+        <v>372</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>334</v>
+        <v>373</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G14" s="13" t="str">
         <f t="shared" si="0"/>
@@ -6904,10 +7328,10 @@
         <v>Y</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>336</v>
+        <v>375</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>337</v>
+        <v>376</v>
       </c>
       <c r="M14" s="17">
         <f t="shared" si="1"/>
@@ -6922,14 +7346,14 @@
         <v>Y</v>
       </c>
       <c r="P14" s="13" t="str">
-        <f>IF(N14="","Y",IF(N14&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD14="","Y",IF(CD14&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="Q14" s="18">
         <v>0.005</v>
       </c>
       <c r="R14" s="13" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="U14" s="13" t="str">
         <f t="shared" si="3"/>
@@ -7070,16 +7494,16 @@
         <v>7.2</v>
       </c>
       <c r="BT14" s="13" t="s">
-        <v>338</v>
+        <v>377</v>
       </c>
       <c r="BU14" s="13" t="s">
-        <v>339</v>
+        <v>378</v>
       </c>
       <c r="BV14" s="13" t="s">
-        <v>334</v>
+        <v>373</v>
       </c>
       <c r="BW14" s="13" t="s">
-        <v>340</v>
+        <v>379</v>
       </c>
       <c r="BX14" s="17">
         <f t="shared" si="27"/>
@@ -7093,25 +7517,38 @@
         <f t="shared" si="29"/>
         <v>46216</v>
       </c>
-    </row>
-    <row r="15" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA14" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="CB14" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="CC14" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="CD14" s="19">
+        <f>IF(OR(L14="",L14="not collected",CC14=""),"",ROUND((BZ14+TIMEVALUE(CC14)-BX14-TIMEVALUE(CA14))*24,1))</f>
+        <v>147.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
-        <v>341</v>
+        <v>382</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>40</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G15" s="13" t="str">
         <f t="shared" si="0"/>
@@ -7129,10 +7566,10 @@
         <v>Y</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="M15" s="17">
         <f t="shared" si="1"/>
@@ -7140,21 +7577,21 @@
       </c>
       <c r="N15" s="17">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O15" s="13" t="str">
         <f>IF(K15="","Y",IF(BY15&lt;=EDATE(BX15,Parameters!$B$23),"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="P15" s="13" t="str">
-        <f>IF(N15="","Y",IF(N15&lt;=Parameters!$B$24,"Y","N"))</f>
-        <v>Y</v>
+        <f>IF(CD15="","Y",IF(CD15&lt;=Parameters!$B$31,"Y","N"))</f>
+        <v>N</v>
       </c>
       <c r="Q15" s="18">
         <v>0.005</v>
       </c>
       <c r="R15" s="13" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="U15" s="13" t="str">
         <f t="shared" si="3"/>
@@ -7249,10 +7686,10 @@
         <v>3.48</v>
       </c>
       <c r="BB15" s="13" t="s">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="BD15" s="13" t="s">
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="BE15" s="13" t="str">
         <f t="shared" si="19"/>
@@ -7279,38 +7716,38 @@
       </c>
       <c r="BN15" s="13" t="str">
         <f t="shared" si="23"/>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="BO15" s="13" t="str">
         <f t="shared" si="24"/>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="BP15" s="18">
         <f t="shared" si="25"/>
         <v>0.35</v>
       </c>
-      <c r="BQ15" s="18">
+      <c r="BQ15" s="18" t="str">
         <f t="shared" si="26"/>
-        <v>0.35</v>
+        <v/>
       </c>
       <c r="BR15" s="13" t="str">
         <f>IF(AND(BO15="Y",COUNTIFS($BX$5:$BX15,$BX15,$BO$5:$BO15,"Y")=1),"Y","N")</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="BS15" s="19">
         <v>8.4</v>
       </c>
       <c r="BT15" s="13" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="BU15" s="13" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="BV15" s="13" t="s">
         <v>40</v>
       </c>
       <c r="BW15" s="13" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="BX15" s="17">
         <f t="shared" si="27"/>
@@ -7322,27 +7759,40 @@
       </c>
       <c r="BZ15" s="17">
         <f t="shared" si="29"/>
-        <v>46228</v>
-      </c>
-    </row>
-    <row r="16" spans="1:78" x14ac:dyDescent="0.2">
+        <v>46238</v>
+      </c>
+      <c r="CA15" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="CB15" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="CC15" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="CD15" s="19">
+        <f>IF(OR(L15="",L15="not collected",CC15=""),"",ROUND((BZ15+TIMEVALUE(CC15)-BX15-TIMEVALUE(CA15))*24,1))</f>
+        <v>339.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
-        <v>347</v>
+        <v>390</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G16" s="13" t="str">
         <f t="shared" si="0"/>
@@ -7360,10 +7810,10 @@
         <v>Y</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>349</v>
+        <v>392</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>350</v>
+        <v>393</v>
       </c>
       <c r="M16" s="17">
         <f t="shared" si="1"/>
@@ -7378,7 +7828,7 @@
         <v>Y</v>
       </c>
       <c r="P16" s="13" t="str">
-        <f>IF(N16="","Y",IF(N16&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD16="","Y",IF(CD16&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>N</v>
       </c>
       <c r="Q16" s="18">
@@ -7431,7 +7881,7 @@
         <v>4.33</v>
       </c>
       <c r="AJ16" s="13" t="s">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="AM16" s="13" t="str">
         <f t="shared" si="11"/>
@@ -7526,16 +7976,16 @@
         <v>6.8</v>
       </c>
       <c r="BT16" s="13" t="s">
-        <v>351</v>
+        <v>394</v>
       </c>
       <c r="BU16" s="13" t="s">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="BV16" s="13" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="BW16" s="13" t="s">
-        <v>353</v>
+        <v>396</v>
       </c>
       <c r="BX16" s="17">
         <f t="shared" si="27"/>
@@ -7549,25 +7999,38 @@
         <f t="shared" si="29"/>
         <v>46260</v>
       </c>
-    </row>
-    <row r="17" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA16" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="CB16" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="CC16" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="CD16" s="19">
+        <f>IF(OR(L16="",L16="not collected",CC16=""),"",ROUND((BZ16+TIMEVALUE(CC16)-BX16-TIMEVALUE(CA16))*24,1))</f>
+        <v>367.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
-        <v>354</v>
+        <v>399</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>355</v>
+        <v>400</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G17" s="13" t="str">
         <f t="shared" si="0"/>
@@ -7585,10 +8048,10 @@
         <v>Y</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>356</v>
+        <v>401</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>357</v>
+        <v>402</v>
       </c>
       <c r="M17" s="17">
         <f t="shared" si="1"/>
@@ -7603,14 +8066,14 @@
         <v>Y</v>
       </c>
       <c r="P17" s="13" t="str">
-        <f>IF(N17="","Y",IF(N17&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD17="","Y",IF(CD17&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="Q17" s="18">
         <v>0.005</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="U17" s="13" t="str">
         <f t="shared" si="3"/>
@@ -7751,16 +8214,16 @@
         <v>7.4</v>
       </c>
       <c r="BT17" s="13" t="s">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="BU17" s="13" t="s">
-        <v>359</v>
+        <v>404</v>
       </c>
       <c r="BV17" s="13" t="s">
-        <v>360</v>
+        <v>405</v>
       </c>
       <c r="BW17" s="13" t="s">
-        <v>361</v>
+        <v>406</v>
       </c>
       <c r="BX17" s="17">
         <f t="shared" si="27"/>
@@ -7774,25 +8237,38 @@
         <f t="shared" si="29"/>
         <v>46258</v>
       </c>
-    </row>
-    <row r="18" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA17" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="CB17" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="CC17" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="CD17" s="19">
+        <f>IF(OR(L17="",L17="not collected",CC17=""),"",ROUND((BZ17+TIMEVALUE(CC17)-BX17-TIMEVALUE(CA17))*24,1))</f>
+        <v>123.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
-        <v>362</v>
+        <v>409</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>355</v>
+        <v>400</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>363</v>
+        <v>410</v>
       </c>
       <c r="G18" s="13" t="str">
         <f t="shared" si="0"/>
@@ -7807,10 +8283,10 @@
         <v>Y</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>356</v>
+        <v>401</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>364</v>
+        <v>411</v>
       </c>
       <c r="M18" s="17">
         <f t="shared" si="1"/>
@@ -7825,7 +8301,7 @@
         <v>Y</v>
       </c>
       <c r="P18" s="13" t="str">
-        <f>IF(N18="","Y",IF(N18&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD18="","Y",IF(CD18&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="Q18" s="18">
@@ -7944,7 +8420,7 @@
         <v>N</v>
       </c>
       <c r="BK18" s="13" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="BN18" s="13" t="str">
         <f t="shared" si="23"/>
@@ -7970,16 +8446,16 @@
         <v>9.4</v>
       </c>
       <c r="BT18" s="13" t="s">
-        <v>365</v>
+        <v>412</v>
       </c>
       <c r="BU18" s="13" t="s">
-        <v>359</v>
+        <v>404</v>
       </c>
       <c r="BV18" s="13" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="BW18" s="13" t="s">
-        <v>366</v>
+        <v>413</v>
       </c>
       <c r="BX18" s="17">
         <f t="shared" si="27"/>
@@ -7989,25 +8465,36 @@
         <f>DATE(VALUE(RIGHT(K18,4)),VALUE(LEFT(K18,2)),VALUE(MID(K18,4,2)))</f>
         <v>46257</v>
       </c>
-    </row>
-    <row r="19" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA18" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="CB18" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="CC18" s="17"/>
+      <c r="CD18" s="19" t="str">
+        <f>IF(OR(L18="",L18="not collected",CC18=""),"",ROUND((BZ18+TIMEVALUE(CC18)-BX18-TIMEVALUE(CA18))*24,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>367</v>
+        <v>415</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>310</v>
+        <v>344</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="G19" s="13" t="str">
         <f t="shared" si="0"/>
@@ -8038,7 +8525,7 @@
         <v>Y</v>
       </c>
       <c r="Q19" s="13" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="U19" s="13" t="str">
         <f t="shared" si="3"/>
@@ -8061,7 +8548,7 @@
         <v>N</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="AD19" s="13" t="str">
         <f t="shared" si="7"/>
@@ -8107,7 +8594,7 @@
         <v>N</v>
       </c>
       <c r="AR19" s="13" t="s">
-        <v>313</v>
+        <v>347</v>
       </c>
       <c r="AV19" s="13" t="str">
         <f t="shared" si="15"/>
@@ -8153,7 +8640,7 @@
         <v>N</v>
       </c>
       <c r="BK19" s="13" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="BN19" s="13" t="str">
         <f t="shared" si="23"/>
@@ -8176,31 +8663,35 @@
         <v>N</v>
       </c>
       <c r="BW19" s="13" t="s">
-        <v>368</v>
+        <v>416</v>
       </c>
       <c r="BX19" s="17">
         <f t="shared" si="27"/>
         <v>46253</v>
       </c>
-    </row>
-    <row r="20" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA19" s="17"/>
+      <c r="CB19" s="17"/>
+      <c r="CC19" s="17"/>
+      <c r="CD19" s="17"/>
+    </row>
+    <row r="20" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
-        <v>369</v>
+        <v>417</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G20" s="13" t="str">
         <f t="shared" si="0"/>
@@ -8218,10 +8709,10 @@
         <v>Y</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>370</v>
+        <v>418</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="M20" s="17">
         <f t="shared" si="1"/>
@@ -8236,14 +8727,14 @@
         <v>Y</v>
       </c>
       <c r="P20" s="13" t="str">
-        <f>IF(N20="","Y",IF(N20&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD20="","Y",IF(CD20&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="Q20" s="18">
         <v>0.005</v>
       </c>
       <c r="R20" s="13" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="U20" s="13" t="str">
         <f t="shared" si="3"/>
@@ -8292,7 +8783,7 @@
         <v>3.15</v>
       </c>
       <c r="AJ20" s="13" t="s">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="AK20" s="16">
         <v>4.15</v>
@@ -8390,16 +8881,16 @@
         <v>7.5</v>
       </c>
       <c r="BT20" s="13" t="s">
-        <v>371</v>
+        <v>419</v>
       </c>
       <c r="BU20" s="13" t="s">
-        <v>372</v>
+        <v>420</v>
       </c>
       <c r="BV20" s="13" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="BW20" s="13" t="s">
-        <v>373</v>
+        <v>421</v>
       </c>
       <c r="BX20" s="17">
         <f t="shared" si="27"/>
@@ -8413,25 +8904,38 @@
         <f t="shared" si="30"/>
         <v>46261</v>
       </c>
-    </row>
-    <row r="21" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA20" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="CB20" s="17" t="s">
+        <v>422</v>
+      </c>
+      <c r="CC20" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="CD20" s="19">
+        <f>IF(OR(L20="",L20="not collected",CC20=""),"",ROUND((BZ20+TIMEVALUE(CC20)-BX20-TIMEVALUE(CA20))*24,1))</f>
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
-        <v>374</v>
+        <v>424</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G21" s="13" t="str">
         <f t="shared" si="0"/>
@@ -8449,10 +8953,10 @@
         <v>Y</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>376</v>
+        <v>426</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>377</v>
+        <v>427</v>
       </c>
       <c r="M21" s="17">
         <f t="shared" si="1"/>
@@ -8467,7 +8971,7 @@
         <v>Y</v>
       </c>
       <c r="P21" s="13" t="str">
-        <f>IF(N21="","Y",IF(N21&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD21="","Y",IF(CD21&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="Q21" s="18">
@@ -8588,40 +9092,46 @@
       <c r="BJ21" s="18">
         <v>0.41</v>
       </c>
+      <c r="BK21" t="s">
+        <v>326</v>
+      </c>
+      <c r="BM21" t="s">
+        <v>384</v>
+      </c>
       <c r="BN21" s="13" t="str">
         <f t="shared" si="23"/>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="BO21" s="13" t="str">
         <f t="shared" si="24"/>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="BP21" s="18">
         <f t="shared" si="25"/>
         <v>0.41</v>
       </c>
-      <c r="BQ21" s="18">
+      <c r="BQ21" s="18" t="str">
         <f t="shared" si="26"/>
-        <v>0.41</v>
+        <v/>
       </c>
       <c r="BR21" s="13" t="str">
         <f>IF(AND(BO21="Y",COUNTIFS($BX$5:$BX21,$BX21,$BO$5:$BO21,"Y")=1),"Y","N")</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="BS21" s="19">
         <v>7.9</v>
       </c>
       <c r="BT21" s="13" t="s">
-        <v>378</v>
+        <v>428</v>
       </c>
       <c r="BU21" s="13" t="s">
-        <v>379</v>
+        <v>429</v>
       </c>
       <c r="BV21" s="13" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="BW21" s="13" t="s">
-        <v>380</v>
+        <v>430</v>
       </c>
       <c r="BX21" s="17">
         <f t="shared" si="27"/>
@@ -8635,25 +9145,38 @@
         <f t="shared" si="30"/>
         <v>46279</v>
       </c>
-    </row>
-    <row r="22" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA21" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="CB21" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="CC21" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="CD21" s="19">
+        <f>IF(OR(L21="",L21="not collected",CC21=""),"",ROUND((BZ21+TIMEVALUE(CC21)-BX21-TIMEVALUE(CA21))*24,1))</f>
+        <v>123.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
-        <v>381</v>
+        <v>432</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G22" s="13" t="str">
         <f t="shared" si="0"/>
@@ -8671,10 +9194,10 @@
         <v>Y</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>383</v>
+        <v>434</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>384</v>
+        <v>435</v>
       </c>
       <c r="M22" s="17">
         <f t="shared" si="1"/>
@@ -8689,14 +9212,14 @@
         <v>Y</v>
       </c>
       <c r="P22" s="13" t="str">
-        <f>IF(N22="","Y",IF(N22&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD22="","Y",IF(CD22&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="Q22" s="18">
         <v>0.005</v>
       </c>
       <c r="R22" s="13" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="U22" s="13" t="str">
         <f t="shared" si="3"/>
@@ -8837,13 +9360,13 @@
         <v>7.3</v>
       </c>
       <c r="BT22" s="13" t="s">
-        <v>385</v>
+        <v>436</v>
       </c>
       <c r="BU22" s="13" t="s">
-        <v>386</v>
+        <v>437</v>
       </c>
       <c r="BV22" s="13" t="s">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="BX22" s="17">
         <f t="shared" si="27"/>
@@ -8857,25 +9380,38 @@
         <f t="shared" si="30"/>
         <v>46293</v>
       </c>
-    </row>
-    <row r="23" spans="1:78" x14ac:dyDescent="0.2">
+      <c r="CA22" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="CB22" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="CC22" s="17" t="s">
+        <v>439</v>
+      </c>
+      <c r="CD22" s="19">
+        <f>IF(OR(L22="",L22="not collected",CC22=""),"",ROUND((BZ22+TIMEVALUE(CC22)-BX22-TIMEVALUE(CA22))*24,1))</f>
+        <v>151.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A23" s="13" t="s">
-        <v>387</v>
+        <v>440</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>388</v>
+        <v>441</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>389</v>
+        <v>442</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G23" s="13" t="str">
         <f t="shared" si="0"/>
@@ -8893,10 +9429,10 @@
         <v>Y</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>364</v>
+        <v>411</v>
       </c>
       <c r="M23" s="17">
         <f t="shared" si="1"/>
@@ -8911,14 +9447,14 @@
         <v>Y</v>
       </c>
       <c r="P23" s="13" t="str">
-        <f>IF(N23="","Y",IF(N23&lt;=Parameters!$B$24,"Y","N"))</f>
+        <f>IF(CD23="","Y",IF(CD23&lt;=Parameters!$B$31,"Y","N"))</f>
         <v>Y</v>
       </c>
       <c r="Q23" s="18">
         <v>0.005</v>
       </c>
       <c r="R23" s="13" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="U23" s="13" t="str">
         <f t="shared" si="3"/>
@@ -9033,7 +9569,7 @@
         <v>Y</v>
       </c>
       <c r="BK23" s="13" t="s">
-        <v>314</v>
+        <v>348</v>
       </c>
       <c r="BN23" s="13" t="str">
         <f t="shared" si="23"/>
@@ -9059,16 +9595,16 @@
         <v>7.4</v>
       </c>
       <c r="BT23" s="13" t="s">
-        <v>391</v>
+        <v>444</v>
       </c>
       <c r="BU23" s="13" t="s">
-        <v>386</v>
+        <v>437</v>
       </c>
       <c r="BV23" s="13" t="s">
-        <v>388</v>
+        <v>441</v>
       </c>
       <c r="BW23" s="13" t="s">
-        <v>392</v>
+        <v>445</v>
       </c>
       <c r="BX23" s="17">
         <f t="shared" si="27"/>
@@ -9077,6 +9613,17 @@
       <c r="BY23" s="17">
         <f>DATE(VALUE(RIGHT(K23,4)),VALUE(LEFT(K23,2)),VALUE(MID(K23,4,2)))</f>
         <v>46291</v>
+      </c>
+      <c r="CA23" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="CB23" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="CC23" s="17"/>
+      <c r="CD23" s="19" t="str">
+        <f>IF(OR(L23="",L23="not collected",CC23=""),"",ROUND((BZ23+TIMEVALUE(CC23)-BX23-TIMEVALUE(CA23))*24,1))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -9100,26 +9647,26 @@
   <sheetData>
     <row r="1" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>393</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
-        <v>394</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>395</v>
+        <v>450</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>396</v>
+        <v>451</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>8</v>
@@ -9128,27 +9675,27 @@
         <v>9</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>397</v>
+        <v>452</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>398</v>
+        <v>453</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>399</v>
+        <v>454</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>400</v>
+        <v>455</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>401</v>
+        <v>456</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>402</v>
+        <v>457</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>15</v>
@@ -9196,7 +9743,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>16</v>
@@ -9244,7 +9791,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>17</v>
@@ -9292,7 +9839,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>18</v>
@@ -9340,7 +9887,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>19</v>
@@ -9388,7 +9935,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>20</v>
@@ -9403,7 +9950,7 @@
       </c>
       <c r="E10" s="17">
         <f>COUNTIFS('Lab Data'!$C$5:$C$23,"Jul",'Lab Data'!$BN$5:$BN$23,"Y")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="17">
         <f>Parameters!$B$15</f>
@@ -9411,11 +9958,11 @@
       </c>
       <c r="G10" s="18">
         <f>IF(E10=0,"none",ROUND(AVERAGEIFS('Lab Data'!$BP$5:$BP$23,'Lab Data'!$C$5:$C$23,"Jul",'Lab Data'!$BN$5:$BN$23,"Y"),3))</f>
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="H10" s="18">
         <f>IF(E10=0,"none",_xlfn.MAXIFS('Lab Data'!$BP$5:$BP$23,'Lab Data'!$C$5:$C$23,"Jul",'Lab Data'!$BN$5:$BN$23,"Y"))</f>
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="I10" s="13" t="str">
         <f t="shared" si="0"/>
@@ -9427,16 +9974,16 @@
       </c>
       <c r="K10" s="13" t="str">
         <f>IF(AND(E10&gt;=F10,L10&gt;=Parameters!$B$30),"Met","Below frequency")</f>
-        <v>Met</v>
+        <v>Below frequency</v>
       </c>
       <c r="L10" s="17">
         <f>IF(E10=0,0,_xlfn.MAXIFS('Lab Data'!$BX$5:$BX$23,'Lab Data'!$C$5:$C$23,"Jul",'Lab Data'!$BN$5:$BN$23,"Y")-_xlfn.MINIFS('Lab Data'!$BX$5:$BX$23,'Lab Data'!$C$5:$C$23,"Jul",'Lab Data'!$BN$5:$BN$23,"Y"))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>15</v>
@@ -9484,7 +10031,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>16</v>
@@ -9532,7 +10079,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>17</v>
@@ -9580,7 +10127,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>18</v>
@@ -9628,7 +10175,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>19</v>
@@ -9676,7 +10223,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>20</v>
@@ -9724,7 +10271,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>15</v>
@@ -9772,7 +10319,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>16</v>
@@ -9820,7 +10367,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>17</v>
@@ -9868,7 +10415,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>18</v>
@@ -9916,7 +10463,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>19</v>
@@ -9964,7 +10511,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>20</v>
@@ -9979,7 +10526,7 @@
       </c>
       <c r="E22" s="17">
         <f>COUNTIFS('Lab Data'!$C$5:$C$23,"Sep",'Lab Data'!$BN$5:$BN$23,"Y")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" s="17">
         <f>Parameters!$B$15</f>
@@ -9987,11 +10534,11 @@
       </c>
       <c r="G22" s="18">
         <f>IF(E22=0,"none",ROUND(AVERAGEIFS('Lab Data'!$BP$5:$BP$23,'Lab Data'!$C$5:$C$23,"Sep",'Lab Data'!$BN$5:$BN$23,"Y"),3))</f>
-        <v>0.325</v>
+        <v>0.24</v>
       </c>
       <c r="H22" s="18">
         <f>IF(E22=0,"none",_xlfn.MAXIFS('Lab Data'!$BP$5:$BP$23,'Lab Data'!$C$5:$C$23,"Sep",'Lab Data'!$BN$5:$BN$23,"Y"))</f>
-        <v>0.41</v>
+        <v>0.24</v>
       </c>
       <c r="I22" s="13" t="str">
         <f t="shared" si="0"/>
@@ -10003,11 +10550,11 @@
       </c>
       <c r="K22" s="13" t="str">
         <f>IF(AND(E22&gt;=F22,L22&gt;=Parameters!$B$30),"Met","Below frequency")</f>
-        <v>Met</v>
+        <v>Below frequency</v>
       </c>
       <c r="L22" s="17">
         <f>IF(E22=0,0,_xlfn.MAXIFS('Lab Data'!$BX$5:$BX$23,'Lab Data'!$C$5:$C$23,"Sep",'Lab Data'!$BN$5:$BN$23,"Y")-_xlfn.MINIFS('Lab Data'!$BX$5:$BX$23,'Lab Data'!$C$5:$C$23,"Sep",'Lab Data'!$BN$5:$BN$23,"Y"))</f>
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10017,7 +10564,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -10036,12 +10583,12 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>403</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
-        <v>404</v>
+        <v>459</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -10049,43 +10596,43 @@
         <v>5</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>405</v>
+        <v>460</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>395</v>
+        <v>450</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>406</v>
+        <v>461</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>407</v>
+        <v>462</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>408</v>
+        <v>463</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>409</v>
+        <v>464</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>410</v>
+        <v>465</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>411</v>
+        <v>466</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>412</v>
+        <v>467</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>413</v>
+        <v>468</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>414</v>
+        <v>469</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>416</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -10379,7 +10926,7 @@
       </c>
       <c r="B10" s="17">
         <f>COUNTIFS('Lab Data'!$BR$5:$BR$23,"Y")</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C10" s="16">
         <f>Parameters!$B$9</f>
@@ -10432,320 +10979,340 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
-        <v>417</v>
+        <v>472</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
-        <v>418</v>
+        <v>473</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>419</v>
+        <v>474</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>420</v>
+        <v>475</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>421</v>
+        <v>476</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="21" t="s">
-        <v>422</v>
+        <v>477</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>423</v>
+        <v>478</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>424</v>
+        <v>479</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="21" t="s">
-        <v>425</v>
+        <v>480</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>426</v>
+        <v>481</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>427</v>
+        <v>482</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="21" t="s">
-        <v>429</v>
+        <v>484</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>431</v>
+        <v>486</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="21" t="s">
-        <v>433</v>
+        <v>488</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>434</v>
+        <v>489</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>435</v>
+        <v>490</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21" t="s">
-        <v>437</v>
+        <v>492</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>438</v>
+        <v>493</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>439</v>
+        <v>494</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="21" t="s">
-        <v>441</v>
+        <v>496</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>442</v>
+        <v>497</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>443</v>
+        <v>498</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="21" t="s">
-        <v>445</v>
+        <v>500</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>446</v>
+        <v>501</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>447</v>
+        <v>502</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="21" t="s">
-        <v>449</v>
+        <v>484</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>450</v>
+        <v>489</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>451</v>
+        <v>504</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21" t="s">
-        <v>449</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>450</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>451</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21" t="s">
-        <v>455</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>456</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>457</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="21" t="s">
+        <v>505</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>489</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>506</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>509</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="21" t="s">
-        <v>459</v>
+        <v>510</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>460</v>
+        <v>511</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>461</v>
+        <v>512</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="21" t="s">
-        <v>463</v>
+        <v>514</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>464</v>
+        <v>515</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>465</v>
+        <v>516</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="21" t="s">
-        <v>463</v>
+        <v>518</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>467</v>
+        <v>519</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>468</v>
+        <v>520</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="21" t="s">
-        <v>470</v>
+        <v>522</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>467</v>
+        <v>523</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>471</v>
+        <v>524</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="21" t="s">
-        <v>473</v>
+        <v>522</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>474</v>
+        <v>526</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>475</v>
+        <v>527</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="15" t="s">
-        <v>477</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>478</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>479</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>480</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>481</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="13" t="s">
-        <v>483</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>484</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>485</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>486</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>487</v>
-      </c>
-      <c r="F33" s="17">
-        <f>_xlfn.DAYS(DATE(2026,6,4),DATE(2026,4,15))</f>
-        <v>50</v>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="21" t="s">
+        <v>529</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>526</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>530</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="21" t="s">
+        <v>532</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>533</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="13" t="s">
-        <v>488</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>489</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>490</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>491</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="F34" s="17">
-        <f>_xlfn.DAYS(DATE(2026,7,14),DATE(2026,7,15))</f>
-        <v>-1</v>
+      <c r="A34" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>537</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>538</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>539</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>540</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="13" t="s">
-        <v>492</v>
+        <v>542</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>543</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>544</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>545</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>546</v>
+      </c>
+      <c r="F35" s="17">
+        <f>_xlfn.DAYS(DATE(2026,5,28),DATE(2026,4,15))</f>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="B36" s="26" t="str">
-        <f>IF(OR(D33="Significant noncompliance",COUNTIFS(L7:L12,"Significant noncompliance")&gt;0),"Significant noncompliance","Not in significant noncompliance")</f>
+      <c r="A36" s="13" t="s">
+        <v>547</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="F36" s="17">
+        <f>_xlfn.DAYS(DATE(2026,8,31),DATE(2026,7,15))</f>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="13" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="B38" s="26" t="str">
+        <f>IF(OR(D35="Significant noncompliance",D36="Significant noncompliance",COUNTIFS(L5:L10,"Significant noncompliance")&gt;0),"Significant noncompliance","Not in significant noncompliance")</f>
         <v>Significant noncompliance</v>
       </c>
     </row>
@@ -10756,7 +11323,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -10764,49 +11331,53 @@
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>495</v>
+        <v>553</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>496</v>
+        <v>554</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>555</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>498</v>
+        <v>557</v>
       </c>
       <c r="C4" s="7">
         <v>4850733</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>499</v>
+        <v>558</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C5" s="7">
         <v>4888995</v>
@@ -10820,12 +11391,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>500</v>
+        <v>559</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C6" s="7">
         <v>4928908</v>
@@ -10839,12 +11410,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>501</v>
+        <v>560</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C7" s="7">
         <v>4928908</v>
@@ -10858,12 +11429,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>502</v>
+        <v>561</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C8" s="7">
         <v>4930795</v>
@@ -10877,12 +11448,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>503</v>
+        <v>562</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C9" s="7">
         <v>4934115</v>
@@ -10896,12 +11467,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>504</v>
+        <v>563</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C10" s="7">
         <v>4966879</v>
@@ -10915,12 +11486,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>334</v>
+        <v>373</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C11" s="7">
         <v>5005480</v>
@@ -10934,12 +11505,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>505</v>
+        <v>564</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C12" s="7">
         <v>5040060</v>
@@ -10953,12 +11524,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>506</v>
+        <v>565</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C13" s="7">
         <v>5073651</v>
@@ -10972,12 +11543,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>507</v>
+        <v>566</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C14" s="7">
         <v>5109294</v>
@@ -10991,12 +11562,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>336</v>
+        <v>375</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C15" s="7">
         <v>5111030</v>
@@ -11010,12 +11581,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>508</v>
+        <v>567</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C16" s="7">
         <v>5113301</v>
@@ -11031,10 +11602,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>337</v>
+        <v>376</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C17" s="7">
         <v>5144730</v>
@@ -11050,10 +11621,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>490</v>
+        <v>568</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C18" s="7">
         <v>5182044</v>
@@ -11069,10 +11640,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>489</v>
+        <v>548</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C19" s="7">
         <v>5214542</v>
@@ -11088,10 +11659,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>509</v>
+        <v>569</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C20" s="7">
         <v>5244482</v>
@@ -11107,7 +11678,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>510</v>
+        <v>570</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="7">
@@ -11118,10 +11689,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>511</v>
+        <v>571</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C22" s="7">
         <v>30947</v>
@@ -11137,10 +11708,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>512</v>
+        <v>572</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C23" s="7">
         <v>33477</v>
@@ -11156,10 +11727,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>513</v>
+        <v>573</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C24" s="7">
         <v>36718</v>
@@ -11175,10 +11746,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>514</v>
+        <v>574</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C25" s="7">
         <v>63743</v>
@@ -11197,7 +11768,7 @@
         <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C26" s="7">
         <v>103622</v>
@@ -11213,10 +11784,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>515</v>
+        <v>575</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C27" s="7">
         <v>136325</v>
@@ -11232,10 +11803,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>516</v>
+        <v>576</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C28" s="7">
         <v>176511</v>
@@ -11251,10 +11822,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>517</v>
+        <v>577</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C29" s="7">
         <v>216356</v>
@@ -11270,10 +11841,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>342</v>
+        <v>578</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C30" s="7">
         <v>220335</v>
@@ -11289,10 +11860,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C31" s="7">
         <v>223792</v>
@@ -11308,10 +11879,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>518</v>
+        <v>579</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C32" s="7">
         <v>262703</v>
@@ -11327,10 +11898,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>519</v>
+        <v>580</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C33" s="7">
         <v>307583</v>
@@ -11346,10 +11917,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>520</v>
+        <v>581</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C34" s="7">
         <v>336064</v>
@@ -11365,10 +11936,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>521</v>
+        <v>582</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C35" s="7">
         <v>365173</v>
@@ -11384,10 +11955,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>522</v>
+        <v>57</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="C36" s="7">
         <v>402867</v>
@@ -11403,10 +11974,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>523</v>
+        <v>583</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C37" s="7">
         <v>405823</v>
@@ -11422,10 +11993,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>524</v>
+        <v>584</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C38" s="7">
         <v>408837</v>
@@ -11441,10 +12012,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>525</v>
+        <v>585</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C39" s="7">
         <v>446931</v>
@@ -11460,10 +12031,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>526</v>
+        <v>383</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C40" s="7">
         <v>475421</v>
@@ -11479,10 +12050,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>527</v>
+        <v>586</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C41" s="7">
         <v>515786</v>
@@ -11498,10 +12069,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>528</v>
+        <v>587</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C42" s="7">
         <v>543050</v>
@@ -11517,10 +12088,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>529</v>
+        <v>588</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C43" s="7">
         <v>571652</v>
@@ -11536,10 +12107,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>530</v>
+        <v>589</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C44" s="7">
         <v>575017</v>
@@ -11555,10 +12126,10 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>531</v>
+        <v>590</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C45" s="7">
         <v>576705</v>
@@ -11574,10 +12145,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>532</v>
+        <v>591</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C46" s="7">
         <v>617789</v>
@@ -11593,10 +12164,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C47" s="7">
         <v>657599</v>
@@ -11612,10 +12183,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>533</v>
+        <v>592</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C48" s="7">
         <v>686236</v>
@@ -11631,10 +12202,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C49" s="7">
         <v>732386</v>
@@ -11650,10 +12221,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C50" s="7">
         <v>770652</v>
@@ -11669,10 +12240,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>349</v>
+        <v>392</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C51" s="7">
         <v>773235</v>
@@ -11688,10 +12259,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>534</v>
+        <v>593</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C52" s="7">
         <v>775779</v>
@@ -11707,10 +12278,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>535</v>
+        <v>594</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C53" s="7">
         <v>815883</v>
@@ -11726,10 +12297,10 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>360</v>
+        <v>405</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C54" s="7">
         <v>846590</v>
@@ -11745,10 +12316,10 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C55" s="7">
         <v>880719</v>
@@ -11764,10 +12335,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C56" s="7">
         <v>914241</v>
@@ -11783,10 +12354,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C57" s="7">
         <v>947766</v>
@@ -11802,10 +12373,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>536</v>
+        <v>595</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C58" s="7">
         <v>951034</v>
@@ -11821,10 +12392,10 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>356</v>
+        <v>401</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C59" s="7">
         <v>954056</v>
@@ -11840,10 +12411,10 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>357</v>
+        <v>402</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C60" s="7">
         <v>994354</v>
@@ -11859,10 +12430,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C61" s="7">
         <v>1030494</v>
@@ -11878,10 +12449,10 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>350</v>
+        <v>393</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C62" s="7">
         <v>1064357</v>
@@ -11897,10 +12468,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C63" s="7">
         <v>1099817</v>
@@ -11916,10 +12487,10 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C64" s="7">
         <v>1133887</v>
@@ -11933,12 +12504,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>370</v>
+        <v>418</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C65" s="7">
         <v>1136948</v>
@@ -11952,12 +12523,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C66" s="7">
         <v>1139175</v>
@@ -11971,12 +12542,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>538</v>
+        <v>103</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="C67" s="7">
         <v>1173773</v>
@@ -11989,13 +12560,16 @@
         <f>IF(D67&gt;Parameters!$B$12,"Yes","No")</f>
         <v>No</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F67" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>539</v>
+        <v>598</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C68" s="7">
         <v>1206477</v>
@@ -12009,12 +12583,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>540</v>
+        <v>599</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C69" s="7">
         <v>1247070</v>
@@ -12028,12 +12602,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>541</v>
+        <v>600</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C70" s="7">
         <v>1279366</v>
@@ -12047,12 +12621,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>542</v>
+        <v>601</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C71" s="7">
         <v>1317021</v>
@@ -12066,12 +12640,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>543</v>
+        <v>602</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C72" s="7">
         <v>1320630</v>
@@ -12085,12 +12659,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>544</v>
+        <v>603</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C73" s="7">
         <v>1322605</v>
@@ -12104,12 +12678,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>545</v>
+        <v>604</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C74" s="7">
         <v>1322605</v>
@@ -12123,12 +12697,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>546</v>
+        <v>605</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C75" s="7">
         <v>1357287</v>
@@ -12142,12 +12716,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C76" s="7">
         <v>1400937</v>
@@ -12161,12 +12735,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C77" s="7">
         <v>1432667</v>
@@ -12180,12 +12754,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>547</v>
+        <v>606</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C78" s="7">
         <v>1461510</v>
@@ -12199,12 +12773,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>376</v>
+        <v>426</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C79" s="7">
         <v>1464312</v>
@@ -12218,12 +12792,12 @@
         <v>No</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>548</v>
+        <v>607</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C80" s="7">
         <v>1468092</v>
@@ -12239,10 +12813,10 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>377</v>
+        <v>427</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C81" s="7">
         <v>1505401</v>
@@ -12258,10 +12832,10 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C82" s="7">
         <v>1540238</v>
@@ -12277,10 +12851,10 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>549</v>
+        <v>608</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C83" s="7">
         <v>1580202</v>
@@ -12296,10 +12870,10 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C84" s="7">
         <v>1608512</v>
@@ -12315,10 +12889,10 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>550</v>
+        <v>609</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C85" s="7">
         <v>1641947</v>
@@ -12334,10 +12908,10 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>551</v>
+        <v>610</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C86" s="7">
         <v>1646101</v>
@@ -12353,10 +12927,10 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>552</v>
+        <v>611</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C87" s="7">
         <v>1649973</v>
@@ -12372,10 +12946,10 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>553</v>
+        <v>612</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C88" s="7">
         <v>1690504</v>
@@ -12391,10 +12965,10 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C89" s="7">
         <v>1724632</v>
@@ -12410,10 +12984,10 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>388</v>
+        <v>441</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C90" s="7">
         <v>1752661</v>
@@ -12429,10 +13003,10 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>554</v>
+        <v>613</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C91" s="7">
         <v>1780577</v>
@@ -12448,10 +13022,10 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>555</v>
+        <v>609</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C92" s="7">
         <v>1819521</v>
@@ -12467,10 +13041,10 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C93" s="7">
         <v>1823199</v>
@@ -12486,10 +13060,10 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>556</v>
+        <v>614</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C94" s="7">
         <v>1825943</v>
@@ -12505,10 +13079,10 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>384</v>
+        <v>435</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C95" s="7">
         <v>1860669</v>
@@ -12524,10 +13098,10 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>383</v>
+        <v>434</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C96" s="7">
         <v>1891352</v>
@@ -12543,10 +13117,10 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="C97" s="7">
         <v>1925843</v>
@@ -12568,16 +13142,16 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>557</v>
+        <v>615</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>558</v>
+        <v>616</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>559</v>
+        <v>617</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
@@ -12599,7 +13173,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B101" s="10">
         <f>_xlfn.MAXIFS($D$5:$D$97,$B$5:$B$97,"Aug")</f>
@@ -12616,7 +13190,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="8" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="B102" s="10">
         <f>_xlfn.MAXIFS($D$5:$D$97,$B$5:$B$97,"Sep")</f>
@@ -12637,7 +13211,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
-        <v>560</v>
+        <v>618</v>
       </c>
       <c r="D104" s="10">
         <f>SUM(D5:D97)</f>
@@ -12650,15 +13224,15 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>561</v>
+        <v>619</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>562</v>
+        <v>620</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
-        <v>563</v>
+        <v>621</v>
       </c>
       <c r="B107" s="10">
         <f>D76</f>
@@ -12667,7 +13241,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
-        <v>564</v>
+        <v>622</v>
       </c>
       <c r="B108" s="10">
         <v>2900</v>
@@ -12675,7 +13249,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
-        <v>565</v>
+        <v>623</v>
       </c>
       <c r="B109" s="10">
         <f>SUM(B107:B108)</f>
@@ -12684,7 +13258,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
-        <v>566</v>
+        <v>624</v>
       </c>
       <c r="B110" s="10">
         <f>MAX(B102,B109)</f>
@@ -12698,7 +13272,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -12712,377 +13286,377 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>567</v>
+        <v>625</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
-        <v>568</v>
+        <v>626</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
-        <v>569</v>
+        <v>627</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>570</v>
+        <v>628</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>571</v>
+        <v>629</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>478</v>
+        <v>537</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>572</v>
+        <v>630</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
-        <v>574</v>
+        <v>632</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>575</v>
+        <v>633</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>576</v>
+        <v>634</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>577</v>
+        <v>635</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>578</v>
+        <v>636</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="21" t="s">
-        <v>579</v>
+        <v>637</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>575</v>
+        <v>633</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>576</v>
+        <v>634</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>580</v>
+        <v>638</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>578</v>
+        <v>636</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
-        <v>581</v>
+        <v>639</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>582</v>
+        <v>640</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>583</v>
+        <v>641</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>584</v>
+        <v>642</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>585</v>
+        <v>643</v>
       </c>
       <c r="G6" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="21" t="s">
-        <v>586</v>
+        <v>644</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>582</v>
+        <v>640</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>576</v>
+        <v>634</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>370</v>
+        <v>418</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>587</v>
+        <v>645</v>
       </c>
       <c r="G7" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="21" t="s">
-        <v>588</v>
+        <v>646</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>589</v>
+        <v>640</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>583</v>
+        <v>647</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>590</v>
+        <v>57</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>75</v>
+        <v>648</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>591</v>
+        <v>649</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="21" t="s">
-        <v>592</v>
+        <v>650</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>593</v>
+        <v>651</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>583</v>
+        <v>641</v>
       </c>
       <c r="E9" s="21" t="s">
+        <v>652</v>
+      </c>
+      <c r="F9" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="F9" s="21" t="s">
-        <v>75</v>
-      </c>
       <c r="G9" s="21" t="s">
-        <v>591</v>
+        <v>649</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="21" t="s">
-        <v>594</v>
+        <v>653</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>78</v>
+        <v>654</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>595</v>
+        <v>641</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>596</v>
+        <v>83</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="21" t="s">
-        <v>597</v>
+        <v>655</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>598</v>
+        <v>86</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>583</v>
+        <v>656</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>599</v>
+        <v>95</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>600</v>
+        <v>657</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="21" t="s">
-        <v>601</v>
+        <v>658</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>598</v>
+        <v>659</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>576</v>
+        <v>641</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>555</v>
+        <v>660</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>602</v>
+        <v>661</v>
       </c>
       <c r="G12" s="21" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="21" t="s">
+        <v>662</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>659</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>634</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>609</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>663</v>
+      </c>
+      <c r="G13" s="21" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="21" t="s">
-        <v>603</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>604</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>583</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>605</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>606</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="21" t="s">
-        <v>607</v>
+        <v>664</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>604</v>
+        <v>665</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>576</v>
+        <v>641</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>390</v>
+        <v>666</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>602</v>
+        <v>667</v>
       </c>
       <c r="G14" s="21" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="21" t="s">
+        <v>668</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>665</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>634</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>663</v>
+      </c>
+      <c r="G15" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
-        <v>608</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>609</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>610</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>583</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>611</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>612</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="21" t="s">
-        <v>613</v>
+        <v>669</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C16" s="21" t="s">
+        <v>665</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>647</v>
+      </c>
+      <c r="E16" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="D16" s="21" t="s">
-        <v>595</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>377</v>
-      </c>
       <c r="F16" s="21" t="s">
-        <v>377</v>
+        <v>670</v>
       </c>
       <c r="G16" s="21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="21" t="s">
-        <v>614</v>
+        <v>671</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>74</v>
+        <v>672</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>615</v>
+        <v>673</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>583</v>
+        <v>641</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>616</v>
+        <v>674</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>75</v>
+        <v>675</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>591</v>
+        <v>636</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="21" t="s">
-        <v>617</v>
+        <v>676</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>615</v>
+        <v>114</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>576</v>
+        <v>656</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>618</v>
+        <v>427</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>619</v>
+        <v>427</v>
       </c>
       <c r="G18" s="21" t="s">
         <v>25</v>
@@ -13090,45 +13664,45 @@
     </row>
     <row r="19" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21" t="s">
-        <v>620</v>
+        <v>677</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>621</v>
+        <v>678</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>583</v>
+        <v>641</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>622</v>
+        <v>679</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>623</v>
+        <v>83</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="21" t="s">
-        <v>624</v>
+        <v>680</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>621</v>
+        <v>678</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>576</v>
+        <v>634</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>625</v>
+        <v>681</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>626</v>
+        <v>682</v>
       </c>
       <c r="G20" s="21" t="s">
         <v>25</v>
@@ -13136,169 +13710,242 @@
     </row>
     <row r="21" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="21" t="s">
-        <v>627</v>
+        <v>683</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>628</v>
+        <v>684</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>583</v>
+        <v>641</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>629</v>
+        <v>685</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>630</v>
+        <v>686</v>
       </c>
       <c r="G21" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="21" t="s">
-        <v>631</v>
+        <v>687</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>125</v>
+        <v>684</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>595</v>
+        <v>634</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>382</v>
+        <v>688</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>553</v>
+        <v>689</v>
       </c>
       <c r="G22" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="21" t="s">
-        <v>632</v>
+        <v>690</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>633</v>
+        <v>61</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>634</v>
+        <v>691</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>489</v>
+        <v>123</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="G23" s="21" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="21" t="s">
+        <v>692</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>693</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>641</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>694</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>695</v>
+      </c>
+      <c r="G24" s="21" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21" t="s">
-        <v>637</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>638</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>639</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>640</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>625</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>641</v>
-      </c>
-      <c r="G24" s="21" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
-        <v>643</v>
+        <v>696</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>644</v>
+        <v>82</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>645</v>
+        <v>140</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>647</v>
+        <v>433</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>648</v>
+        <v>612</v>
       </c>
       <c r="G25" s="21" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="13" t="s">
-        <v>652</v>
-      </c>
-      <c r="B28" s="17">
-        <f>COUNTIFS($G$4:$G$25,"Met")</f>
-        <v>11</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="21" t="s">
+        <v>697</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>698</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>699</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>700</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>548</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>701</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="21" t="s">
+        <v>702</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>703</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>704</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>705</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>688</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>706</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="21" t="s">
+        <v>708</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>709</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>710</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>711</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>712</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>713</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="13" t="s">
-        <v>653</v>
-      </c>
-      <c r="B29" s="17">
-        <f>COUNTIFS($G$4:$G$25,"Late")</f>
-        <v>5</v>
-      </c>
+      <c r="A29" s="13"/>
+      <c r="B29" s="17"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="13" t="s">
-        <v>654</v>
-      </c>
-      <c r="B30" s="17">
-        <f>COUNTIFS($G$4:$G$25,"Not made")</f>
-        <v>4</v>
+      <c r="A30" s="15" t="s">
+        <v>715</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="13" t="s">
-        <v>655</v>
-      </c>
-      <c r="B31" s="17">
-        <f>COUNTIFS($G$4:$G$25,"Pending")</f>
+      <c r="A31" s="21" t="s">
+        <v>717</v>
+      </c>
+      <c r="B31" s="21">
+        <f>COUNTIFS($G$4:$G$28,"Met")</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="21" t="s">
+        <v>718</v>
+      </c>
+      <c r="B32" s="21">
+        <f>COUNTIFS($G$4:$G$28,"Late")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="21" t="s">
+        <v>719</v>
+      </c>
+      <c r="B33" s="21">
+        <f>COUNTIFS($G$4:$G$28,"Not made")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="21" t="s">
+        <v>720</v>
+      </c>
+      <c r="B34" s="21">
+        <f>COUNTIFS($G$4:$G$28,"Pending")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="13" t="s">
-        <v>656</v>
-      </c>
-      <c r="B32" s="17">
-        <f>COUNTIFS($G$4:$G$25,"Open")</f>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="21" t="s">
+        <v>721</v>
+      </c>
+      <c r="B35" s="21">
+        <f>COUNTIFS($G$4:$G$28,"Open")</f>
         <v>1</v>
       </c>
     </row>
@@ -13309,7 +13956,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="118" customWidth="1"/>
@@ -13317,92 +13964,97 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="26" t="s">
-        <v>657</v>
+        <v>722</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
-        <v>658</v>
+        <v>723</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="21" t="s">
-        <v>660</v>
+        <v>725</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
-        <v>661</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="21" t="s">
-        <v>662</v>
+        <v>727</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="21" t="s">
-        <v>663</v>
+        <v>728</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="21" t="s">
-        <v>664</v>
+        <v>729</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="21" t="s">
-        <v>665</v>
+        <v>730</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="98" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="21" t="s">
-        <v>666</v>
+        <v>731</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="21" t="s">
-        <v>667</v>
+        <v>732</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="21" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="21" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="70" customHeight="1" x14ac:dyDescent="0.2">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="21" t="s">
-        <v>671</v>
+        <v>736</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="98" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="21" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="21" t="s">
-        <v>673</v>
+        <v>738</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21" t="s">
-        <v>674</v>
+        <v>739</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="21" t="s">
+        <v>740</v>
       </c>
     </row>
   </sheetData>
